--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -905,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119713735</v>
+        <v>119713553</v>
       </c>
       <c r="B4" t="n">
         <v>97907</v>
@@ -940,12 +940,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -957,14 +957,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fanfluken, Sura sn, Vstm</t>
+          <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558369</v>
+        <v>558372</v>
       </c>
       <c r="R4" t="n">
-        <v>6624275</v>
+        <v>6624267</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1007,11 +1007,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Enstaka överblommade plantor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1168,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119713553</v>
+        <v>119713808</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>8432</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1180,54 +1175,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fanfluken, Vstm</t>
+          <t>Fanfluken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558372</v>
+        <v>558363</v>
       </c>
       <c r="R6" t="n">
-        <v>6624267</v>
+        <v>6624123</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1270,6 +1258,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På tall-låga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1297,10 +1290,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119713808</v>
+        <v>119713516</v>
       </c>
       <c r="B7" t="n">
-        <v>8432</v>
+        <v>97907</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1309,36 +1302,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558363</v>
+        <v>558369</v>
       </c>
       <c r="R7" t="n">
-        <v>6624123</v>
+        <v>6624271</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1392,11 +1392,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På tall-låga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1424,7 +1419,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119713763</v>
+        <v>119713818</v>
       </c>
       <c r="B8" t="n">
         <v>97907</v>
@@ -1459,12 +1454,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1480,10 +1475,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558353</v>
+        <v>558246</v>
       </c>
       <c r="R8" t="n">
-        <v>6624271</v>
+        <v>6624165</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1553,10 +1548,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119713775</v>
+        <v>119713512</v>
       </c>
       <c r="B9" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1565,38 +1560,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558433</v>
+        <v>558369</v>
       </c>
       <c r="R9" t="n">
-        <v>6624268</v>
+        <v>6624269</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1650,11 +1650,6 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1682,10 +1677,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119713516</v>
+        <v>119713775</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1694,43 +1689,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1738,10 +1728,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558369</v>
+        <v>558433</v>
       </c>
       <c r="R10" t="n">
-        <v>6624271</v>
+        <v>6624268</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1784,6 +1774,11 @@
       <c r="AB10" t="inlineStr">
         <is>
           <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1811,7 +1806,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119713512</v>
+        <v>119713735</v>
       </c>
       <c r="B11" t="n">
         <v>97907</v>
@@ -1870,7 +1865,7 @@
         <v>558369</v>
       </c>
       <c r="R11" t="n">
-        <v>6624269</v>
+        <v>6624275</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1913,6 +1908,11 @@
       <c r="AB11" t="inlineStr">
         <is>
           <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Enstaka överblommade plantor</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1940,7 +1940,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119713818</v>
+        <v>119713763</v>
       </c>
       <c r="B12" t="n">
         <v>97907</v>
@@ -1975,12 +1975,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558246</v>
+        <v>558353</v>
       </c>
       <c r="R12" t="n">
-        <v>6624165</v>
+        <v>6624271</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -1034,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119713527</v>
+        <v>119713808</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>8432</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,43 +1046,36 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1090,10 +1083,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558367</v>
+        <v>558363</v>
       </c>
       <c r="R5" t="n">
-        <v>6624274</v>
+        <v>6624123</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1136,6 +1129,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På tall-låga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119713808</v>
+        <v>119713527</v>
       </c>
       <c r="B6" t="n">
-        <v>8432</v>
+        <v>97907</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,36 +1173,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1212,10 +1217,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558363</v>
+        <v>558367</v>
       </c>
       <c r="R6" t="n">
-        <v>6624123</v>
+        <v>6624274</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1258,11 +1263,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På tall-låga</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119713553</v>
+        <v>119713775</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,25 +917,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -945,26 +945,21 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fanfluken, Vstm</t>
+          <t>Fanfluken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558372</v>
+        <v>558433</v>
       </c>
       <c r="R4" t="n">
-        <v>6624267</v>
+        <v>6624268</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1007,6 +1002,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119713808</v>
+        <v>119713553</v>
       </c>
       <c r="B5" t="n">
-        <v>8432</v>
+        <v>97907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,47 +1046,54 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fanfluken, Sura sn, Vstm</t>
+          <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558363</v>
+        <v>558372</v>
       </c>
       <c r="R5" t="n">
-        <v>6624123</v>
+        <v>6624267</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1129,11 +1136,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På tall-låga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,7 +1163,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119713527</v>
+        <v>119713512</v>
       </c>
       <c r="B6" t="n">
         <v>97907</v>
@@ -1196,12 +1198,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1217,10 +1219,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558367</v>
+        <v>558369</v>
       </c>
       <c r="R6" t="n">
-        <v>6624274</v>
+        <v>6624269</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1290,7 +1292,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119713516</v>
+        <v>119713735</v>
       </c>
       <c r="B7" t="n">
         <v>97907</v>
@@ -1349,7 +1351,7 @@
         <v>558369</v>
       </c>
       <c r="R7" t="n">
-        <v>6624271</v>
+        <v>6624275</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1392,6 +1394,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Enstaka överblommade plantor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,7 +1426,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119713818</v>
+        <v>119713516</v>
       </c>
       <c r="B8" t="n">
         <v>97907</v>
@@ -1454,12 +1461,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1475,10 +1482,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558246</v>
+        <v>558369</v>
       </c>
       <c r="R8" t="n">
-        <v>6624165</v>
+        <v>6624271</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1548,10 +1555,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119713512</v>
+        <v>119713808</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>8432</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1560,43 +1567,36 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558369</v>
+        <v>558363</v>
       </c>
       <c r="R9" t="n">
-        <v>6624269</v>
+        <v>6624123</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1650,6 +1650,11 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På tall-låga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1677,10 +1682,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119713775</v>
+        <v>119713527</v>
       </c>
       <c r="B10" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1689,25 +1694,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1717,10 +1722,15 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1728,10 +1738,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558433</v>
+        <v>558367</v>
       </c>
       <c r="R10" t="n">
-        <v>6624268</v>
+        <v>6624274</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1774,11 +1784,6 @@
       <c r="AB10" t="inlineStr">
         <is>
           <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1806,7 +1811,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119713735</v>
+        <v>119713763</v>
       </c>
       <c r="B11" t="n">
         <v>97907</v>
@@ -1841,12 +1846,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1862,10 +1867,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558369</v>
+        <v>558353</v>
       </c>
       <c r="R11" t="n">
-        <v>6624275</v>
+        <v>6624271</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1908,11 +1913,6 @@
       <c r="AB11" t="inlineStr">
         <is>
           <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Enstaka överblommade plantor</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1940,7 +1940,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119713763</v>
+        <v>119713818</v>
       </c>
       <c r="B12" t="n">
         <v>97907</v>
@@ -1975,12 +1975,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558353</v>
+        <v>558246</v>
       </c>
       <c r="R12" t="n">
-        <v>6624271</v>
+        <v>6624165</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119713775</v>
+        <v>119713516</v>
       </c>
       <c r="B4" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,38 +917,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -956,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558433</v>
+        <v>558369</v>
       </c>
       <c r="R4" t="n">
-        <v>6624268</v>
+        <v>6624271</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1002,11 +1007,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,7 +1034,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119713553</v>
+        <v>119713512</v>
       </c>
       <c r="B5" t="n">
         <v>97907</v>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1086,14 +1086,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fanfluken, Vstm</t>
+          <t>Fanfluken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558372</v>
+        <v>558369</v>
       </c>
       <c r="R5" t="n">
-        <v>6624267</v>
+        <v>6624269</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1163,7 +1163,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119713512</v>
+        <v>119713763</v>
       </c>
       <c r="B6" t="n">
         <v>97907</v>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558369</v>
+        <v>558353</v>
       </c>
       <c r="R6" t="n">
-        <v>6624269</v>
+        <v>6624271</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119713735</v>
+        <v>119713808</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>8432</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,43 +1304,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1348,10 +1341,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558369</v>
+        <v>558363</v>
       </c>
       <c r="R7" t="n">
-        <v>6624275</v>
+        <v>6624123</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1398,7 +1391,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Enstaka överblommade plantor</t>
+          <t>På tall-låga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1426,10 +1419,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119713516</v>
+        <v>119713775</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1438,43 +1431,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1482,10 +1470,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558369</v>
+        <v>558433</v>
       </c>
       <c r="R8" t="n">
-        <v>6624271</v>
+        <v>6624268</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1528,6 +1516,11 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1555,10 +1548,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119713808</v>
+        <v>119713553</v>
       </c>
       <c r="B9" t="n">
-        <v>8432</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1567,47 +1560,54 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fanfluken, Sura sn, Vstm</t>
+          <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558363</v>
+        <v>558372</v>
       </c>
       <c r="R9" t="n">
-        <v>6624123</v>
+        <v>6624267</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1650,11 +1650,6 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På tall-låga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1682,7 +1677,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119713527</v>
+        <v>119713818</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1717,12 +1712,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1738,10 +1733,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558367</v>
+        <v>558246</v>
       </c>
       <c r="R10" t="n">
-        <v>6624274</v>
+        <v>6624165</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1811,7 +1806,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119713763</v>
+        <v>119713735</v>
       </c>
       <c r="B11" t="n">
         <v>97907</v>
@@ -1846,12 +1841,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1867,10 +1862,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558353</v>
+        <v>558369</v>
       </c>
       <c r="R11" t="n">
-        <v>6624271</v>
+        <v>6624275</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1913,6 +1908,11 @@
       <c r="AB11" t="inlineStr">
         <is>
           <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Enstaka överblommade plantor</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1940,7 +1940,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119713818</v>
+        <v>119713527</v>
       </c>
       <c r="B12" t="n">
         <v>97907</v>
@@ -1975,12 +1975,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558246</v>
+        <v>558367</v>
       </c>
       <c r="R12" t="n">
-        <v>6624165</v>
+        <v>6624274</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -1292,10 +1292,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119713808</v>
+        <v>119713553</v>
       </c>
       <c r="B7" t="n">
-        <v>8432</v>
+        <v>97907</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,47 +1304,54 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fanfluken, Sura sn, Vstm</t>
+          <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558363</v>
+        <v>558372</v>
       </c>
       <c r="R7" t="n">
-        <v>6624123</v>
+        <v>6624267</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1387,11 +1394,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På tall-låga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,10 +1421,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119713775</v>
+        <v>119713808</v>
       </c>
       <c r="B8" t="n">
-        <v>90527</v>
+        <v>8432</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1435,34 +1437,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558433</v>
+        <v>558363</v>
       </c>
       <c r="R8" t="n">
-        <v>6624268</v>
+        <v>6624123</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>På tall-låga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1548,10 +1548,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119713553</v>
+        <v>119713775</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1560,25 +1560,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1588,26 +1588,21 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fanfluken, Vstm</t>
+          <t>Fanfluken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558372</v>
+        <v>558433</v>
       </c>
       <c r="R9" t="n">
-        <v>6624267</v>
+        <v>6624268</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1650,6 +1645,11 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -1292,10 +1292,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119713553</v>
+        <v>119713808</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>8432</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,54 +1304,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fanfluken, Vstm</t>
+          <t>Fanfluken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558372</v>
+        <v>558363</v>
       </c>
       <c r="R7" t="n">
-        <v>6624267</v>
+        <v>6624123</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1394,6 +1387,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På tall-låga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,10 +1419,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119713808</v>
+        <v>119713775</v>
       </c>
       <c r="B8" t="n">
-        <v>8432</v>
+        <v>90527</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1437,32 +1435,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558363</v>
+        <v>558433</v>
       </c>
       <c r="R8" t="n">
-        <v>6624123</v>
+        <v>6624268</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På tall-låga</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1548,10 +1548,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119713775</v>
+        <v>119713553</v>
       </c>
       <c r="B9" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1560,25 +1560,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1588,21 +1588,26 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fanfluken, Sura sn, Vstm</t>
+          <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558433</v>
+        <v>558372</v>
       </c>
       <c r="R9" t="n">
-        <v>6624268</v>
+        <v>6624267</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1645,11 +1650,6 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119713516</v>
+        <v>119713808</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>8432</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,43 +917,36 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -961,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558369</v>
+        <v>558363</v>
       </c>
       <c r="R4" t="n">
-        <v>6624271</v>
+        <v>6624123</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1007,6 +1000,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På tall-låga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119713512</v>
+        <v>119713553</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,12 +1067,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1086,14 +1084,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fanfluken, Sura sn, Vstm</t>
+          <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558369</v>
+        <v>558372</v>
       </c>
       <c r="R5" t="n">
-        <v>6624269</v>
+        <v>6624267</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1163,10 +1161,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119713763</v>
+        <v>119713735</v>
       </c>
       <c r="B6" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1198,12 +1196,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1219,10 +1217,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558353</v>
+        <v>558369</v>
       </c>
       <c r="R6" t="n">
-        <v>6624271</v>
+        <v>6624275</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1265,6 +1263,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Enstaka överblommade plantor</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,10 +1295,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119713553</v>
+        <v>119713775</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>90545</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,25 +1307,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1332,26 +1335,21 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fanfluken, Vstm</t>
+          <t>Fanfluken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558372</v>
+        <v>558433</v>
       </c>
       <c r="R7" t="n">
-        <v>6624267</v>
+        <v>6624268</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1394,6 +1392,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,10 +1424,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119713808</v>
+        <v>119713512</v>
       </c>
       <c r="B8" t="n">
-        <v>8432</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,36 +1436,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1470,10 +1480,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558363</v>
+        <v>558369</v>
       </c>
       <c r="R8" t="n">
-        <v>6624123</v>
+        <v>6624269</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1516,11 +1526,6 @@
       <c r="AB8" t="inlineStr">
         <is>
           <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På tall-låga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1548,10 +1553,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119713775</v>
+        <v>119713527</v>
       </c>
       <c r="B9" t="n">
-        <v>90527</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1560,25 +1565,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1588,10 +1593,15 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1599,10 +1609,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558433</v>
+        <v>558367</v>
       </c>
       <c r="R9" t="n">
-        <v>6624268</v>
+        <v>6624274</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1645,11 +1655,6 @@
       <c r="AB9" t="inlineStr">
         <is>
           <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1677,10 +1682,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119713818</v>
+        <v>119713516</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1712,12 +1717,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1733,10 +1738,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558246</v>
+        <v>558369</v>
       </c>
       <c r="R10" t="n">
-        <v>6624165</v>
+        <v>6624271</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1806,10 +1811,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119713735</v>
+        <v>119713763</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1841,12 +1846,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1862,10 +1867,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558369</v>
+        <v>558353</v>
       </c>
       <c r="R11" t="n">
-        <v>6624275</v>
+        <v>6624271</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1908,11 +1913,6 @@
       <c r="AB11" t="inlineStr">
         <is>
           <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Enstaka överblommade plantor</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1940,10 +1940,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119713527</v>
+        <v>119713818</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1975,12 +1975,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558367</v>
+        <v>558246</v>
       </c>
       <c r="R12" t="n">
-        <v>6624274</v>
+        <v>6624165</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3551,6 +3551,851 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121394944</v>
+      </c>
+      <c r="B27" t="n">
+        <v>90662</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>558441</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6624265</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2022-11-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2022-11-12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121394943</v>
+      </c>
+      <c r="B28" t="n">
+        <v>95628</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>53</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>558390</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6624295</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-11-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-11-12</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121394549</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91999</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>558468</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6624096</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121394934</v>
+      </c>
+      <c r="B30" t="n">
+        <v>95628</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>53</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>558377</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6624106</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2022-11-12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2022-11-12</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>121394933</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8432</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>558377</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6624106</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2022-11-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2022-11-12</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>121394942</v>
+      </c>
+      <c r="B32" t="n">
+        <v>95944</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>990</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Liten hornflikmossa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lophozia ascendens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Warnst.) R.M.Schust.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>558390</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6624295</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2022-11-12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2022-11-12</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>121394932</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91089</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>558394</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6624091</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2022-11-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2022-11-12</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>121394945</v>
+      </c>
+      <c r="B34" t="n">
+        <v>95628</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>53</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>558441</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6624265</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2022-11-12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2022-11-12</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -2069,10 +2069,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121359469</v>
+        <v>121359466</v>
       </c>
       <c r="B13" t="n">
-        <v>90687</v>
+        <v>90662</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2081,25 +2081,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558491</v>
+        <v>558467</v>
       </c>
       <c r="R13" t="n">
         <v>6624274</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121359461</v>
+        <v>121359460</v>
       </c>
       <c r="B14" t="n">
-        <v>79216</v>
+        <v>8432</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2187,25 +2187,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2281,10 +2281,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121359462</v>
+        <v>121359458</v>
       </c>
       <c r="B15" t="n">
-        <v>90891</v>
+        <v>91999</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2293,25 +2293,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1106</v>
+        <v>5448</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558376</v>
+        <v>558350</v>
       </c>
       <c r="R15" t="n">
-        <v>6624261</v>
+        <v>6624211</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121359458</v>
+        <v>121359462</v>
       </c>
       <c r="B16" t="n">
-        <v>91989</v>
+        <v>90901</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2399,25 +2399,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5448</v>
+        <v>1106</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558350</v>
+        <v>558376</v>
       </c>
       <c r="R16" t="n">
-        <v>6624211</v>
+        <v>6624261</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121359460</v>
+        <v>121359459</v>
       </c>
       <c r="B17" t="n">
-        <v>8432</v>
+        <v>79219</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2505,25 +2505,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558352</v>
+        <v>558364</v>
       </c>
       <c r="R17" t="n">
-        <v>6624226</v>
+        <v>6624216</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121359444</v>
+        <v>121359471</v>
       </c>
       <c r="B18" t="n">
-        <v>91996</v>
+        <v>95628</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2611,41 +2611,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558433</v>
+        <v>558521</v>
       </c>
       <c r="R18" t="n">
-        <v>6624286</v>
+        <v>6624319</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2686,7 +2683,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2709,10 +2705,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121359465</v>
+        <v>121359506</v>
       </c>
       <c r="B19" t="n">
-        <v>91079</v>
+        <v>8432</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2721,20 +2717,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6040162</v>
+        <v>106545</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2744,10 +2745,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558460</v>
+        <v>558352</v>
       </c>
       <c r="R19" t="n">
-        <v>6624272</v>
+        <v>6624128</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2788,7 +2789,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2811,10 +2811,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121359457</v>
+        <v>121359443</v>
       </c>
       <c r="B20" t="n">
-        <v>91991</v>
+        <v>90711</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2827,21 +2827,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2851,10 +2851,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558395</v>
+        <v>558441</v>
       </c>
       <c r="R20" t="n">
-        <v>6624316</v>
+        <v>6624265</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2917,10 +2917,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121359466</v>
+        <v>121359461</v>
       </c>
       <c r="B21" t="n">
-        <v>90652</v>
+        <v>79219</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2929,25 +2929,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558467</v>
+        <v>558352</v>
       </c>
       <c r="R21" t="n">
-        <v>6624274</v>
+        <v>6624226</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3026,7 +3026,7 @@
         <v>121359467</v>
       </c>
       <c r="B22" t="n">
-        <v>90904</v>
+        <v>90914</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3129,10 +3129,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121359506</v>
+        <v>121359457</v>
       </c>
       <c r="B23" t="n">
-        <v>8432</v>
+        <v>92001</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3141,25 +3141,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>5449</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558352</v>
+        <v>558395</v>
       </c>
       <c r="R23" t="n">
-        <v>6624128</v>
+        <v>6624316</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121359471</v>
+        <v>121359444</v>
       </c>
       <c r="B24" t="n">
-        <v>95618</v>
+        <v>92006</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3247,38 +3247,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558521</v>
+        <v>558433</v>
       </c>
       <c r="R24" t="n">
-        <v>6624319</v>
+        <v>6624286</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3319,6 +3322,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3341,10 +3345,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121359443</v>
+        <v>121359465</v>
       </c>
       <c r="B25" t="n">
-        <v>90701</v>
+        <v>91089</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3357,21 +3361,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Gränsticka</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3381,10 +3380,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558441</v>
+        <v>558460</v>
       </c>
       <c r="R25" t="n">
-        <v>6624265</v>
+        <v>6624272</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3425,6 +3424,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3447,10 +3447,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121359459</v>
+        <v>121359469</v>
       </c>
       <c r="B26" t="n">
-        <v>79216</v>
+        <v>90697</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3463,21 +3463,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558364</v>
+        <v>558491</v>
       </c>
       <c r="R26" t="n">
-        <v>6624216</v>
+        <v>6624274</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121394944</v>
+        <v>121394932</v>
       </c>
       <c r="B27" t="n">
-        <v>90662</v>
+        <v>91089</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3565,25 +3565,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3593,10 +3588,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558441</v>
+        <v>558394</v>
       </c>
       <c r="R27" t="n">
-        <v>6624265</v>
+        <v>6624091</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3637,6 +3632,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3659,10 +3655,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121394943</v>
+        <v>121394549</v>
       </c>
       <c r="B28" t="n">
-        <v>95628</v>
+        <v>91999</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3675,21 +3671,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>5448</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3699,10 +3695,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558390</v>
+        <v>558468</v>
       </c>
       <c r="R28" t="n">
-        <v>6624295</v>
+        <v>6624096</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3729,12 +3725,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3765,10 +3761,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121394549</v>
+        <v>121394942</v>
       </c>
       <c r="B29" t="n">
-        <v>91999</v>
+        <v>95944</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3777,25 +3773,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5448</v>
+        <v>990</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3805,10 +3801,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558468</v>
+        <v>558390</v>
       </c>
       <c r="R29" t="n">
-        <v>6624096</v>
+        <v>6624295</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3835,12 +3831,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3849,6 +3845,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3871,7 +3868,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121394934</v>
+        <v>121394945</v>
       </c>
       <c r="B30" t="n">
         <v>95628</v>
@@ -3911,10 +3908,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558377</v>
+        <v>558441</v>
       </c>
       <c r="R30" t="n">
-        <v>6624106</v>
+        <v>6624265</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3977,10 +3974,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121394933</v>
+        <v>121394943</v>
       </c>
       <c r="B31" t="n">
-        <v>8432</v>
+        <v>95628</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3989,25 +3986,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4017,10 +4014,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558377</v>
+        <v>558390</v>
       </c>
       <c r="R31" t="n">
-        <v>6624106</v>
+        <v>6624295</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4083,10 +4080,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121394942</v>
+        <v>121394933</v>
       </c>
       <c r="B32" t="n">
-        <v>95944</v>
+        <v>8432</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4095,25 +4092,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>990</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4123,10 +4120,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558390</v>
+        <v>558377</v>
       </c>
       <c r="R32" t="n">
-        <v>6624295</v>
+        <v>6624106</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4167,7 +4164,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4190,10 +4186,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121394932</v>
+        <v>121394934</v>
       </c>
       <c r="B33" t="n">
-        <v>91089</v>
+        <v>95628</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4206,16 +4202,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6040162</v>
+        <v>53</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4225,10 +4226,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558394</v>
+        <v>558377</v>
       </c>
       <c r="R33" t="n">
-        <v>6624091</v>
+        <v>6624106</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4269,7 +4270,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4292,10 +4292,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121394945</v>
+        <v>121394944</v>
       </c>
       <c r="B34" t="n">
-        <v>95628</v>
+        <v>90662</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4304,25 +4304,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4396,6 +4396,4507 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>121394324</v>
+      </c>
+      <c r="B35" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>558478</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6624257</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>121394333</v>
+      </c>
+      <c r="B36" t="n">
+        <v>95628</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>53</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>558528</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6624316</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>121394352</v>
+      </c>
+      <c r="B37" t="n">
+        <v>5169</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>558363</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6624071</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>121394356</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91388</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>757</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hapalopilus aurantiacus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>558364</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6624122</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2022-11-12</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2022-11-12</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>121394322</v>
+      </c>
+      <c r="B39" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>558492</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6624223</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>121394342</v>
+      </c>
+      <c r="B40" t="n">
+        <v>74647</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>558435</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6624227</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>121394548</v>
+      </c>
+      <c r="B41" t="n">
+        <v>92001</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>558480</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6624122</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>121394309</v>
+      </c>
+      <c r="B42" t="n">
+        <v>95667</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>558437</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6624264</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>121394363</v>
+      </c>
+      <c r="B43" t="n">
+        <v>5169</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>558367</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6624219</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>121394303</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98081</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>558385</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6624276</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>121394344</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91985</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>558407</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6624166</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>121394306</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98081</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>558437</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6624213</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>121394350</v>
+      </c>
+      <c r="B47" t="n">
+        <v>94747</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>558402</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6624073</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>121394343</v>
+      </c>
+      <c r="B48" t="n">
+        <v>74647</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>558405</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6624226</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>121394321</v>
+      </c>
+      <c r="B49" t="n">
+        <v>95628</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>53</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>558450</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6624202</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2021-10-29</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2021-10-29</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>121394354</v>
+      </c>
+      <c r="B50" t="n">
+        <v>86285</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>558390</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6624037</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>121394270</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98081</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>558522</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6624290</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>121394353</v>
+      </c>
+      <c r="B52" t="n">
+        <v>4766</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>558363</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6624071</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>121394305</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98081</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>558420</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6624193</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>121394345</v>
+      </c>
+      <c r="B54" t="n">
+        <v>97029</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>558386</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6624222</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>121394348</v>
+      </c>
+      <c r="B55" t="n">
+        <v>92004</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1968</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Grantaggsvamp</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Phellodon violascens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>558437</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6624152</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>121394339</v>
+      </c>
+      <c r="B56" t="n">
+        <v>74647</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>558458</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6624309</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>121394272</v>
+      </c>
+      <c r="B57" t="n">
+        <v>58216</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>558519</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6624313</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>under ved i barrskog</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>121394323</v>
+      </c>
+      <c r="B58" t="n">
+        <v>5169</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>558492</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6624223</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>121394355</v>
+      </c>
+      <c r="B59" t="n">
+        <v>92170</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>558377</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6624159</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>undersida av grov ved mot mark # tall</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>121394357</v>
+      </c>
+      <c r="B60" t="n">
+        <v>95375</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>558396</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6624233</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>121394325</v>
+      </c>
+      <c r="B61" t="n">
+        <v>5169</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>558478</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6624257</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>121394326</v>
+      </c>
+      <c r="B62" t="n">
+        <v>4766</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>558478</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6624257</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>121394319</v>
+      </c>
+      <c r="B63" t="n">
+        <v>8432</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>558461</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6624164</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2021-10-29</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2021-10-29</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>121394494</v>
+      </c>
+      <c r="B64" t="n">
+        <v>89403</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>558369</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6624121</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2021-10-29</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2021-10-29</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>tallskog på finmorän</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>121394365</v>
+      </c>
+      <c r="B65" t="n">
+        <v>91089</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>558351</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6624213</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>121394310</v>
+      </c>
+      <c r="B66" t="n">
+        <v>95628</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>53</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>558437</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6624264</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>121394364</v>
+      </c>
+      <c r="B67" t="n">
+        <v>8432</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>558351</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6624213</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>121394304</v>
+      </c>
+      <c r="B68" t="n">
+        <v>98081</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>558372</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6624277</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>121394327</v>
+      </c>
+      <c r="B69" t="n">
+        <v>90711</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>558466</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6624295</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>121394351</v>
+      </c>
+      <c r="B70" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>558363</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6624071</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>121394314</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91089</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>558428</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6624048</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>121394315</v>
+      </c>
+      <c r="B72" t="n">
+        <v>91957</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6055</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Spadskinn</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Stereopsis vitellina</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>558428</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6624044</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2021-10-29</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2021-10-29</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>121394313</v>
+      </c>
+      <c r="B73" t="n">
+        <v>91090</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>558412</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6624060</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>121394359</v>
+      </c>
+      <c r="B74" t="n">
+        <v>74647</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>558414</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6624238</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>121394320</v>
+      </c>
+      <c r="B75" t="n">
+        <v>89753</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>558465</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6624192</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2021-10-29</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2021-10-29</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>121394349</v>
+      </c>
+      <c r="B76" t="n">
+        <v>84292</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>3518</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Smal svampklubba</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Tolypocladium ophioglossoides</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>558419</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6624081</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -3553,10 +3553,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121394932</v>
+        <v>121394549</v>
       </c>
       <c r="B27" t="n">
-        <v>91089</v>
+        <v>91999</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3569,16 +3569,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6040162</v>
+        <v>5448</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3588,10 +3593,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558394</v>
+        <v>558468</v>
       </c>
       <c r="R27" t="n">
-        <v>6624091</v>
+        <v>6624096</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3618,12 +3623,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3632,7 +3637,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3655,10 +3659,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121394549</v>
+        <v>121394932</v>
       </c>
       <c r="B28" t="n">
-        <v>91999</v>
+        <v>91089</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3671,21 +3675,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5448</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Svartvit taggsvamp</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3695,10 +3694,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558468</v>
+        <v>558394</v>
       </c>
       <c r="R28" t="n">
-        <v>6624096</v>
+        <v>6624091</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3725,12 +3724,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3739,6 +3738,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -6314,10 +6314,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121394305</v>
+        <v>121394272</v>
       </c>
       <c r="B53" t="n">
-        <v>98081</v>
+        <v>58216</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6326,30 +6326,35 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>208242</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6358,10 +6363,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>558420</v>
+        <v>558519</v>
       </c>
       <c r="R53" t="n">
-        <v>6624193</v>
+        <v>6624313</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6394,6 +6399,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>under ved i barrskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6424,10 +6434,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121394345</v>
+        <v>121394305</v>
       </c>
       <c r="B54" t="n">
-        <v>97029</v>
+        <v>98081</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6436,34 +6446,42 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221944</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>558386</v>
+        <v>558420</v>
       </c>
       <c r="R54" t="n">
-        <v>6624222</v>
+        <v>6624193</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6490,12 +6508,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6504,7 +6522,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6527,10 +6544,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121394348</v>
+        <v>121394345</v>
       </c>
       <c r="B55" t="n">
-        <v>92004</v>
+        <v>97029</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6539,27 +6556,23 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1968</v>
+        <v>221944</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6567,10 +6580,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>558437</v>
+        <v>558386</v>
       </c>
       <c r="R55" t="n">
-        <v>6624152</v>
+        <v>6624222</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6611,6 +6624,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6633,10 +6647,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121394339</v>
+        <v>121394348</v>
       </c>
       <c r="B56" t="n">
-        <v>74647</v>
+        <v>92004</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6645,25 +6659,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6426</v>
+        <v>1968</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6673,10 +6687,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>558458</v>
+        <v>558437</v>
       </c>
       <c r="R56" t="n">
-        <v>6624309</v>
+        <v>6624152</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6739,10 +6753,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121394272</v>
+        <v>121394339</v>
       </c>
       <c r="B57" t="n">
-        <v>58216</v>
+        <v>74647</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6755,43 +6769,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>208242</v>
+        <v>6426</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>558519</v>
+        <v>558458</v>
       </c>
       <c r="R57" t="n">
-        <v>6624313</v>
+        <v>6624309</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6818,17 +6823,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>under ved i barrskog</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -2175,10 +2175,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121359460</v>
+        <v>121359444</v>
       </c>
       <c r="B14" t="n">
-        <v>8432</v>
+        <v>92006</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2191,34 +2191,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558352</v>
+        <v>558433</v>
       </c>
       <c r="R14" t="n">
-        <v>6624226</v>
+        <v>6624286</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2259,6 +2262,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2281,10 +2285,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121359458</v>
+        <v>121359457</v>
       </c>
       <c r="B15" t="n">
-        <v>91999</v>
+        <v>92001</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2297,21 +2301,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5448</v>
+        <v>5449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2321,10 +2325,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558350</v>
+        <v>558395</v>
       </c>
       <c r="R15" t="n">
-        <v>6624211</v>
+        <v>6624316</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2387,10 +2391,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121359462</v>
+        <v>121359458</v>
       </c>
       <c r="B16" t="n">
-        <v>90901</v>
+        <v>91999</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2399,25 +2403,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1106</v>
+        <v>5448</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2427,10 +2431,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558376</v>
+        <v>558350</v>
       </c>
       <c r="R16" t="n">
-        <v>6624261</v>
+        <v>6624211</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2493,7 +2497,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121359459</v>
+        <v>121359461</v>
       </c>
       <c r="B17" t="n">
         <v>79219</v>
@@ -2533,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558364</v>
+        <v>558352</v>
       </c>
       <c r="R17" t="n">
-        <v>6624216</v>
+        <v>6624226</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2599,10 +2603,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121359471</v>
+        <v>121359462</v>
       </c>
       <c r="B18" t="n">
-        <v>95628</v>
+        <v>90901</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2611,25 +2615,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>1106</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2639,10 +2643,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558521</v>
+        <v>558376</v>
       </c>
       <c r="R18" t="n">
-        <v>6624319</v>
+        <v>6624261</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2705,7 +2709,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121359506</v>
+        <v>121359460</v>
       </c>
       <c r="B19" t="n">
         <v>8432</v>
@@ -2748,7 +2752,7 @@
         <v>558352</v>
       </c>
       <c r="R19" t="n">
-        <v>6624128</v>
+        <v>6624226</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2811,10 +2815,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121359443</v>
+        <v>121359506</v>
       </c>
       <c r="B20" t="n">
-        <v>90711</v>
+        <v>8432</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2823,25 +2827,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2851,10 +2855,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558441</v>
+        <v>558352</v>
       </c>
       <c r="R20" t="n">
-        <v>6624265</v>
+        <v>6624128</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2917,10 +2921,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121359461</v>
+        <v>121359465</v>
       </c>
       <c r="B21" t="n">
-        <v>79219</v>
+        <v>91089</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2933,21 +2937,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2957,10 +2956,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558352</v>
+        <v>558460</v>
       </c>
       <c r="R21" t="n">
-        <v>6624226</v>
+        <v>6624272</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3001,6 +3000,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121359467</v>
+        <v>121359469</v>
       </c>
       <c r="B22" t="n">
-        <v>90914</v>
+        <v>90697</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3039,21 +3039,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1101</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558464</v>
+        <v>558491</v>
       </c>
       <c r="R22" t="n">
-        <v>6624306</v>
+        <v>6624274</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3129,10 +3129,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121359457</v>
+        <v>121359459</v>
       </c>
       <c r="B23" t="n">
-        <v>92001</v>
+        <v>79219</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3145,21 +3145,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558395</v>
+        <v>558364</v>
       </c>
       <c r="R23" t="n">
-        <v>6624316</v>
+        <v>6624216</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121359444</v>
+        <v>121359467</v>
       </c>
       <c r="B24" t="n">
-        <v>92006</v>
+        <v>90914</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3247,41 +3247,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>1101</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558433</v>
+        <v>558464</v>
       </c>
       <c r="R24" t="n">
-        <v>6624286</v>
+        <v>6624306</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3322,7 +3319,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3345,10 +3341,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121359465</v>
+        <v>121359443</v>
       </c>
       <c r="B25" t="n">
-        <v>91089</v>
+        <v>90711</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3361,16 +3357,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6040162</v>
+        <v>1204</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3380,10 +3381,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558460</v>
+        <v>558441</v>
       </c>
       <c r="R25" t="n">
-        <v>6624272</v>
+        <v>6624265</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3424,7 +3425,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3447,10 +3447,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121359469</v>
+        <v>121359471</v>
       </c>
       <c r="B26" t="n">
-        <v>90697</v>
+        <v>95628</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3463,21 +3463,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558491</v>
+        <v>558521</v>
       </c>
       <c r="R26" t="n">
-        <v>6624274</v>
+        <v>6624319</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121394549</v>
+        <v>121394945</v>
       </c>
       <c r="B27" t="n">
-        <v>91999</v>
+        <v>95628</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3569,21 +3569,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5448</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558468</v>
+        <v>558441</v>
       </c>
       <c r="R27" t="n">
-        <v>6624096</v>
+        <v>6624265</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3623,12 +3623,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3868,7 +3868,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121394945</v>
+        <v>121394934</v>
       </c>
       <c r="B30" t="n">
         <v>95628</v>
@@ -3908,10 +3908,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558441</v>
+        <v>558377</v>
       </c>
       <c r="R30" t="n">
-        <v>6624265</v>
+        <v>6624106</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3974,10 +3974,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121394943</v>
+        <v>121394933</v>
       </c>
       <c r="B31" t="n">
-        <v>95628</v>
+        <v>8432</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3986,25 +3986,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4014,10 +4014,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558390</v>
+        <v>558377</v>
       </c>
       <c r="R31" t="n">
-        <v>6624295</v>
+        <v>6624106</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4080,10 +4080,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121394933</v>
+        <v>121394549</v>
       </c>
       <c r="B32" t="n">
-        <v>8432</v>
+        <v>91999</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4092,25 +4092,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>5448</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558377</v>
+        <v>558468</v>
       </c>
       <c r="R32" t="n">
-        <v>6624106</v>
+        <v>6624096</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4186,10 +4186,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121394934</v>
+        <v>121394944</v>
       </c>
       <c r="B33" t="n">
-        <v>95628</v>
+        <v>90662</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4198,25 +4198,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558377</v>
+        <v>558441</v>
       </c>
       <c r="R33" t="n">
-        <v>6624106</v>
+        <v>6624265</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4292,10 +4292,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121394944</v>
+        <v>121394943</v>
       </c>
       <c r="B34" t="n">
-        <v>90662</v>
+        <v>95628</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4304,25 +4304,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4332,10 +4332,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558441</v>
+        <v>558390</v>
       </c>
       <c r="R34" t="n">
-        <v>6624265</v>
+        <v>6624295</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4398,10 +4398,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121394324</v>
+        <v>121394348</v>
       </c>
       <c r="B35" t="n">
-        <v>5189</v>
+        <v>92004</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4410,25 +4410,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>105930</v>
+        <v>1968</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4438,10 +4438,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558478</v>
+        <v>558437</v>
       </c>
       <c r="R35" t="n">
-        <v>6624257</v>
+        <v>6624152</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4504,10 +4504,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121394333</v>
+        <v>121394272</v>
       </c>
       <c r="B36" t="n">
-        <v>95628</v>
+        <v>58216</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4516,38 +4516,47 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>208242</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558528</v>
+        <v>558519</v>
       </c>
       <c r="R36" t="n">
-        <v>6624316</v>
+        <v>6624313</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4574,12 +4583,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>under ved i barrskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4610,10 +4624,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121394352</v>
+        <v>121394324</v>
       </c>
       <c r="B37" t="n">
-        <v>5169</v>
+        <v>5189</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4626,21 +4640,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4650,10 +4664,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558363</v>
+        <v>558478</v>
       </c>
       <c r="R37" t="n">
-        <v>6624071</v>
+        <v>6624257</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4716,10 +4730,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121394356</v>
+        <v>121394344</v>
       </c>
       <c r="B38" t="n">
-        <v>91388</v>
+        <v>91985</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4728,20 +4742,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>757</v>
+        <v>4366</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4751,10 +4770,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558364</v>
+        <v>558407</v>
       </c>
       <c r="R38" t="n">
-        <v>6624122</v>
+        <v>6624166</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4781,12 +4800,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4795,7 +4814,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4818,10 +4836,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121394322</v>
+        <v>121394321</v>
       </c>
       <c r="B39" t="n">
-        <v>5189</v>
+        <v>95628</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4830,25 +4848,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4858,10 +4876,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558492</v>
+        <v>558450</v>
       </c>
       <c r="R39" t="n">
-        <v>6624223</v>
+        <v>6624202</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4888,12 +4906,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4924,7 +4942,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121394342</v>
+        <v>121394359</v>
       </c>
       <c r="B40" t="n">
         <v>74647</v>
@@ -4964,10 +4982,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558435</v>
+        <v>558414</v>
       </c>
       <c r="R40" t="n">
-        <v>6624227</v>
+        <v>6624238</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4994,12 +5012,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5030,10 +5048,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121394548</v>
+        <v>121394314</v>
       </c>
       <c r="B41" t="n">
-        <v>92001</v>
+        <v>91089</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5046,21 +5064,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5449</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5070,10 +5083,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558480</v>
+        <v>558428</v>
       </c>
       <c r="R41" t="n">
-        <v>6624122</v>
+        <v>6624048</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5100,12 +5113,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5114,6 +5132,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5136,10 +5155,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121394309</v>
+        <v>121394339</v>
       </c>
       <c r="B42" t="n">
-        <v>95667</v>
+        <v>74647</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5152,21 +5171,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5176,10 +5195,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558437</v>
+        <v>558458</v>
       </c>
       <c r="R42" t="n">
-        <v>6624264</v>
+        <v>6624309</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5206,12 +5225,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5348,10 +5367,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121394303</v>
+        <v>121394351</v>
       </c>
       <c r="B44" t="n">
-        <v>98081</v>
+        <v>5189</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5360,42 +5379,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558385</v>
+        <v>558363</v>
       </c>
       <c r="R44" t="n">
-        <v>6624276</v>
+        <v>6624071</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5422,12 +5437,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5458,10 +5473,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121394344</v>
+        <v>121394355</v>
       </c>
       <c r="B45" t="n">
-        <v>91985</v>
+        <v>92170</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5470,38 +5485,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4366</v>
+        <v>2079</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>558407</v>
+        <v>558377</v>
       </c>
       <c r="R45" t="n">
-        <v>6624166</v>
+        <v>6624159</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5528,12 +5546,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5542,8 +5560,24 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>undersida av grov ved mot mark # tall</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5564,10 +5598,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121394306</v>
+        <v>121394320</v>
       </c>
       <c r="B46" t="n">
-        <v>98081</v>
+        <v>89753</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5576,42 +5610,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558437</v>
+        <v>558465</v>
       </c>
       <c r="R46" t="n">
-        <v>6624213</v>
+        <v>6624192</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5638,12 +5668,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5674,10 +5704,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121394350</v>
+        <v>121394548</v>
       </c>
       <c r="B47" t="n">
-        <v>94747</v>
+        <v>92001</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5686,25 +5716,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2170</v>
+        <v>5449</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5714,10 +5744,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558402</v>
+        <v>558480</v>
       </c>
       <c r="R47" t="n">
-        <v>6624073</v>
+        <v>6624122</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5744,12 +5774,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5780,10 +5810,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121394343</v>
+        <v>121394333</v>
       </c>
       <c r="B48" t="n">
-        <v>74647</v>
+        <v>95628</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5792,25 +5822,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5820,10 +5850,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>558405</v>
+        <v>558528</v>
       </c>
       <c r="R48" t="n">
-        <v>6624226</v>
+        <v>6624316</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5886,10 +5916,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121394321</v>
+        <v>121394353</v>
       </c>
       <c r="B49" t="n">
-        <v>95628</v>
+        <v>4766</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5898,25 +5928,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5926,10 +5956,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558450</v>
+        <v>558363</v>
       </c>
       <c r="R49" t="n">
-        <v>6624202</v>
+        <v>6624071</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5956,12 +5986,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5992,10 +6022,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121394354</v>
+        <v>121394304</v>
       </c>
       <c r="B50" t="n">
-        <v>86285</v>
+        <v>98081</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6004,38 +6034,42 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3739</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>558390</v>
+        <v>558372</v>
       </c>
       <c r="R50" t="n">
-        <v>6624037</v>
+        <v>6624277</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6062,12 +6096,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6098,10 +6132,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121394270</v>
+        <v>121394322</v>
       </c>
       <c r="B51" t="n">
-        <v>98081</v>
+        <v>5189</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6110,42 +6144,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>558522</v>
+        <v>558492</v>
       </c>
       <c r="R51" t="n">
-        <v>6624290</v>
+        <v>6624223</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6172,12 +6202,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6208,10 +6238,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121394353</v>
+        <v>121394364</v>
       </c>
       <c r="B52" t="n">
-        <v>4766</v>
+        <v>8432</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6224,21 +6254,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100299</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6248,10 +6278,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>558363</v>
+        <v>558351</v>
       </c>
       <c r="R52" t="n">
-        <v>6624071</v>
+        <v>6624213</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6278,12 +6308,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6314,10 +6344,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121394272</v>
+        <v>121394270</v>
       </c>
       <c r="B53" t="n">
-        <v>58216</v>
+        <v>98081</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6326,35 +6356,30 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>208242</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6363,10 +6388,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>558519</v>
+        <v>558522</v>
       </c>
       <c r="R53" t="n">
-        <v>6624313</v>
+        <v>6624290</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6399,11 +6424,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>under ved i barrskog</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6434,10 +6454,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121394305</v>
+        <v>121394356</v>
       </c>
       <c r="B54" t="n">
-        <v>98081</v>
+        <v>91388</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6446,42 +6466,33 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>558420</v>
+        <v>558364</v>
       </c>
       <c r="R54" t="n">
-        <v>6624193</v>
+        <v>6624122</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6508,12 +6519,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6522,6 +6533,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6544,10 +6556,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121394345</v>
+        <v>121394313</v>
       </c>
       <c r="B55" t="n">
-        <v>97029</v>
+        <v>91090</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6556,23 +6568,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221944</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Lopplummer (aggregat)</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6580,10 +6591,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>558386</v>
+        <v>558412</v>
       </c>
       <c r="R55" t="n">
-        <v>6624222</v>
+        <v>6624060</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6616,6 +6627,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6647,10 +6663,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121394348</v>
+        <v>121394350</v>
       </c>
       <c r="B56" t="n">
-        <v>92004</v>
+        <v>94747</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6659,25 +6675,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1968</v>
+        <v>2170</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6687,10 +6703,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>558437</v>
+        <v>558402</v>
       </c>
       <c r="R56" t="n">
-        <v>6624152</v>
+        <v>6624073</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6753,10 +6769,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121394339</v>
+        <v>121394319</v>
       </c>
       <c r="B57" t="n">
-        <v>74647</v>
+        <v>8432</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6769,21 +6785,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6426</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6793,10 +6809,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>558458</v>
+        <v>558461</v>
       </c>
       <c r="R57" t="n">
-        <v>6624309</v>
+        <v>6624164</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6823,12 +6839,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6859,10 +6875,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121394323</v>
+        <v>121394326</v>
       </c>
       <c r="B58" t="n">
-        <v>5169</v>
+        <v>4766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6875,21 +6891,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6899,10 +6915,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>558492</v>
+        <v>558478</v>
       </c>
       <c r="R58" t="n">
-        <v>6624223</v>
+        <v>6624257</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6965,10 +6981,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121394355</v>
+        <v>121394352</v>
       </c>
       <c r="B59" t="n">
-        <v>92170</v>
+        <v>5169</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6977,41 +6993,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2079</v>
+        <v>100526</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>558377</v>
+        <v>558363</v>
       </c>
       <c r="R59" t="n">
-        <v>6624159</v>
+        <v>6624071</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7038,12 +7051,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7052,24 +7065,8 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AL59" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>undersida av grov ved mot mark # tall</t>
-        </is>
-      </c>
-      <c r="AQ59" t="inlineStr">
-        <is>
-          <t>Ralf Lundmark</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7090,10 +7087,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121394357</v>
+        <v>121394306</v>
       </c>
       <c r="B60" t="n">
-        <v>95375</v>
+        <v>98081</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7102,38 +7099,42 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>558396</v>
+        <v>558437</v>
       </c>
       <c r="R60" t="n">
-        <v>6624233</v>
+        <v>6624213</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7160,12 +7161,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7196,10 +7197,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121394325</v>
+        <v>121394342</v>
       </c>
       <c r="B61" t="n">
-        <v>5169</v>
+        <v>74647</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7212,21 +7213,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7236,10 +7237,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>558478</v>
+        <v>558435</v>
       </c>
       <c r="R61" t="n">
-        <v>6624257</v>
+        <v>6624227</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7302,10 +7303,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121394326</v>
+        <v>121394357</v>
       </c>
       <c r="B62" t="n">
-        <v>4766</v>
+        <v>95375</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7318,21 +7319,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100299</v>
+        <v>2869</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7342,10 +7343,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>558478</v>
+        <v>558396</v>
       </c>
       <c r="R62" t="n">
-        <v>6624257</v>
+        <v>6624233</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7372,12 +7373,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7408,10 +7409,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121394319</v>
+        <v>121394349</v>
       </c>
       <c r="B63" t="n">
-        <v>8432</v>
+        <v>84292</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7424,21 +7425,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>3518</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7448,10 +7449,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>558461</v>
+        <v>558419</v>
       </c>
       <c r="R63" t="n">
-        <v>6624164</v>
+        <v>6624081</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7478,12 +7479,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7514,10 +7515,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121394494</v>
+        <v>121394354</v>
       </c>
       <c r="B64" t="n">
-        <v>89403</v>
+        <v>86285</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7526,25 +7527,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6286</v>
+        <v>3739</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7554,10 +7555,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>558369</v>
+        <v>558390</v>
       </c>
       <c r="R64" t="n">
-        <v>6624121</v>
+        <v>6624037</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7584,12 +7585,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7600,11 +7601,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>tallskog på finmorän</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7625,10 +7621,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121394365</v>
+        <v>121394343</v>
       </c>
       <c r="B65" t="n">
-        <v>91089</v>
+        <v>74647</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7637,20 +7633,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6040162</v>
+        <v>6426</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7660,10 +7661,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>558351</v>
+        <v>558405</v>
       </c>
       <c r="R65" t="n">
-        <v>6624213</v>
+        <v>6624226</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7690,12 +7691,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7704,7 +7705,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7727,10 +7727,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121394310</v>
+        <v>121394494</v>
       </c>
       <c r="B66" t="n">
-        <v>95628</v>
+        <v>89403</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7739,25 +7739,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>53</v>
+        <v>6286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7767,10 +7767,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>558437</v>
+        <v>558369</v>
       </c>
       <c r="R66" t="n">
-        <v>6624264</v>
+        <v>6624121</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7797,12 +7797,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7813,6 +7813,11 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>tallskog på finmorän</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -7833,10 +7838,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121394364</v>
+        <v>121394310</v>
       </c>
       <c r="B67" t="n">
-        <v>8432</v>
+        <v>95628</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7845,25 +7850,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7873,10 +7878,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>558351</v>
+        <v>558437</v>
       </c>
       <c r="R67" t="n">
-        <v>6624213</v>
+        <v>6624264</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7903,12 +7908,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7939,7 +7944,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121394304</v>
+        <v>121394303</v>
       </c>
       <c r="B68" t="n">
         <v>98081</v>
@@ -7974,7 +7979,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7983,10 +7988,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>558372</v>
+        <v>558385</v>
       </c>
       <c r="R68" t="n">
-        <v>6624277</v>
+        <v>6624276</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8049,10 +8054,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121394327</v>
+        <v>121394323</v>
       </c>
       <c r="B69" t="n">
-        <v>90711</v>
+        <v>5169</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8061,25 +8066,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1204</v>
+        <v>100526</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8089,10 +8094,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>558466</v>
+        <v>558492</v>
       </c>
       <c r="R69" t="n">
-        <v>6624295</v>
+        <v>6624223</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8155,10 +8160,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121394351</v>
+        <v>121394345</v>
       </c>
       <c r="B70" t="n">
-        <v>5189</v>
+        <v>97029</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8171,23 +8176,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>105930</v>
+        <v>221944</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8195,10 +8196,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>558363</v>
+        <v>558386</v>
       </c>
       <c r="R70" t="n">
-        <v>6624071</v>
+        <v>6624222</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8239,6 +8240,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8261,10 +8263,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121394314</v>
+        <v>121394327</v>
       </c>
       <c r="B71" t="n">
-        <v>91089</v>
+        <v>90711</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8277,16 +8279,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6040162</v>
+        <v>1204</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8296,10 +8303,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>558428</v>
+        <v>558466</v>
       </c>
       <c r="R71" t="n">
-        <v>6624048</v>
+        <v>6624295</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8334,18 +8341,12 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8368,10 +8369,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121394315</v>
+        <v>121394365</v>
       </c>
       <c r="B72" t="n">
-        <v>91957</v>
+        <v>91089</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8380,25 +8381,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6055</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Spadskinn</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8408,10 +8404,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>558428</v>
+        <v>558351</v>
       </c>
       <c r="R72" t="n">
-        <v>6624044</v>
+        <v>6624213</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8438,12 +8434,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8452,6 +8448,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8474,10 +8471,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121394313</v>
+        <v>121394325</v>
       </c>
       <c r="B73" t="n">
-        <v>91090</v>
+        <v>5169</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8486,20 +8483,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6040186</v>
+        <v>100526</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8509,10 +8511,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>558412</v>
+        <v>558478</v>
       </c>
       <c r="R73" t="n">
-        <v>6624060</v>
+        <v>6624257</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8547,18 +8549,12 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8581,10 +8577,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121394359</v>
+        <v>121394309</v>
       </c>
       <c r="B74" t="n">
-        <v>74647</v>
+        <v>95667</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8597,21 +8593,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8621,10 +8617,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>558414</v>
+        <v>558437</v>
       </c>
       <c r="R74" t="n">
-        <v>6624238</v>
+        <v>6624264</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8651,12 +8647,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8687,10 +8683,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121394320</v>
+        <v>121394305</v>
       </c>
       <c r="B75" t="n">
-        <v>89753</v>
+        <v>98081</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8699,38 +8695,42 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>558465</v>
+        <v>558420</v>
       </c>
       <c r="R75" t="n">
-        <v>6624192</v>
+        <v>6624193</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8757,12 +8757,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8793,10 +8793,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121394349</v>
+        <v>121394315</v>
       </c>
       <c r="B76" t="n">
-        <v>84292</v>
+        <v>91957</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8805,25 +8805,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3518</v>
+        <v>6055</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8833,10 +8833,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>558419</v>
+        <v>558428</v>
       </c>
       <c r="R76" t="n">
-        <v>6624081</v>
+        <v>6624044</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD76" t="b">

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -5261,10 +5261,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121394363</v>
+        <v>121394548</v>
       </c>
       <c r="B43" t="n">
-        <v>5169</v>
+        <v>92001</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5273,25 +5273,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100526</v>
+        <v>5449</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558367</v>
+        <v>558480</v>
       </c>
       <c r="R43" t="n">
-        <v>6624219</v>
+        <v>6624122</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5331,12 +5331,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5367,10 +5367,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121394351</v>
+        <v>121394363</v>
       </c>
       <c r="B44" t="n">
-        <v>5189</v>
+        <v>5169</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5383,21 +5383,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5407,10 +5407,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558363</v>
+        <v>558367</v>
       </c>
       <c r="R44" t="n">
-        <v>6624071</v>
+        <v>6624219</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5437,12 +5437,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5704,10 +5704,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121394548</v>
+        <v>121394351</v>
       </c>
       <c r="B47" t="n">
-        <v>92001</v>
+        <v>5189</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5716,25 +5716,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5449</v>
+        <v>105930</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5744,10 +5744,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558480</v>
+        <v>558363</v>
       </c>
       <c r="R47" t="n">
-        <v>6624122</v>
+        <v>6624071</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5774,12 +5774,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6022,10 +6022,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121394304</v>
+        <v>121394322</v>
       </c>
       <c r="B50" t="n">
-        <v>98081</v>
+        <v>5189</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6034,42 +6034,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>558372</v>
+        <v>558492</v>
       </c>
       <c r="R50" t="n">
-        <v>6624277</v>
+        <v>6624223</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6096,12 +6092,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6132,10 +6128,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121394322</v>
+        <v>121394304</v>
       </c>
       <c r="B51" t="n">
-        <v>5189</v>
+        <v>98081</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6144,38 +6140,42 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>558492</v>
+        <v>558372</v>
       </c>
       <c r="R51" t="n">
-        <v>6624223</v>
+        <v>6624277</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6202,12 +6202,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6238,10 +6238,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121394364</v>
+        <v>121394270</v>
       </c>
       <c r="B52" t="n">
-        <v>8432</v>
+        <v>98081</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6250,38 +6250,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>558351</v>
+        <v>558522</v>
       </c>
       <c r="R52" t="n">
-        <v>6624213</v>
+        <v>6624290</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6308,12 +6312,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6344,10 +6348,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121394270</v>
+        <v>121394364</v>
       </c>
       <c r="B53" t="n">
-        <v>98081</v>
+        <v>8432</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6356,42 +6360,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>558522</v>
+        <v>558351</v>
       </c>
       <c r="R53" t="n">
-        <v>6624290</v>
+        <v>6624213</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6418,12 +6418,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6981,10 +6981,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121394352</v>
+        <v>121394357</v>
       </c>
       <c r="B59" t="n">
-        <v>5169</v>
+        <v>95375</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6997,21 +6997,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100526</v>
+        <v>2869</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7021,10 +7021,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>558363</v>
+        <v>558396</v>
       </c>
       <c r="R59" t="n">
-        <v>6624071</v>
+        <v>6624233</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7051,12 +7051,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7087,10 +7087,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121394306</v>
+        <v>121394352</v>
       </c>
       <c r="B60" t="n">
-        <v>98081</v>
+        <v>5169</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7099,42 +7099,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>558437</v>
+        <v>558363</v>
       </c>
       <c r="R60" t="n">
-        <v>6624213</v>
+        <v>6624071</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7161,12 +7157,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7197,10 +7193,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121394342</v>
+        <v>121394306</v>
       </c>
       <c r="B61" t="n">
-        <v>74647</v>
+        <v>98081</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7209,38 +7205,42 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>558435</v>
+        <v>558437</v>
       </c>
       <c r="R61" t="n">
-        <v>6624227</v>
+        <v>6624213</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7267,12 +7267,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7303,10 +7303,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121394357</v>
+        <v>121394342</v>
       </c>
       <c r="B62" t="n">
-        <v>95375</v>
+        <v>74647</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7319,21 +7319,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2869</v>
+        <v>6426</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7343,10 +7343,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>558396</v>
+        <v>558435</v>
       </c>
       <c r="R62" t="n">
-        <v>6624233</v>
+        <v>6624227</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7409,10 +7409,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121394349</v>
+        <v>121394343</v>
       </c>
       <c r="B63" t="n">
-        <v>84292</v>
+        <v>74647</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7425,21 +7425,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3518</v>
+        <v>6426</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7449,10 +7449,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>558419</v>
+        <v>558405</v>
       </c>
       <c r="R63" t="n">
-        <v>6624081</v>
+        <v>6624226</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7515,10 +7515,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121394354</v>
+        <v>121394494</v>
       </c>
       <c r="B64" t="n">
-        <v>86285</v>
+        <v>89403</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7527,25 +7527,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3739</v>
+        <v>6286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7555,10 +7555,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>558390</v>
+        <v>558369</v>
       </c>
       <c r="R64" t="n">
-        <v>6624037</v>
+        <v>6624121</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7601,6 +7601,11 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>tallskog på finmorän</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7621,10 +7626,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121394343</v>
+        <v>121394349</v>
       </c>
       <c r="B65" t="n">
-        <v>74647</v>
+        <v>84292</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7637,21 +7642,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6426</v>
+        <v>3518</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7661,10 +7666,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>558405</v>
+        <v>558419</v>
       </c>
       <c r="R65" t="n">
-        <v>6624226</v>
+        <v>6624081</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7727,10 +7732,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121394494</v>
+        <v>121394354</v>
       </c>
       <c r="B66" t="n">
-        <v>89403</v>
+        <v>86285</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7739,25 +7744,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6286</v>
+        <v>3739</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7767,10 +7772,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>558369</v>
+        <v>558390</v>
       </c>
       <c r="R66" t="n">
-        <v>6624121</v>
+        <v>6624037</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7797,12 +7802,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7813,11 +7818,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>tallskog på finmorän</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8054,10 +8054,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121394323</v>
+        <v>121394365</v>
       </c>
       <c r="B69" t="n">
-        <v>5169</v>
+        <v>91089</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8066,25 +8066,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8094,10 +8089,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>558492</v>
+        <v>558351</v>
       </c>
       <c r="R69" t="n">
-        <v>6624223</v>
+        <v>6624213</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8124,12 +8119,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8138,6 +8133,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8160,10 +8156,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121394345</v>
+        <v>121394327</v>
       </c>
       <c r="B70" t="n">
-        <v>97029</v>
+        <v>90711</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8172,23 +8168,27 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221944</v>
+        <v>1204</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8196,10 +8196,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>558386</v>
+        <v>558466</v>
       </c>
       <c r="R70" t="n">
-        <v>6624222</v>
+        <v>6624295</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8240,7 +8240,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8263,10 +8262,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121394327</v>
+        <v>121394323</v>
       </c>
       <c r="B71" t="n">
-        <v>90711</v>
+        <v>5169</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8275,25 +8274,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1204</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8303,10 +8302,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>558466</v>
+        <v>558492</v>
       </c>
       <c r="R71" t="n">
-        <v>6624295</v>
+        <v>6624223</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8369,10 +8368,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121394365</v>
+        <v>121394345</v>
       </c>
       <c r="B72" t="n">
-        <v>91089</v>
+        <v>97029</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8381,22 +8380,23 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6040162</v>
+        <v>221944</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8404,10 +8404,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>558351</v>
+        <v>558386</v>
       </c>
       <c r="R72" t="n">
-        <v>6624213</v>
+        <v>6624222</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8434,12 +8434,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -2069,10 +2069,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121359466</v>
+        <v>121359443</v>
       </c>
       <c r="B13" t="n">
-        <v>90662</v>
+        <v>90723</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2081,25 +2081,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2109,10 +2109,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558467</v>
+        <v>558441</v>
       </c>
       <c r="R13" t="n">
-        <v>6624274</v>
+        <v>6624265</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121359444</v>
+        <v>121359506</v>
       </c>
       <c r="B14" t="n">
-        <v>92006</v>
+        <v>8432</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2191,37 +2191,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558433</v>
+        <v>558352</v>
       </c>
       <c r="R14" t="n">
-        <v>6624286</v>
+        <v>6624128</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2262,7 +2259,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2288,7 +2284,7 @@
         <v>121359457</v>
       </c>
       <c r="B15" t="n">
-        <v>92001</v>
+        <v>92013</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2391,10 +2387,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121359458</v>
+        <v>121359459</v>
       </c>
       <c r="B16" t="n">
-        <v>91999</v>
+        <v>79222</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2407,21 +2403,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5448</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2431,10 +2427,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558350</v>
+        <v>558364</v>
       </c>
       <c r="R16" t="n">
-        <v>6624211</v>
+        <v>6624216</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2500,7 +2496,7 @@
         <v>121359461</v>
       </c>
       <c r="B17" t="n">
-        <v>79219</v>
+        <v>79222</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2603,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121359462</v>
+        <v>121359460</v>
       </c>
       <c r="B18" t="n">
-        <v>90901</v>
+        <v>8432</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2615,25 +2611,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1106</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2643,10 +2639,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558376</v>
+        <v>558352</v>
       </c>
       <c r="R18" t="n">
-        <v>6624261</v>
+        <v>6624226</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2709,10 +2705,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121359460</v>
+        <v>121359469</v>
       </c>
       <c r="B19" t="n">
-        <v>8432</v>
+        <v>90709</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2721,25 +2717,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2749,10 +2745,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558352</v>
+        <v>558491</v>
       </c>
       <c r="R19" t="n">
-        <v>6624226</v>
+        <v>6624274</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2815,10 +2811,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121359506</v>
+        <v>121359467</v>
       </c>
       <c r="B20" t="n">
-        <v>8432</v>
+        <v>90926</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2827,25 +2823,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>1101</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2855,10 +2851,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558352</v>
+        <v>558464</v>
       </c>
       <c r="R20" t="n">
-        <v>6624128</v>
+        <v>6624306</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2921,10 +2917,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121359465</v>
+        <v>121359471</v>
       </c>
       <c r="B21" t="n">
-        <v>91089</v>
+        <v>95641</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2937,16 +2933,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6040162</v>
+        <v>53</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2956,10 +2957,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558460</v>
+        <v>558521</v>
       </c>
       <c r="R21" t="n">
-        <v>6624272</v>
+        <v>6624319</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3000,7 +3001,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121359469</v>
+        <v>121359466</v>
       </c>
       <c r="B22" t="n">
-        <v>90697</v>
+        <v>90674</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3035,25 +3035,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558491</v>
+        <v>558467</v>
       </c>
       <c r="R22" t="n">
         <v>6624274</v>
@@ -3129,10 +3129,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121359459</v>
+        <v>121359465</v>
       </c>
       <c r="B23" t="n">
-        <v>79219</v>
+        <v>91101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3145,21 +3145,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3169,10 +3164,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558364</v>
+        <v>558460</v>
       </c>
       <c r="R23" t="n">
-        <v>6624216</v>
+        <v>6624272</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3213,6 +3208,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3235,10 +3231,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121359467</v>
+        <v>121359458</v>
       </c>
       <c r="B24" t="n">
-        <v>90914</v>
+        <v>92011</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3251,21 +3247,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1101</v>
+        <v>5448</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3275,10 +3271,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558464</v>
+        <v>558350</v>
       </c>
       <c r="R24" t="n">
-        <v>6624306</v>
+        <v>6624211</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3341,10 +3337,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121359443</v>
+        <v>121359462</v>
       </c>
       <c r="B25" t="n">
-        <v>90711</v>
+        <v>90913</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3353,25 +3349,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>1106</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3381,10 +3377,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558441</v>
+        <v>558376</v>
       </c>
       <c r="R25" t="n">
-        <v>6624265</v>
+        <v>6624261</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3447,10 +3443,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121359471</v>
+        <v>121359444</v>
       </c>
       <c r="B26" t="n">
-        <v>95628</v>
+        <v>92018</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3459,38 +3455,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>5964</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558521</v>
+        <v>558433</v>
       </c>
       <c r="R26" t="n">
-        <v>6624319</v>
+        <v>6624286</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3531,6 +3530,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121394945</v>
+        <v>121394549</v>
       </c>
       <c r="B27" t="n">
-        <v>95628</v>
+        <v>92011</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3569,21 +3569,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>5448</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558441</v>
+        <v>558468</v>
       </c>
       <c r="R27" t="n">
-        <v>6624265</v>
+        <v>6624096</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3623,12 +3623,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3659,10 +3659,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121394932</v>
+        <v>121394934</v>
       </c>
       <c r="B28" t="n">
-        <v>91089</v>
+        <v>95641</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3675,16 +3675,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6040162</v>
+        <v>53</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3694,10 +3699,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558394</v>
+        <v>558377</v>
       </c>
       <c r="R28" t="n">
-        <v>6624091</v>
+        <v>6624106</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3738,7 +3743,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3761,10 +3765,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121394942</v>
+        <v>121394932</v>
       </c>
       <c r="B29" t="n">
-        <v>95944</v>
+        <v>91101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3773,25 +3777,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>990</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Liten hornflikmossa</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3801,10 +3800,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558390</v>
+        <v>558394</v>
       </c>
       <c r="R29" t="n">
-        <v>6624295</v>
+        <v>6624091</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3868,10 +3867,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121394934</v>
+        <v>121394933</v>
       </c>
       <c r="B30" t="n">
-        <v>95628</v>
+        <v>8432</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3880,25 +3879,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3974,10 +3973,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121394933</v>
+        <v>121394942</v>
       </c>
       <c r="B31" t="n">
-        <v>8432</v>
+        <v>95957</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3986,25 +3985,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>990</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4014,10 +4013,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558377</v>
+        <v>558390</v>
       </c>
       <c r="R31" t="n">
-        <v>6624106</v>
+        <v>6624295</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4058,6 +4057,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4080,10 +4080,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121394549</v>
+        <v>121394943</v>
       </c>
       <c r="B32" t="n">
-        <v>91999</v>
+        <v>95641</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4096,21 +4096,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5448</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558468</v>
+        <v>558390</v>
       </c>
       <c r="R32" t="n">
-        <v>6624096</v>
+        <v>6624295</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4189,7 +4189,7 @@
         <v>121394944</v>
       </c>
       <c r="B33" t="n">
-        <v>90662</v>
+        <v>90674</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4292,10 +4292,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121394943</v>
+        <v>121394945</v>
       </c>
       <c r="B34" t="n">
-        <v>95628</v>
+        <v>95641</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4332,10 +4332,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558390</v>
+        <v>558441</v>
       </c>
       <c r="R34" t="n">
-        <v>6624295</v>
+        <v>6624265</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4398,10 +4398,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121394348</v>
+        <v>121394322</v>
       </c>
       <c r="B35" t="n">
-        <v>92004</v>
+        <v>5189</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4410,25 +4410,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1968</v>
+        <v>105930</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4438,10 +4438,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558437</v>
+        <v>558492</v>
       </c>
       <c r="R35" t="n">
-        <v>6624152</v>
+        <v>6624223</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4504,10 +4504,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121394272</v>
+        <v>121394353</v>
       </c>
       <c r="B36" t="n">
-        <v>58216</v>
+        <v>4766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4520,43 +4520,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>208242</v>
+        <v>100299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558519</v>
+        <v>558363</v>
       </c>
       <c r="R36" t="n">
-        <v>6624313</v>
+        <v>6624071</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4583,17 +4574,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>under ved i barrskog</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4624,10 +4610,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121394324</v>
+        <v>121394321</v>
       </c>
       <c r="B37" t="n">
-        <v>5189</v>
+        <v>95641</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4636,25 +4622,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4664,10 +4650,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558478</v>
+        <v>558450</v>
       </c>
       <c r="R37" t="n">
-        <v>6624257</v>
+        <v>6624202</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4694,12 +4680,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4730,10 +4716,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121394344</v>
+        <v>121394345</v>
       </c>
       <c r="B38" t="n">
-        <v>91985</v>
+        <v>97042</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4746,23 +4732,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4366</v>
+        <v>221944</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Banker</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4770,10 +4752,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558407</v>
+        <v>558386</v>
       </c>
       <c r="R38" t="n">
-        <v>6624166</v>
+        <v>6624222</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4814,6 +4796,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4836,10 +4819,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121394321</v>
+        <v>121394305</v>
       </c>
       <c r="B39" t="n">
-        <v>95628</v>
+        <v>98094</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4848,38 +4831,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558450</v>
+        <v>558420</v>
       </c>
       <c r="R39" t="n">
-        <v>6624202</v>
+        <v>6624193</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4906,12 +4893,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4942,10 +4929,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121394359</v>
+        <v>121394352</v>
       </c>
       <c r="B40" t="n">
-        <v>74647</v>
+        <v>5169</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4958,21 +4945,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6426</v>
+        <v>100526</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4982,10 +4969,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558414</v>
+        <v>558363</v>
       </c>
       <c r="R40" t="n">
-        <v>6624238</v>
+        <v>6624071</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5012,12 +4999,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5048,10 +5035,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121394314</v>
+        <v>121394272</v>
       </c>
       <c r="B41" t="n">
-        <v>91089</v>
+        <v>58216</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5060,33 +5047,47 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6040162</v>
+        <v>208242</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558428</v>
+        <v>558519</v>
       </c>
       <c r="R41" t="n">
-        <v>6624048</v>
+        <v>6624313</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5113,17 +5114,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>under ved i barrskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5132,7 +5133,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5155,10 +5155,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121394339</v>
+        <v>121394342</v>
       </c>
       <c r="B42" t="n">
-        <v>74647</v>
+        <v>74649</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5195,10 +5195,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558458</v>
+        <v>558435</v>
       </c>
       <c r="R42" t="n">
-        <v>6624309</v>
+        <v>6624227</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5261,10 +5261,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121394548</v>
+        <v>121394349</v>
       </c>
       <c r="B43" t="n">
-        <v>92001</v>
+        <v>84297</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5273,25 +5273,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5449</v>
+        <v>3518</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558480</v>
+        <v>558419</v>
       </c>
       <c r="R43" t="n">
-        <v>6624122</v>
+        <v>6624081</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5331,12 +5331,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5367,10 +5367,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121394363</v>
+        <v>121394306</v>
       </c>
       <c r="B44" t="n">
-        <v>5169</v>
+        <v>98094</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5379,38 +5379,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558367</v>
+        <v>558437</v>
       </c>
       <c r="R44" t="n">
-        <v>6624219</v>
+        <v>6624213</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5437,12 +5441,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5473,10 +5477,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121394355</v>
+        <v>121394356</v>
       </c>
       <c r="B45" t="n">
-        <v>92170</v>
+        <v>91400</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5489,37 +5493,29 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2079</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Nordtagging</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>558377</v>
+        <v>558364</v>
       </c>
       <c r="R45" t="n">
-        <v>6624159</v>
+        <v>6624122</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5546,12 +5542,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5563,21 +5559,6 @@
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AL45" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>undersida av grov ved mot mark # tall</t>
-        </is>
-      </c>
-      <c r="AQ45" t="inlineStr">
-        <is>
-          <t>Ralf Lundmark</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5598,10 +5579,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121394320</v>
+        <v>121394348</v>
       </c>
       <c r="B46" t="n">
-        <v>89753</v>
+        <v>92016</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5614,21 +5595,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1962</v>
+        <v>1968</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5638,10 +5619,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558465</v>
+        <v>558437</v>
       </c>
       <c r="R46" t="n">
-        <v>6624192</v>
+        <v>6624152</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5668,12 +5649,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5704,10 +5685,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121394351</v>
+        <v>121394310</v>
       </c>
       <c r="B47" t="n">
-        <v>5189</v>
+        <v>95641</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5716,25 +5697,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5744,10 +5725,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558363</v>
+        <v>558437</v>
       </c>
       <c r="R47" t="n">
-        <v>6624071</v>
+        <v>6624264</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5774,12 +5755,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5813,7 +5794,7 @@
         <v>121394333</v>
       </c>
       <c r="B48" t="n">
-        <v>95628</v>
+        <v>95641</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5916,10 +5897,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121394353</v>
+        <v>121394309</v>
       </c>
       <c r="B49" t="n">
-        <v>4766</v>
+        <v>95680</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5932,21 +5913,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100299</v>
+        <v>2590</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5956,10 +5937,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558363</v>
+        <v>558437</v>
       </c>
       <c r="R49" t="n">
-        <v>6624071</v>
+        <v>6624264</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5986,12 +5967,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6022,10 +6003,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121394322</v>
+        <v>121394315</v>
       </c>
       <c r="B50" t="n">
-        <v>5189</v>
+        <v>91969</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6034,25 +6015,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>105930</v>
+        <v>6055</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6062,10 +6043,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>558492</v>
+        <v>558428</v>
       </c>
       <c r="R50" t="n">
-        <v>6624223</v>
+        <v>6624044</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6092,12 +6073,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6128,10 +6109,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121394304</v>
+        <v>121394548</v>
       </c>
       <c r="B51" t="n">
-        <v>98081</v>
+        <v>92013</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6140,42 +6121,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>558372</v>
+        <v>558480</v>
       </c>
       <c r="R51" t="n">
-        <v>6624277</v>
+        <v>6624122</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6202,12 +6179,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6238,10 +6215,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121394270</v>
+        <v>121394325</v>
       </c>
       <c r="B52" t="n">
-        <v>98081</v>
+        <v>5169</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6250,42 +6227,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>558522</v>
+        <v>558478</v>
       </c>
       <c r="R52" t="n">
-        <v>6624290</v>
+        <v>6624257</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6312,12 +6285,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6348,10 +6321,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121394364</v>
+        <v>121394323</v>
       </c>
       <c r="B53" t="n">
-        <v>8432</v>
+        <v>5169</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6364,21 +6337,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6388,10 +6361,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>558351</v>
+        <v>558492</v>
       </c>
       <c r="R53" t="n">
-        <v>6624213</v>
+        <v>6624223</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6418,12 +6391,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6454,10 +6427,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121394356</v>
+        <v>121394355</v>
       </c>
       <c r="B54" t="n">
-        <v>91388</v>
+        <v>92182</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6470,29 +6443,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>757</v>
+        <v>2079</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>558364</v>
+        <v>558377</v>
       </c>
       <c r="R54" t="n">
-        <v>6624122</v>
+        <v>6624159</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6519,12 +6500,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6536,6 +6517,21 @@
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>undersida av grov ved mot mark # tall</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6556,10 +6552,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121394313</v>
+        <v>121394319</v>
       </c>
       <c r="B55" t="n">
-        <v>91090</v>
+        <v>8432</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6568,20 +6564,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6040186</v>
+        <v>106545</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6591,10 +6592,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>558412</v>
+        <v>558461</v>
       </c>
       <c r="R55" t="n">
-        <v>6624060</v>
+        <v>6624164</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6621,17 +6622,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6640,7 +6636,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6663,10 +6658,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121394350</v>
+        <v>121394364</v>
       </c>
       <c r="B56" t="n">
-        <v>94747</v>
+        <v>8432</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6679,21 +6674,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2170</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6703,10 +6698,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>558402</v>
+        <v>558351</v>
       </c>
       <c r="R56" t="n">
-        <v>6624073</v>
+        <v>6624213</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6733,12 +6728,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6769,10 +6764,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121394319</v>
+        <v>121394494</v>
       </c>
       <c r="B57" t="n">
-        <v>8432</v>
+        <v>89410</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6781,25 +6776,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>106545</v>
+        <v>6286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6809,10 +6804,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>558461</v>
+        <v>558369</v>
       </c>
       <c r="R57" t="n">
-        <v>6624164</v>
+        <v>6624121</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6855,6 +6850,11 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>tallskog på finmorän</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -6981,10 +6981,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121394357</v>
+        <v>121394304</v>
       </c>
       <c r="B59" t="n">
-        <v>95375</v>
+        <v>98094</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6993,38 +6993,42 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>558396</v>
+        <v>558372</v>
       </c>
       <c r="R59" t="n">
-        <v>6624233</v>
+        <v>6624277</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7051,12 +7055,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7087,10 +7091,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121394352</v>
+        <v>121394343</v>
       </c>
       <c r="B60" t="n">
-        <v>5169</v>
+        <v>74649</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7103,21 +7107,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7127,10 +7131,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>558363</v>
+        <v>558405</v>
       </c>
       <c r="R60" t="n">
-        <v>6624071</v>
+        <v>6624226</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7193,10 +7197,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121394306</v>
+        <v>121394320</v>
       </c>
       <c r="B61" t="n">
-        <v>98081</v>
+        <v>89760</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7205,42 +7209,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>558437</v>
+        <v>558465</v>
       </c>
       <c r="R61" t="n">
-        <v>6624213</v>
+        <v>6624192</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7267,12 +7267,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7303,10 +7303,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121394342</v>
+        <v>121394313</v>
       </c>
       <c r="B62" t="n">
-        <v>74647</v>
+        <v>91102</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7315,25 +7315,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6426</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Kattfotslav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7343,10 +7338,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>558435</v>
+        <v>558412</v>
       </c>
       <c r="R62" t="n">
-        <v>6624227</v>
+        <v>6624060</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7381,12 +7376,18 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7409,10 +7410,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121394343</v>
+        <v>121394365</v>
       </c>
       <c r="B63" t="n">
-        <v>74647</v>
+        <v>91101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7421,25 +7422,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6426</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Kattfotslav</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7449,10 +7445,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>558405</v>
+        <v>558351</v>
       </c>
       <c r="R63" t="n">
-        <v>6624226</v>
+        <v>6624213</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7479,12 +7475,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7493,6 +7489,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7515,10 +7512,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121394494</v>
+        <v>121394363</v>
       </c>
       <c r="B64" t="n">
-        <v>89403</v>
+        <v>5169</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7527,25 +7524,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6286</v>
+        <v>100526</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7555,10 +7552,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>558369</v>
+        <v>558367</v>
       </c>
       <c r="R64" t="n">
-        <v>6624121</v>
+        <v>6624219</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7585,12 +7582,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7601,11 +7598,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>tallskog på finmorän</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7626,10 +7618,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121394349</v>
+        <v>121394351</v>
       </c>
       <c r="B65" t="n">
-        <v>84292</v>
+        <v>5189</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7642,21 +7634,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3518</v>
+        <v>105930</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7666,10 +7658,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>558419</v>
+        <v>558363</v>
       </c>
       <c r="R65" t="n">
-        <v>6624081</v>
+        <v>6624071</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7732,10 +7724,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121394354</v>
+        <v>121394270</v>
       </c>
       <c r="B66" t="n">
-        <v>86285</v>
+        <v>98094</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7744,38 +7736,42 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3739</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>558390</v>
+        <v>558522</v>
       </c>
       <c r="R66" t="n">
-        <v>6624037</v>
+        <v>6624290</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7802,12 +7798,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7838,10 +7834,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121394310</v>
+        <v>121394359</v>
       </c>
       <c r="B67" t="n">
-        <v>95628</v>
+        <v>74649</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7850,25 +7846,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7878,10 +7874,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>558437</v>
+        <v>558414</v>
       </c>
       <c r="R67" t="n">
-        <v>6624264</v>
+        <v>6624238</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7908,12 +7904,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7947,7 +7943,7 @@
         <v>121394303</v>
       </c>
       <c r="B68" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8054,10 +8050,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121394365</v>
+        <v>121394357</v>
       </c>
       <c r="B69" t="n">
-        <v>91089</v>
+        <v>95388</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8066,20 +8062,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6040162</v>
+        <v>2869</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8089,10 +8090,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>558351</v>
+        <v>558396</v>
       </c>
       <c r="R69" t="n">
-        <v>6624213</v>
+        <v>6624233</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8133,7 +8134,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8156,10 +8156,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121394327</v>
+        <v>121394350</v>
       </c>
       <c r="B70" t="n">
-        <v>90711</v>
+        <v>94759</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8168,25 +8168,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1204</v>
+        <v>2170</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8196,10 +8196,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>558466</v>
+        <v>558402</v>
       </c>
       <c r="R70" t="n">
-        <v>6624295</v>
+        <v>6624073</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8262,10 +8262,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121394323</v>
+        <v>121394324</v>
       </c>
       <c r="B71" t="n">
-        <v>5169</v>
+        <v>5189</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8278,21 +8278,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8302,10 +8302,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>558492</v>
+        <v>558478</v>
       </c>
       <c r="R71" t="n">
-        <v>6624223</v>
+        <v>6624257</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8368,10 +8368,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121394345</v>
+        <v>121394327</v>
       </c>
       <c r="B72" t="n">
-        <v>97029</v>
+        <v>90723</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8380,23 +8380,27 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221944</v>
+        <v>1204</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8404,10 +8408,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>558386</v>
+        <v>558466</v>
       </c>
       <c r="R72" t="n">
-        <v>6624222</v>
+        <v>6624295</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8448,7 +8452,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8471,10 +8474,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121394325</v>
+        <v>121394344</v>
       </c>
       <c r="B73" t="n">
-        <v>5169</v>
+        <v>91997</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8487,21 +8490,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100526</v>
+        <v>4366</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8511,10 +8514,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>558478</v>
+        <v>558407</v>
       </c>
       <c r="R73" t="n">
-        <v>6624257</v>
+        <v>6624166</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8577,10 +8580,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121394309</v>
+        <v>121394354</v>
       </c>
       <c r="B74" t="n">
-        <v>95667</v>
+        <v>86291</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8589,25 +8592,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2590</v>
+        <v>3739</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8617,10 +8620,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>558437</v>
+        <v>558390</v>
       </c>
       <c r="R74" t="n">
-        <v>6624264</v>
+        <v>6624037</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8647,12 +8650,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8683,10 +8686,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121394305</v>
+        <v>121394339</v>
       </c>
       <c r="B75" t="n">
-        <v>98081</v>
+        <v>74649</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8695,42 +8698,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>558420</v>
+        <v>558458</v>
       </c>
       <c r="R75" t="n">
-        <v>6624193</v>
+        <v>6624309</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8757,12 +8756,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8793,10 +8792,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121394315</v>
+        <v>121394314</v>
       </c>
       <c r="B76" t="n">
-        <v>91957</v>
+        <v>91101</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8805,25 +8804,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6055</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Spadskinn</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8836,7 +8830,7 @@
         <v>558428</v>
       </c>
       <c r="R76" t="n">
-        <v>6624044</v>
+        <v>6624048</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8863,12 +8857,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8877,6 +8876,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -2069,10 +2069,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121359443</v>
+        <v>121359469</v>
       </c>
       <c r="B13" t="n">
-        <v>90723</v>
+        <v>90710</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2085,21 +2085,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2109,10 +2109,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558441</v>
+        <v>558491</v>
       </c>
       <c r="R13" t="n">
-        <v>6624265</v>
+        <v>6624274</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121359506</v>
+        <v>121359462</v>
       </c>
       <c r="B14" t="n">
-        <v>8432</v>
+        <v>90914</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2187,25 +2187,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>1106</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558352</v>
+        <v>558376</v>
       </c>
       <c r="R14" t="n">
-        <v>6624128</v>
+        <v>6624261</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2281,10 +2281,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121359457</v>
+        <v>121359461</v>
       </c>
       <c r="B15" t="n">
-        <v>92013</v>
+        <v>79222</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2297,21 +2297,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558395</v>
+        <v>558352</v>
       </c>
       <c r="R15" t="n">
-        <v>6624316</v>
+        <v>6624226</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121359459</v>
+        <v>121359467</v>
       </c>
       <c r="B16" t="n">
-        <v>79222</v>
+        <v>90927</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2403,21 +2403,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>1101</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558364</v>
+        <v>558464</v>
       </c>
       <c r="R16" t="n">
-        <v>6624216</v>
+        <v>6624306</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121359461</v>
+        <v>121359506</v>
       </c>
       <c r="B17" t="n">
-        <v>79222</v>
+        <v>8432</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2505,25 +2505,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2536,7 +2536,7 @@
         <v>558352</v>
       </c>
       <c r="R17" t="n">
-        <v>6624226</v>
+        <v>6624128</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2705,10 +2705,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121359469</v>
+        <v>121359466</v>
       </c>
       <c r="B19" t="n">
-        <v>90709</v>
+        <v>90675</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2717,25 +2717,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2745,7 +2745,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558491</v>
+        <v>558467</v>
       </c>
       <c r="R19" t="n">
         <v>6624274</v>
@@ -2811,10 +2811,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121359467</v>
+        <v>121359458</v>
       </c>
       <c r="B20" t="n">
-        <v>90926</v>
+        <v>92012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2827,21 +2827,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1101</v>
+        <v>5448</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2851,10 +2851,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558464</v>
+        <v>558350</v>
       </c>
       <c r="R20" t="n">
-        <v>6624306</v>
+        <v>6624211</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2917,10 +2917,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121359471</v>
+        <v>121359465</v>
       </c>
       <c r="B21" t="n">
-        <v>95641</v>
+        <v>91102</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2933,21 +2933,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2957,10 +2952,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558521</v>
+        <v>558460</v>
       </c>
       <c r="R21" t="n">
-        <v>6624319</v>
+        <v>6624272</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3001,6 +2996,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3023,10 +3019,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121359466</v>
+        <v>121359457</v>
       </c>
       <c r="B22" t="n">
-        <v>90674</v>
+        <v>92014</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3035,25 +3031,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>5449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3063,10 +3059,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558467</v>
+        <v>558395</v>
       </c>
       <c r="R22" t="n">
-        <v>6624274</v>
+        <v>6624316</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3129,10 +3125,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121359465</v>
+        <v>121359443</v>
       </c>
       <c r="B23" t="n">
-        <v>91101</v>
+        <v>90724</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3145,16 +3141,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6040162</v>
+        <v>1204</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3164,10 +3165,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558460</v>
+        <v>558441</v>
       </c>
       <c r="R23" t="n">
-        <v>6624272</v>
+        <v>6624265</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3208,7 +3209,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3231,10 +3231,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121359458</v>
+        <v>121359444</v>
       </c>
       <c r="B24" t="n">
-        <v>92011</v>
+        <v>92019</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3243,38 +3243,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5448</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558350</v>
+        <v>558433</v>
       </c>
       <c r="R24" t="n">
-        <v>6624211</v>
+        <v>6624286</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3315,6 +3318,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3337,10 +3341,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121359462</v>
+        <v>121359471</v>
       </c>
       <c r="B25" t="n">
-        <v>90913</v>
+        <v>95642</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3349,25 +3353,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1106</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3377,10 +3381,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558376</v>
+        <v>558521</v>
       </c>
       <c r="R25" t="n">
-        <v>6624261</v>
+        <v>6624319</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3443,10 +3447,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121359444</v>
+        <v>121359459</v>
       </c>
       <c r="B26" t="n">
-        <v>92018</v>
+        <v>79222</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3455,41 +3459,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5964</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558433</v>
+        <v>558364</v>
       </c>
       <c r="R26" t="n">
-        <v>6624286</v>
+        <v>6624216</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3530,7 +3531,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121394549</v>
+        <v>121394942</v>
       </c>
       <c r="B27" t="n">
-        <v>92011</v>
+        <v>95958</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3565,25 +3565,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5448</v>
+        <v>990</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558468</v>
+        <v>558390</v>
       </c>
       <c r="R27" t="n">
-        <v>6624096</v>
+        <v>6624295</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3623,12 +3623,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3637,6 +3637,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3659,10 +3660,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121394934</v>
+        <v>121394932</v>
       </c>
       <c r="B28" t="n">
-        <v>95641</v>
+        <v>91102</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3675,21 +3676,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3699,10 +3695,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558377</v>
+        <v>558394</v>
       </c>
       <c r="R28" t="n">
-        <v>6624106</v>
+        <v>6624091</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3743,6 +3739,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3765,10 +3762,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121394932</v>
+        <v>121394943</v>
       </c>
       <c r="B29" t="n">
-        <v>91101</v>
+        <v>95642</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3781,16 +3778,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6040162</v>
+        <v>53</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3800,10 +3802,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558394</v>
+        <v>558390</v>
       </c>
       <c r="R29" t="n">
-        <v>6624091</v>
+        <v>6624295</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3844,7 +3846,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3867,10 +3868,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121394933</v>
+        <v>121394549</v>
       </c>
       <c r="B30" t="n">
-        <v>8432</v>
+        <v>92012</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3879,25 +3880,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>5448</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3907,10 +3908,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558377</v>
+        <v>558468</v>
       </c>
       <c r="R30" t="n">
-        <v>6624106</v>
+        <v>6624096</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3937,12 +3938,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3973,10 +3974,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121394942</v>
+        <v>121394944</v>
       </c>
       <c r="B31" t="n">
-        <v>95957</v>
+        <v>90675</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3985,25 +3986,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>990</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4013,10 +4014,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558390</v>
+        <v>558441</v>
       </c>
       <c r="R31" t="n">
-        <v>6624295</v>
+        <v>6624265</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4057,7 +4058,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4080,10 +4080,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121394943</v>
+        <v>121394933</v>
       </c>
       <c r="B32" t="n">
-        <v>95641</v>
+        <v>8432</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4092,25 +4092,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558390</v>
+        <v>558377</v>
       </c>
       <c r="R32" t="n">
-        <v>6624295</v>
+        <v>6624106</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4186,10 +4186,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121394944</v>
+        <v>121394945</v>
       </c>
       <c r="B33" t="n">
-        <v>90674</v>
+        <v>95642</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4198,25 +4198,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4292,10 +4292,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121394945</v>
+        <v>121394934</v>
       </c>
       <c r="B34" t="n">
-        <v>95641</v>
+        <v>95642</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4332,10 +4332,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558441</v>
+        <v>558377</v>
       </c>
       <c r="R34" t="n">
-        <v>6624265</v>
+        <v>6624106</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4398,10 +4398,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121394322</v>
+        <v>121394345</v>
       </c>
       <c r="B35" t="n">
-        <v>5189</v>
+        <v>97043</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4414,23 +4414,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>105930</v>
+        <v>221944</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4438,10 +4434,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558492</v>
+        <v>558386</v>
       </c>
       <c r="R35" t="n">
-        <v>6624223</v>
+        <v>6624222</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4482,6 +4478,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4504,10 +4501,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121394353</v>
+        <v>121394355</v>
       </c>
       <c r="B36" t="n">
-        <v>4766</v>
+        <v>92183</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4516,38 +4513,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100299</v>
+        <v>2079</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558363</v>
+        <v>558377</v>
       </c>
       <c r="R36" t="n">
-        <v>6624071</v>
+        <v>6624159</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4574,12 +4574,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4588,8 +4588,24 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>undersida av grov ved mot mark # tall</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4610,10 +4626,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121394321</v>
+        <v>121394343</v>
       </c>
       <c r="B37" t="n">
-        <v>95641</v>
+        <v>74649</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4622,25 +4638,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4650,10 +4666,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558450</v>
+        <v>558405</v>
       </c>
       <c r="R37" t="n">
-        <v>6624202</v>
+        <v>6624226</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4680,12 +4696,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4716,10 +4732,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121394345</v>
+        <v>121394304</v>
       </c>
       <c r="B38" t="n">
-        <v>97042</v>
+        <v>98095</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4728,34 +4744,42 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221944</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558386</v>
+        <v>558372</v>
       </c>
       <c r="R38" t="n">
-        <v>6624222</v>
+        <v>6624277</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4782,12 +4806,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4796,7 +4820,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4819,10 +4842,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121394305</v>
+        <v>121394320</v>
       </c>
       <c r="B39" t="n">
-        <v>98094</v>
+        <v>89761</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4831,42 +4854,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558420</v>
+        <v>558465</v>
       </c>
       <c r="R39" t="n">
-        <v>6624193</v>
+        <v>6624192</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4893,12 +4912,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4929,10 +4948,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121394352</v>
+        <v>121394319</v>
       </c>
       <c r="B40" t="n">
-        <v>5169</v>
+        <v>8432</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4945,21 +4964,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4969,10 +4988,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558363</v>
+        <v>558461</v>
       </c>
       <c r="R40" t="n">
-        <v>6624071</v>
+        <v>6624164</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4999,12 +5018,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5035,10 +5054,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121394272</v>
+        <v>121394333</v>
       </c>
       <c r="B41" t="n">
-        <v>58216</v>
+        <v>95642</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5047,47 +5066,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>208242</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558519</v>
+        <v>558528</v>
       </c>
       <c r="R41" t="n">
-        <v>6624313</v>
+        <v>6624316</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5114,17 +5124,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>under ved i barrskog</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5155,10 +5160,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121394342</v>
+        <v>121394353</v>
       </c>
       <c r="B42" t="n">
-        <v>74649</v>
+        <v>4766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5171,21 +5176,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6426</v>
+        <v>100299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5195,10 +5200,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558435</v>
+        <v>558363</v>
       </c>
       <c r="R42" t="n">
-        <v>6624227</v>
+        <v>6624071</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5261,10 +5266,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121394349</v>
+        <v>121394364</v>
       </c>
       <c r="B43" t="n">
-        <v>84297</v>
+        <v>8432</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5277,21 +5282,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3518</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5301,10 +5306,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558419</v>
+        <v>558351</v>
       </c>
       <c r="R43" t="n">
-        <v>6624081</v>
+        <v>6624213</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5331,12 +5336,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5367,10 +5372,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121394306</v>
+        <v>121394365</v>
       </c>
       <c r="B44" t="n">
-        <v>98094</v>
+        <v>91102</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5379,39 +5384,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558437</v>
+        <v>558351</v>
       </c>
       <c r="R44" t="n">
         <v>6624213</v>
@@ -5441,12 +5437,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5455,6 +5451,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5477,10 +5474,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121394356</v>
+        <v>121394321</v>
       </c>
       <c r="B45" t="n">
-        <v>91400</v>
+        <v>95642</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5493,16 +5490,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>757</v>
+        <v>53</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5512,10 +5514,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>558364</v>
+        <v>558450</v>
       </c>
       <c r="R45" t="n">
-        <v>6624122</v>
+        <v>6624202</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5542,12 +5544,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5556,7 +5558,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5579,10 +5580,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121394348</v>
+        <v>121394356</v>
       </c>
       <c r="B46" t="n">
-        <v>92016</v>
+        <v>91401</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5595,21 +5596,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1968</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Grantaggsvamp</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5619,10 +5615,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558437</v>
+        <v>558364</v>
       </c>
       <c r="R46" t="n">
-        <v>6624152</v>
+        <v>6624122</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5649,12 +5645,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5663,6 +5659,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5685,10 +5682,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121394310</v>
+        <v>121394322</v>
       </c>
       <c r="B47" t="n">
-        <v>95641</v>
+        <v>5189</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5697,25 +5694,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5725,10 +5722,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558437</v>
+        <v>558492</v>
       </c>
       <c r="R47" t="n">
-        <v>6624264</v>
+        <v>6624223</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5755,12 +5752,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5791,10 +5788,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121394333</v>
+        <v>121394305</v>
       </c>
       <c r="B48" t="n">
-        <v>95641</v>
+        <v>98095</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5803,38 +5800,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>558528</v>
+        <v>558420</v>
       </c>
       <c r="R48" t="n">
-        <v>6624316</v>
+        <v>6624193</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5861,12 +5862,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5897,10 +5898,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121394309</v>
+        <v>121394325</v>
       </c>
       <c r="B49" t="n">
-        <v>95680</v>
+        <v>5169</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5913,21 +5914,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2590</v>
+        <v>100526</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5937,10 +5938,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558437</v>
+        <v>558478</v>
       </c>
       <c r="R49" t="n">
-        <v>6624264</v>
+        <v>6624257</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5967,12 +5968,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6003,10 +6004,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121394315</v>
+        <v>121394326</v>
       </c>
       <c r="B50" t="n">
-        <v>91969</v>
+        <v>4766</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6015,25 +6016,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6055</v>
+        <v>100299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6043,10 +6044,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>558428</v>
+        <v>558478</v>
       </c>
       <c r="R50" t="n">
-        <v>6624044</v>
+        <v>6624257</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6073,12 +6074,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6109,10 +6110,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121394548</v>
+        <v>121394352</v>
       </c>
       <c r="B51" t="n">
-        <v>92013</v>
+        <v>5169</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6121,25 +6122,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5449</v>
+        <v>100526</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6149,10 +6150,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>558480</v>
+        <v>558363</v>
       </c>
       <c r="R51" t="n">
-        <v>6624122</v>
+        <v>6624071</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6179,12 +6180,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6215,10 +6216,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121394325</v>
+        <v>121394494</v>
       </c>
       <c r="B52" t="n">
-        <v>5169</v>
+        <v>89411</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6227,25 +6228,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100526</v>
+        <v>6286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6255,10 +6256,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>558478</v>
+        <v>558369</v>
       </c>
       <c r="R52" t="n">
-        <v>6624257</v>
+        <v>6624121</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6285,12 +6286,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6301,6 +6302,11 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>tallskog på finmorän</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6321,10 +6327,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121394323</v>
+        <v>121394349</v>
       </c>
       <c r="B53" t="n">
-        <v>5169</v>
+        <v>84297</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6337,21 +6343,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100526</v>
+        <v>3518</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6361,10 +6367,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>558492</v>
+        <v>558419</v>
       </c>
       <c r="R53" t="n">
-        <v>6624223</v>
+        <v>6624081</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6427,10 +6433,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121394355</v>
+        <v>121394344</v>
       </c>
       <c r="B54" t="n">
-        <v>92182</v>
+        <v>91998</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6439,41 +6445,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2079</v>
+        <v>4366</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>558377</v>
+        <v>558407</v>
       </c>
       <c r="R54" t="n">
-        <v>6624159</v>
+        <v>6624166</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6500,12 +6503,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6514,24 +6517,8 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AL54" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>undersida av grov ved mot mark # tall</t>
-        </is>
-      </c>
-      <c r="AQ54" t="inlineStr">
-        <is>
-          <t>Ralf Lundmark</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6552,10 +6539,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121394319</v>
+        <v>121394324</v>
       </c>
       <c r="B55" t="n">
-        <v>8432</v>
+        <v>5189</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6568,21 +6555,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6592,10 +6579,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>558461</v>
+        <v>558478</v>
       </c>
       <c r="R55" t="n">
-        <v>6624164</v>
+        <v>6624257</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6622,12 +6609,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6658,10 +6645,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121394364</v>
+        <v>121394327</v>
       </c>
       <c r="B56" t="n">
-        <v>8432</v>
+        <v>90724</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6670,25 +6657,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>1204</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6698,10 +6685,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>558351</v>
+        <v>558466</v>
       </c>
       <c r="R56" t="n">
-        <v>6624213</v>
+        <v>6624295</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6728,12 +6715,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6764,10 +6751,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121394494</v>
+        <v>121394354</v>
       </c>
       <c r="B57" t="n">
-        <v>89410</v>
+        <v>86291</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6776,25 +6763,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6286</v>
+        <v>3739</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6804,10 +6791,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>558369</v>
+        <v>558390</v>
       </c>
       <c r="R57" t="n">
-        <v>6624121</v>
+        <v>6624037</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6834,12 +6821,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6850,11 +6837,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>tallskog på finmorän</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -6875,10 +6857,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121394326</v>
+        <v>121394357</v>
       </c>
       <c r="B58" t="n">
-        <v>4766</v>
+        <v>95389</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6891,21 +6873,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100299</v>
+        <v>2869</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6915,10 +6897,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>558478</v>
+        <v>558396</v>
       </c>
       <c r="R58" t="n">
-        <v>6624257</v>
+        <v>6624233</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6945,12 +6927,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6981,10 +6963,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121394304</v>
+        <v>121394272</v>
       </c>
       <c r="B59" t="n">
-        <v>98094</v>
+        <v>58216</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6993,30 +6975,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>208242</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7025,10 +7012,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>558372</v>
+        <v>558519</v>
       </c>
       <c r="R59" t="n">
-        <v>6624277</v>
+        <v>6624313</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7061,6 +7048,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>under ved i barrskog</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7091,10 +7083,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121394343</v>
+        <v>121394323</v>
       </c>
       <c r="B60" t="n">
-        <v>74649</v>
+        <v>5169</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7107,21 +7099,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6426</v>
+        <v>100526</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7131,10 +7123,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>558405</v>
+        <v>558492</v>
       </c>
       <c r="R60" t="n">
-        <v>6624226</v>
+        <v>6624223</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7197,10 +7189,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121394320</v>
+        <v>121394351</v>
       </c>
       <c r="B61" t="n">
-        <v>89760</v>
+        <v>5189</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7209,25 +7201,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1962</v>
+        <v>105930</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7237,10 +7229,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>558465</v>
+        <v>558363</v>
       </c>
       <c r="R61" t="n">
-        <v>6624192</v>
+        <v>6624071</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7267,12 +7259,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7303,7 +7295,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121394313</v>
+        <v>121394314</v>
       </c>
       <c r="B62" t="n">
         <v>91102</v>
@@ -7319,16 +7311,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6040186</v>
+        <v>6040162</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7338,10 +7330,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>558412</v>
+        <v>558428</v>
       </c>
       <c r="R62" t="n">
-        <v>6624060</v>
+        <v>6624048</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7378,7 +7370,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7410,10 +7402,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121394365</v>
+        <v>121394310</v>
       </c>
       <c r="B63" t="n">
-        <v>91101</v>
+        <v>95642</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7426,16 +7418,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6040162</v>
+        <v>53</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7445,10 +7442,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>558351</v>
+        <v>558437</v>
       </c>
       <c r="R63" t="n">
-        <v>6624213</v>
+        <v>6624264</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7475,12 +7472,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7489,7 +7486,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7512,10 +7508,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121394363</v>
+        <v>121394348</v>
       </c>
       <c r="B64" t="n">
-        <v>5169</v>
+        <v>92017</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7524,25 +7520,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100526</v>
+        <v>1968</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7552,10 +7548,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>558367</v>
+        <v>558437</v>
       </c>
       <c r="R64" t="n">
-        <v>6624219</v>
+        <v>6624152</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7582,12 +7578,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7618,10 +7614,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121394351</v>
+        <v>121394303</v>
       </c>
       <c r="B65" t="n">
-        <v>5189</v>
+        <v>98095</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7630,38 +7626,42 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>558363</v>
+        <v>558385</v>
       </c>
       <c r="R65" t="n">
-        <v>6624071</v>
+        <v>6624276</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7688,12 +7688,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7724,10 +7724,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121394270</v>
+        <v>121394339</v>
       </c>
       <c r="B66" t="n">
-        <v>98094</v>
+        <v>74649</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7736,42 +7736,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>558522</v>
+        <v>558458</v>
       </c>
       <c r="R66" t="n">
-        <v>6624290</v>
+        <v>6624309</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7798,12 +7794,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7834,10 +7830,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121394359</v>
+        <v>121394309</v>
       </c>
       <c r="B67" t="n">
-        <v>74649</v>
+        <v>95681</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7850,21 +7846,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6426</v>
+        <v>2590</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7874,10 +7870,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>558414</v>
+        <v>558437</v>
       </c>
       <c r="R67" t="n">
-        <v>6624238</v>
+        <v>6624264</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7904,12 +7900,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7940,10 +7936,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121394303</v>
+        <v>121394350</v>
       </c>
       <c r="B68" t="n">
-        <v>98094</v>
+        <v>94760</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7952,42 +7948,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>558385</v>
+        <v>558402</v>
       </c>
       <c r="R68" t="n">
-        <v>6624276</v>
+        <v>6624073</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8014,12 +8006,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8050,10 +8042,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121394357</v>
+        <v>121394306</v>
       </c>
       <c r="B69" t="n">
-        <v>95388</v>
+        <v>98095</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8062,38 +8054,42 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>558396</v>
+        <v>558437</v>
       </c>
       <c r="R69" t="n">
-        <v>6624233</v>
+        <v>6624213</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8120,12 +8116,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8156,10 +8152,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121394350</v>
+        <v>121394548</v>
       </c>
       <c r="B70" t="n">
-        <v>94759</v>
+        <v>92014</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8168,25 +8164,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2170</v>
+        <v>5449</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8196,10 +8192,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>558402</v>
+        <v>558480</v>
       </c>
       <c r="R70" t="n">
-        <v>6624073</v>
+        <v>6624122</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8226,12 +8222,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8262,10 +8258,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121394324</v>
+        <v>121394315</v>
       </c>
       <c r="B71" t="n">
-        <v>5189</v>
+        <v>91970</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8274,25 +8270,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>105930</v>
+        <v>6055</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8302,10 +8298,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>558478</v>
+        <v>558428</v>
       </c>
       <c r="R71" t="n">
-        <v>6624257</v>
+        <v>6624044</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8332,12 +8328,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8368,10 +8364,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121394327</v>
+        <v>121394313</v>
       </c>
       <c r="B72" t="n">
-        <v>90723</v>
+        <v>91103</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8384,21 +8380,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1204</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Gränsticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8408,10 +8399,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>558466</v>
+        <v>558412</v>
       </c>
       <c r="R72" t="n">
-        <v>6624295</v>
+        <v>6624060</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8446,12 +8437,18 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8474,10 +8471,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121394344</v>
+        <v>121394363</v>
       </c>
       <c r="B73" t="n">
-        <v>91997</v>
+        <v>5169</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8490,21 +8487,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4366</v>
+        <v>100526</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8514,10 +8511,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>558407</v>
+        <v>558367</v>
       </c>
       <c r="R73" t="n">
-        <v>6624166</v>
+        <v>6624219</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8544,12 +8541,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8580,10 +8577,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121394354</v>
+        <v>121394342</v>
       </c>
       <c r="B74" t="n">
-        <v>86291</v>
+        <v>74649</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8592,25 +8589,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3739</v>
+        <v>6426</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8620,10 +8617,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>558390</v>
+        <v>558435</v>
       </c>
       <c r="R74" t="n">
-        <v>6624037</v>
+        <v>6624227</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8686,7 +8683,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121394339</v>
+        <v>121394359</v>
       </c>
       <c r="B75" t="n">
         <v>74649</v>
@@ -8726,10 +8723,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>558458</v>
+        <v>558414</v>
       </c>
       <c r="R75" t="n">
-        <v>6624309</v>
+        <v>6624238</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8756,12 +8753,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8792,10 +8789,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121394314</v>
+        <v>121394270</v>
       </c>
       <c r="B76" t="n">
-        <v>91101</v>
+        <v>98095</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8804,33 +8801,42 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6040162</v>
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>558428</v>
+        <v>558522</v>
       </c>
       <c r="R76" t="n">
-        <v>6624048</v>
+        <v>6624290</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8857,17 +8863,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8876,7 +8877,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -2069,10 +2069,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121359469</v>
+        <v>121359506</v>
       </c>
       <c r="B13" t="n">
-        <v>90710</v>
+        <v>8435</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2081,25 +2081,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2109,10 +2109,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558491</v>
+        <v>558352</v>
       </c>
       <c r="R13" t="n">
-        <v>6624274</v>
+        <v>6624128</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121359462</v>
+        <v>121359465</v>
       </c>
       <c r="B14" t="n">
-        <v>90914</v>
+        <v>91105</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2187,25 +2187,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1106</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Vågticka</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2215,10 +2210,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558376</v>
+        <v>558460</v>
       </c>
       <c r="R14" t="n">
-        <v>6624261</v>
+        <v>6624272</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2259,6 +2254,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2281,10 +2277,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121359461</v>
+        <v>121359444</v>
       </c>
       <c r="B15" t="n">
-        <v>79222</v>
+        <v>92022</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2293,38 +2289,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558352</v>
+        <v>558433</v>
       </c>
       <c r="R15" t="n">
-        <v>6624226</v>
+        <v>6624286</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2365,6 +2364,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121359467</v>
+        <v>121359443</v>
       </c>
       <c r="B16" t="n">
-        <v>90927</v>
+        <v>90727</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2403,21 +2403,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1101</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558464</v>
+        <v>558441</v>
       </c>
       <c r="R16" t="n">
-        <v>6624306</v>
+        <v>6624265</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121359506</v>
+        <v>121359469</v>
       </c>
       <c r="B17" t="n">
-        <v>8432</v>
+        <v>90713</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2505,25 +2505,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558352</v>
+        <v>558491</v>
       </c>
       <c r="R17" t="n">
-        <v>6624128</v>
+        <v>6624274</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121359460</v>
+        <v>121359461</v>
       </c>
       <c r="B18" t="n">
-        <v>8432</v>
+        <v>79225</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2611,25 +2611,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2705,10 +2705,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121359466</v>
+        <v>121359462</v>
       </c>
       <c r="B19" t="n">
-        <v>90675</v>
+        <v>90917</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2717,25 +2717,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>1106</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558467</v>
+        <v>558376</v>
       </c>
       <c r="R19" t="n">
-        <v>6624274</v>
+        <v>6624261</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2811,10 +2811,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121359458</v>
+        <v>121359459</v>
       </c>
       <c r="B20" t="n">
-        <v>92012</v>
+        <v>79225</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2827,21 +2827,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5448</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2851,10 +2851,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558350</v>
+        <v>558364</v>
       </c>
       <c r="R20" t="n">
-        <v>6624211</v>
+        <v>6624216</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2917,10 +2917,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121359465</v>
+        <v>121359458</v>
       </c>
       <c r="B21" t="n">
-        <v>91102</v>
+        <v>92015</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2933,16 +2933,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6040162</v>
+        <v>5448</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2952,10 +2957,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558460</v>
+        <v>558350</v>
       </c>
       <c r="R21" t="n">
-        <v>6624272</v>
+        <v>6624211</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2996,7 +3001,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3019,10 +3023,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121359457</v>
+        <v>121359467</v>
       </c>
       <c r="B22" t="n">
-        <v>92014</v>
+        <v>90930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3035,21 +3039,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>1101</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3059,10 +3063,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558395</v>
+        <v>558464</v>
       </c>
       <c r="R22" t="n">
-        <v>6624316</v>
+        <v>6624306</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3125,10 +3129,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121359443</v>
+        <v>121359466</v>
       </c>
       <c r="B23" t="n">
-        <v>90724</v>
+        <v>90678</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3137,25 +3141,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3165,10 +3169,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558441</v>
+        <v>558467</v>
       </c>
       <c r="R23" t="n">
-        <v>6624265</v>
+        <v>6624274</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3231,10 +3235,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121359444</v>
+        <v>121359457</v>
       </c>
       <c r="B24" t="n">
-        <v>92019</v>
+        <v>92017</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3243,41 +3247,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>5449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558433</v>
+        <v>558395</v>
       </c>
       <c r="R24" t="n">
-        <v>6624286</v>
+        <v>6624316</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3318,7 +3319,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3341,10 +3341,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121359471</v>
+        <v>121359460</v>
       </c>
       <c r="B25" t="n">
-        <v>95642</v>
+        <v>8435</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3353,25 +3353,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558521</v>
+        <v>558352</v>
       </c>
       <c r="R25" t="n">
-        <v>6624319</v>
+        <v>6624226</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3447,10 +3447,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121359459</v>
+        <v>121359471</v>
       </c>
       <c r="B26" t="n">
-        <v>79222</v>
+        <v>95645</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3463,21 +3463,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558364</v>
+        <v>558521</v>
       </c>
       <c r="R26" t="n">
-        <v>6624216</v>
+        <v>6624319</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121394942</v>
+        <v>121394933</v>
       </c>
       <c r="B27" t="n">
-        <v>95958</v>
+        <v>8435</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3565,25 +3565,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>990</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558390</v>
+        <v>558377</v>
       </c>
       <c r="R27" t="n">
-        <v>6624295</v>
+        <v>6624106</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3637,7 +3637,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3660,10 +3659,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121394932</v>
+        <v>121394549</v>
       </c>
       <c r="B28" t="n">
-        <v>91102</v>
+        <v>92015</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3676,16 +3675,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6040162</v>
+        <v>5448</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3695,10 +3699,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558394</v>
+        <v>558468</v>
       </c>
       <c r="R28" t="n">
-        <v>6624091</v>
+        <v>6624096</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3725,12 +3729,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3739,7 +3743,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3762,10 +3765,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121394943</v>
+        <v>121394942</v>
       </c>
       <c r="B29" t="n">
-        <v>95642</v>
+        <v>95961</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3774,25 +3777,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>990</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3846,6 +3849,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3868,10 +3872,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121394549</v>
+        <v>121394945</v>
       </c>
       <c r="B30" t="n">
-        <v>92012</v>
+        <v>95645</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3884,21 +3888,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5448</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3908,10 +3912,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558468</v>
+        <v>558441</v>
       </c>
       <c r="R30" t="n">
-        <v>6624096</v>
+        <v>6624265</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3938,12 +3942,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3977,7 +3981,7 @@
         <v>121394944</v>
       </c>
       <c r="B31" t="n">
-        <v>90675</v>
+        <v>90678</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4080,10 +4084,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121394933</v>
+        <v>121394932</v>
       </c>
       <c r="B32" t="n">
-        <v>8432</v>
+        <v>91105</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4092,25 +4096,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Mindre märgborre</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4120,10 +4119,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558377</v>
+        <v>558394</v>
       </c>
       <c r="R32" t="n">
-        <v>6624106</v>
+        <v>6624091</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4164,6 +4163,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4186,10 +4186,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121394945</v>
+        <v>121394943</v>
       </c>
       <c r="B33" t="n">
-        <v>95642</v>
+        <v>95645</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558441</v>
+        <v>558390</v>
       </c>
       <c r="R33" t="n">
-        <v>6624265</v>
+        <v>6624295</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4295,7 +4295,7 @@
         <v>121394934</v>
       </c>
       <c r="B34" t="n">
-        <v>95642</v>
+        <v>95645</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4398,10 +4398,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121394345</v>
+        <v>121394339</v>
       </c>
       <c r="B35" t="n">
-        <v>97043</v>
+        <v>74652</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4414,19 +4414,23 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221944</v>
+        <v>6426</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4434,10 +4438,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558386</v>
+        <v>558458</v>
       </c>
       <c r="R35" t="n">
-        <v>6624222</v>
+        <v>6624309</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4478,7 +4482,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4501,10 +4504,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121394355</v>
+        <v>121394364</v>
       </c>
       <c r="B36" t="n">
-        <v>92183</v>
+        <v>8435</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4513,41 +4516,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2079</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558377</v>
+        <v>558351</v>
       </c>
       <c r="R36" t="n">
-        <v>6624159</v>
+        <v>6624213</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4588,24 +4588,8 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AL36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>undersida av grov ved mot mark # tall</t>
-        </is>
-      </c>
-      <c r="AQ36" t="inlineStr">
-        <is>
-          <t>Ralf Lundmark</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4626,10 +4610,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121394343</v>
+        <v>121394314</v>
       </c>
       <c r="B37" t="n">
-        <v>74649</v>
+        <v>91105</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4638,25 +4622,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6426</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Kattfotslav</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4666,10 +4645,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558405</v>
+        <v>558428</v>
       </c>
       <c r="R37" t="n">
-        <v>6624226</v>
+        <v>6624048</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4704,12 +4683,18 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4732,10 +4717,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121394304</v>
+        <v>121394349</v>
       </c>
       <c r="B38" t="n">
-        <v>98095</v>
+        <v>84300</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4744,42 +4729,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>3518</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558372</v>
+        <v>558419</v>
       </c>
       <c r="R38" t="n">
-        <v>6624277</v>
+        <v>6624081</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4806,12 +4787,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4842,10 +4823,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121394320</v>
+        <v>121394305</v>
       </c>
       <c r="B39" t="n">
-        <v>89761</v>
+        <v>98098</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4854,38 +4835,42 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558465</v>
+        <v>558420</v>
       </c>
       <c r="R39" t="n">
-        <v>6624192</v>
+        <v>6624193</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4912,12 +4897,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4948,10 +4933,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121394319</v>
+        <v>121394304</v>
       </c>
       <c r="B40" t="n">
-        <v>8432</v>
+        <v>98098</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4960,38 +4945,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558461</v>
+        <v>558372</v>
       </c>
       <c r="R40" t="n">
-        <v>6624164</v>
+        <v>6624277</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5018,12 +5007,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5057,7 +5046,7 @@
         <v>121394333</v>
       </c>
       <c r="B41" t="n">
-        <v>95642</v>
+        <v>95645</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5160,10 +5149,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121394353</v>
+        <v>121394348</v>
       </c>
       <c r="B42" t="n">
-        <v>4766</v>
+        <v>92020</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5172,25 +5161,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100299</v>
+        <v>1968</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5200,10 +5189,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558363</v>
+        <v>558437</v>
       </c>
       <c r="R42" t="n">
-        <v>6624071</v>
+        <v>6624152</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5266,10 +5255,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121394364</v>
+        <v>121394355</v>
       </c>
       <c r="B43" t="n">
-        <v>8432</v>
+        <v>92186</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5278,38 +5267,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558351</v>
+        <v>558377</v>
       </c>
       <c r="R43" t="n">
-        <v>6624213</v>
+        <v>6624159</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5350,8 +5342,24 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>undersida av grov ved mot mark # tall</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5372,10 +5380,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121394365</v>
+        <v>121394548</v>
       </c>
       <c r="B44" t="n">
-        <v>91102</v>
+        <v>92017</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5388,16 +5396,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6040162</v>
+        <v>5449</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5407,10 +5420,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558351</v>
+        <v>558480</v>
       </c>
       <c r="R44" t="n">
-        <v>6624213</v>
+        <v>6624122</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5437,12 +5450,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5451,7 +5464,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5474,10 +5486,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121394321</v>
+        <v>121394343</v>
       </c>
       <c r="B45" t="n">
-        <v>95642</v>
+        <v>74652</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5486,25 +5498,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5514,10 +5526,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>558450</v>
+        <v>558405</v>
       </c>
       <c r="R45" t="n">
-        <v>6624202</v>
+        <v>6624226</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5544,12 +5556,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5580,10 +5592,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121394356</v>
+        <v>121394359</v>
       </c>
       <c r="B46" t="n">
-        <v>91401</v>
+        <v>74652</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5592,20 +5604,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>757</v>
+        <v>6426</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5615,10 +5632,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558364</v>
+        <v>558414</v>
       </c>
       <c r="R46" t="n">
-        <v>6624122</v>
+        <v>6624238</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5645,12 +5662,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5659,7 +5676,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5682,10 +5698,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121394322</v>
+        <v>121394344</v>
       </c>
       <c r="B47" t="n">
-        <v>5189</v>
+        <v>92001</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5698,21 +5714,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>105930</v>
+        <v>4366</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5722,10 +5738,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558492</v>
+        <v>558407</v>
       </c>
       <c r="R47" t="n">
-        <v>6624223</v>
+        <v>6624166</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5788,10 +5804,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121394305</v>
+        <v>121394357</v>
       </c>
       <c r="B48" t="n">
-        <v>98095</v>
+        <v>95392</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5800,42 +5816,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>558420</v>
+        <v>558396</v>
       </c>
       <c r="R48" t="n">
-        <v>6624193</v>
+        <v>6624233</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5862,12 +5874,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5898,10 +5910,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121394325</v>
+        <v>121394324</v>
       </c>
       <c r="B49" t="n">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5914,21 +5926,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6004,10 +6016,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121394326</v>
+        <v>121394325</v>
       </c>
       <c r="B50" t="n">
-        <v>4766</v>
+        <v>5172</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6020,21 +6032,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6110,10 +6122,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121394352</v>
+        <v>121394351</v>
       </c>
       <c r="B51" t="n">
-        <v>5169</v>
+        <v>5192</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6126,21 +6138,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6216,10 +6228,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121394494</v>
+        <v>121394270</v>
       </c>
       <c r="B52" t="n">
-        <v>89411</v>
+        <v>98098</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6232,34 +6244,38 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6286</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>558369</v>
+        <v>558522</v>
       </c>
       <c r="R52" t="n">
-        <v>6624121</v>
+        <v>6624290</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6286,12 +6302,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6302,11 +6318,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>tallskog på finmorän</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6327,10 +6338,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121394349</v>
+        <v>121394356</v>
       </c>
       <c r="B53" t="n">
-        <v>84297</v>
+        <v>91404</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6339,25 +6350,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3518</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Smal svampklubba</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6367,10 +6373,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>558419</v>
+        <v>558364</v>
       </c>
       <c r="R53" t="n">
-        <v>6624081</v>
+        <v>6624122</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6397,12 +6403,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6411,6 +6417,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6433,10 +6440,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121394344</v>
+        <v>121394352</v>
       </c>
       <c r="B54" t="n">
-        <v>91998</v>
+        <v>5172</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6449,21 +6456,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4366</v>
+        <v>100526</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6473,10 +6480,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>558407</v>
+        <v>558363</v>
       </c>
       <c r="R54" t="n">
-        <v>6624166</v>
+        <v>6624071</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6539,10 +6546,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121394324</v>
+        <v>121394306</v>
       </c>
       <c r="B55" t="n">
-        <v>5189</v>
+        <v>98098</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6551,38 +6558,42 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>558478</v>
+        <v>558437</v>
       </c>
       <c r="R55" t="n">
-        <v>6624257</v>
+        <v>6624213</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6609,12 +6620,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6645,10 +6656,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121394327</v>
+        <v>121394321</v>
       </c>
       <c r="B56" t="n">
-        <v>90724</v>
+        <v>95645</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6661,21 +6672,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1204</v>
+        <v>53</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6685,10 +6696,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>558466</v>
+        <v>558450</v>
       </c>
       <c r="R56" t="n">
-        <v>6624295</v>
+        <v>6624202</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6715,12 +6726,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6751,10 +6762,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121394354</v>
+        <v>121394310</v>
       </c>
       <c r="B57" t="n">
-        <v>86291</v>
+        <v>95645</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6767,21 +6778,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3739</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6791,10 +6802,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>558390</v>
+        <v>558437</v>
       </c>
       <c r="R57" t="n">
-        <v>6624037</v>
+        <v>6624264</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6821,12 +6832,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6857,10 +6868,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121394357</v>
+        <v>121394272</v>
       </c>
       <c r="B58" t="n">
-        <v>95389</v>
+        <v>58219</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6873,34 +6884,43 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2869</v>
+        <v>208242</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>558396</v>
+        <v>558519</v>
       </c>
       <c r="R58" t="n">
-        <v>6624233</v>
+        <v>6624313</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6927,12 +6947,17 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>under ved i barrskog</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6963,10 +6988,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121394272</v>
+        <v>121394363</v>
       </c>
       <c r="B59" t="n">
-        <v>58216</v>
+        <v>5172</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6979,43 +7004,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>208242</v>
+        <v>100526</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>558519</v>
+        <v>558367</v>
       </c>
       <c r="R59" t="n">
-        <v>6624313</v>
+        <v>6624219</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7042,17 +7058,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>under ved i barrskog</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7083,10 +7094,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121394323</v>
+        <v>121394345</v>
       </c>
       <c r="B60" t="n">
-        <v>5169</v>
+        <v>97046</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7099,23 +7110,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100526</v>
+        <v>221944</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7123,10 +7130,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>558492</v>
+        <v>558386</v>
       </c>
       <c r="R60" t="n">
-        <v>6624223</v>
+        <v>6624222</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7167,6 +7174,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7189,10 +7197,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121394351</v>
+        <v>121394327</v>
       </c>
       <c r="B61" t="n">
-        <v>5189</v>
+        <v>90727</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7201,25 +7209,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>105930</v>
+        <v>1204</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7229,10 +7237,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>558363</v>
+        <v>558466</v>
       </c>
       <c r="R61" t="n">
-        <v>6624071</v>
+        <v>6624295</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7295,10 +7303,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121394314</v>
+        <v>121394322</v>
       </c>
       <c r="B62" t="n">
-        <v>91102</v>
+        <v>5192</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7307,20 +7315,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6040162</v>
+        <v>105930</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7330,10 +7343,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>558428</v>
+        <v>558492</v>
       </c>
       <c r="R62" t="n">
-        <v>6624048</v>
+        <v>6624223</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7368,18 +7381,12 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7402,10 +7409,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121394310</v>
+        <v>121394303</v>
       </c>
       <c r="B63" t="n">
-        <v>95642</v>
+        <v>98098</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7414,38 +7421,42 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>558437</v>
+        <v>558385</v>
       </c>
       <c r="R63" t="n">
-        <v>6624264</v>
+        <v>6624276</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7508,10 +7519,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121394348</v>
+        <v>121394354</v>
       </c>
       <c r="B64" t="n">
-        <v>92017</v>
+        <v>86294</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7524,21 +7535,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1968</v>
+        <v>3739</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7548,10 +7559,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>558437</v>
+        <v>558390</v>
       </c>
       <c r="R64" t="n">
-        <v>6624152</v>
+        <v>6624037</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7614,10 +7625,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121394303</v>
+        <v>121394315</v>
       </c>
       <c r="B65" t="n">
-        <v>98095</v>
+        <v>91973</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7630,38 +7641,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6055</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>558385</v>
+        <v>558428</v>
       </c>
       <c r="R65" t="n">
-        <v>6624276</v>
+        <v>6624044</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7688,12 +7695,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7724,10 +7731,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121394339</v>
+        <v>121394319</v>
       </c>
       <c r="B66" t="n">
-        <v>74649</v>
+        <v>8435</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7740,21 +7747,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6426</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7764,10 +7771,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>558458</v>
+        <v>558461</v>
       </c>
       <c r="R66" t="n">
-        <v>6624309</v>
+        <v>6624164</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7794,12 +7801,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7830,10 +7837,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121394309</v>
+        <v>121394365</v>
       </c>
       <c r="B67" t="n">
-        <v>95681</v>
+        <v>91105</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7842,25 +7849,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2590</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Kornknutmossa</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7870,10 +7872,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>558437</v>
+        <v>558351</v>
       </c>
       <c r="R67" t="n">
-        <v>6624264</v>
+        <v>6624213</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7900,12 +7902,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7914,6 +7916,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7936,10 +7939,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121394350</v>
+        <v>121394320</v>
       </c>
       <c r="B68" t="n">
-        <v>94760</v>
+        <v>89764</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7948,25 +7951,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2170</v>
+        <v>1962</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7976,10 +7979,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>558402</v>
+        <v>558465</v>
       </c>
       <c r="R68" t="n">
-        <v>6624073</v>
+        <v>6624192</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8006,12 +8009,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8042,10 +8045,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121394306</v>
+        <v>121394309</v>
       </c>
       <c r="B69" t="n">
-        <v>98095</v>
+        <v>95684</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8054,32 +8057,28 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
@@ -8089,7 +8088,7 @@
         <v>558437</v>
       </c>
       <c r="R69" t="n">
-        <v>6624213</v>
+        <v>6624264</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8152,10 +8151,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121394548</v>
+        <v>121394353</v>
       </c>
       <c r="B70" t="n">
-        <v>92014</v>
+        <v>4769</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8164,25 +8163,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5449</v>
+        <v>100299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8192,10 +8191,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>558480</v>
+        <v>558363</v>
       </c>
       <c r="R70" t="n">
-        <v>6624122</v>
+        <v>6624071</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8222,12 +8221,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8258,10 +8257,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121394315</v>
+        <v>121394323</v>
       </c>
       <c r="B71" t="n">
-        <v>91970</v>
+        <v>5172</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8270,25 +8269,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6055</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8298,10 +8297,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>558428</v>
+        <v>558492</v>
       </c>
       <c r="R71" t="n">
-        <v>6624044</v>
+        <v>6624223</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8328,12 +8327,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8364,10 +8363,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121394313</v>
+        <v>121394350</v>
       </c>
       <c r="B72" t="n">
-        <v>91103</v>
+        <v>94763</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8376,20 +8375,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6040186</v>
+        <v>2170</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8399,10 +8403,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>558412</v>
+        <v>558402</v>
       </c>
       <c r="R72" t="n">
-        <v>6624060</v>
+        <v>6624073</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8437,18 +8441,12 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8471,10 +8469,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121394363</v>
+        <v>121394494</v>
       </c>
       <c r="B73" t="n">
-        <v>5169</v>
+        <v>89414</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8483,25 +8481,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100526</v>
+        <v>6286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8511,10 +8509,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>558367</v>
+        <v>558369</v>
       </c>
       <c r="R73" t="n">
-        <v>6624219</v>
+        <v>6624121</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8541,12 +8539,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8557,6 +8555,11 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>tallskog på finmorän</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8577,10 +8580,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121394342</v>
+        <v>121394313</v>
       </c>
       <c r="B74" t="n">
-        <v>74649</v>
+        <v>91106</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8589,25 +8592,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6426</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Kattfotslav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8617,10 +8615,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>558435</v>
+        <v>558412</v>
       </c>
       <c r="R74" t="n">
-        <v>6624227</v>
+        <v>6624060</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8655,12 +8653,18 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8683,10 +8687,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121394359</v>
+        <v>121394326</v>
       </c>
       <c r="B75" t="n">
-        <v>74649</v>
+        <v>4769</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8699,21 +8703,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6426</v>
+        <v>100299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8723,10 +8727,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>558414</v>
+        <v>558478</v>
       </c>
       <c r="R75" t="n">
-        <v>6624238</v>
+        <v>6624257</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8753,12 +8757,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8789,10 +8793,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121394270</v>
+        <v>121394342</v>
       </c>
       <c r="B76" t="n">
-        <v>98095</v>
+        <v>74652</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8801,42 +8805,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>558522</v>
+        <v>558435</v>
       </c>
       <c r="R76" t="n">
-        <v>6624290</v>
+        <v>6624227</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD76" t="b">

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -2069,10 +2069,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121359506</v>
+        <v>121359457</v>
       </c>
       <c r="B13" t="n">
-        <v>8435</v>
+        <v>92017</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2081,25 +2081,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2109,10 +2109,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558352</v>
+        <v>558395</v>
       </c>
       <c r="R13" t="n">
-        <v>6624128</v>
+        <v>6624316</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121359444</v>
+        <v>121359461</v>
       </c>
       <c r="B15" t="n">
-        <v>92022</v>
+        <v>79225</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2289,41 +2289,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558433</v>
+        <v>558352</v>
       </c>
       <c r="R15" t="n">
-        <v>6624286</v>
+        <v>6624226</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2364,7 +2361,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2387,10 +2383,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121359443</v>
+        <v>121359444</v>
       </c>
       <c r="B16" t="n">
-        <v>90727</v>
+        <v>92022</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2399,38 +2395,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558441</v>
+        <v>558433</v>
       </c>
       <c r="R16" t="n">
-        <v>6624265</v>
+        <v>6624286</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2471,6 +2470,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121359469</v>
+        <v>121359460</v>
       </c>
       <c r="B17" t="n">
-        <v>90713</v>
+        <v>8435</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2505,25 +2505,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558491</v>
+        <v>558352</v>
       </c>
       <c r="R17" t="n">
-        <v>6624274</v>
+        <v>6624226</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121359461</v>
+        <v>121359471</v>
       </c>
       <c r="B18" t="n">
-        <v>79225</v>
+        <v>95645</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2615,21 +2615,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558352</v>
+        <v>558521</v>
       </c>
       <c r="R18" t="n">
-        <v>6624226</v>
+        <v>6624319</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2705,10 +2705,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121359462</v>
+        <v>121359466</v>
       </c>
       <c r="B19" t="n">
-        <v>90917</v>
+        <v>90678</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2717,25 +2717,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1106</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558376</v>
+        <v>558467</v>
       </c>
       <c r="R19" t="n">
-        <v>6624261</v>
+        <v>6624274</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2811,10 +2811,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121359459</v>
+        <v>121359443</v>
       </c>
       <c r="B20" t="n">
-        <v>79225</v>
+        <v>90727</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2827,21 +2827,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2851,10 +2851,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558364</v>
+        <v>558441</v>
       </c>
       <c r="R20" t="n">
-        <v>6624216</v>
+        <v>6624265</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2917,10 +2917,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121359458</v>
+        <v>121359506</v>
       </c>
       <c r="B21" t="n">
-        <v>92015</v>
+        <v>8435</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2929,25 +2929,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5448</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558350</v>
+        <v>558352</v>
       </c>
       <c r="R21" t="n">
-        <v>6624211</v>
+        <v>6624128</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121359467</v>
+        <v>121359469</v>
       </c>
       <c r="B22" t="n">
-        <v>90930</v>
+        <v>90713</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3039,21 +3039,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1101</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3063,10 +3063,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558464</v>
+        <v>558491</v>
       </c>
       <c r="R22" t="n">
-        <v>6624306</v>
+        <v>6624274</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3129,10 +3129,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121359466</v>
+        <v>121359459</v>
       </c>
       <c r="B23" t="n">
-        <v>90678</v>
+        <v>79225</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3141,25 +3141,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558467</v>
+        <v>558364</v>
       </c>
       <c r="R23" t="n">
-        <v>6624274</v>
+        <v>6624216</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121359457</v>
+        <v>121359467</v>
       </c>
       <c r="B24" t="n">
-        <v>92017</v>
+        <v>90930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3251,21 +3251,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>1101</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558395</v>
+        <v>558464</v>
       </c>
       <c r="R24" t="n">
-        <v>6624316</v>
+        <v>6624306</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3341,10 +3341,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121359460</v>
+        <v>121359462</v>
       </c>
       <c r="B25" t="n">
-        <v>8435</v>
+        <v>90917</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3353,25 +3353,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>1106</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558352</v>
+        <v>558376</v>
       </c>
       <c r="R25" t="n">
-        <v>6624226</v>
+        <v>6624261</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3447,10 +3447,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121359471</v>
+        <v>121359458</v>
       </c>
       <c r="B26" t="n">
-        <v>95645</v>
+        <v>92015</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3463,21 +3463,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>53</v>
+        <v>5448</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558521</v>
+        <v>558350</v>
       </c>
       <c r="R26" t="n">
-        <v>6624319</v>
+        <v>6624211</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121394933</v>
+        <v>121394944</v>
       </c>
       <c r="B27" t="n">
-        <v>8435</v>
+        <v>90678</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3569,21 +3569,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558377</v>
+        <v>558441</v>
       </c>
       <c r="R27" t="n">
-        <v>6624106</v>
+        <v>6624265</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3659,10 +3659,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121394549</v>
+        <v>121394932</v>
       </c>
       <c r="B28" t="n">
-        <v>92015</v>
+        <v>91105</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3675,21 +3675,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5448</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Svartvit taggsvamp</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3699,10 +3694,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558468</v>
+        <v>558394</v>
       </c>
       <c r="R28" t="n">
-        <v>6624096</v>
+        <v>6624091</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3729,12 +3724,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3743,6 +3738,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3765,10 +3761,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121394942</v>
+        <v>121394943</v>
       </c>
       <c r="B29" t="n">
-        <v>95961</v>
+        <v>95645</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3777,25 +3773,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>990</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3849,7 +3845,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3872,7 +3867,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121394945</v>
+        <v>121394934</v>
       </c>
       <c r="B30" t="n">
         <v>95645</v>
@@ -3912,10 +3907,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558441</v>
+        <v>558377</v>
       </c>
       <c r="R30" t="n">
-        <v>6624265</v>
+        <v>6624106</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3978,10 +3973,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121394944</v>
+        <v>121394549</v>
       </c>
       <c r="B31" t="n">
-        <v>90678</v>
+        <v>92015</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3990,25 +3985,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>5448</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4018,10 +4013,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558441</v>
+        <v>558468</v>
       </c>
       <c r="R31" t="n">
-        <v>6624265</v>
+        <v>6624096</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4048,12 +4043,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4084,10 +4079,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121394932</v>
+        <v>121394933</v>
       </c>
       <c r="B32" t="n">
-        <v>91105</v>
+        <v>8435</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4096,20 +4091,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6040162</v>
+        <v>106545</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558394</v>
+        <v>558377</v>
       </c>
       <c r="R32" t="n">
-        <v>6624091</v>
+        <v>6624106</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4163,7 +4163,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4186,10 +4185,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121394943</v>
+        <v>121394942</v>
       </c>
       <c r="B33" t="n">
-        <v>95645</v>
+        <v>95961</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4198,25 +4197,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>990</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4270,6 +4269,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4292,7 +4292,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121394934</v>
+        <v>121394945</v>
       </c>
       <c r="B34" t="n">
         <v>95645</v>
@@ -4332,10 +4332,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558377</v>
+        <v>558441</v>
       </c>
       <c r="R34" t="n">
-        <v>6624106</v>
+        <v>6624265</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4398,10 +4398,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121394339</v>
+        <v>121394364</v>
       </c>
       <c r="B35" t="n">
-        <v>74652</v>
+        <v>8435</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4414,21 +4414,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6426</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4438,10 +4438,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558458</v>
+        <v>558351</v>
       </c>
       <c r="R35" t="n">
-        <v>6624309</v>
+        <v>6624213</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4468,12 +4468,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4504,10 +4504,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121394364</v>
+        <v>121394310</v>
       </c>
       <c r="B36" t="n">
-        <v>8435</v>
+        <v>95645</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4516,25 +4516,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558351</v>
+        <v>558437</v>
       </c>
       <c r="R36" t="n">
-        <v>6624213</v>
+        <v>6624264</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4574,12 +4574,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4610,10 +4610,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121394314</v>
+        <v>121394355</v>
       </c>
       <c r="B37" t="n">
-        <v>91105</v>
+        <v>92186</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4626,29 +4626,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6040162</v>
+        <v>2079</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558428</v>
+        <v>558377</v>
       </c>
       <c r="R37" t="n">
-        <v>6624048</v>
+        <v>6624159</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4675,17 +4683,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4697,6 +4700,21 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>undersida av grov ved mot mark # tall</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4717,10 +4735,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121394349</v>
+        <v>121394315</v>
       </c>
       <c r="B38" t="n">
-        <v>84300</v>
+        <v>91973</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4729,25 +4747,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3518</v>
+        <v>6055</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4757,10 +4775,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558419</v>
+        <v>558428</v>
       </c>
       <c r="R38" t="n">
-        <v>6624081</v>
+        <v>6624044</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4787,12 +4805,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4823,10 +4841,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121394305</v>
+        <v>121394325</v>
       </c>
       <c r="B39" t="n">
-        <v>98098</v>
+        <v>5172</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4835,42 +4853,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558420</v>
+        <v>558478</v>
       </c>
       <c r="R39" t="n">
-        <v>6624193</v>
+        <v>6624257</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4897,12 +4911,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4933,7 +4947,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121394304</v>
+        <v>121394303</v>
       </c>
       <c r="B40" t="n">
         <v>98098</v>
@@ -4968,7 +4982,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4977,10 +4991,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558372</v>
+        <v>558385</v>
       </c>
       <c r="R40" t="n">
-        <v>6624277</v>
+        <v>6624276</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5043,10 +5057,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121394333</v>
+        <v>121394343</v>
       </c>
       <c r="B41" t="n">
-        <v>95645</v>
+        <v>74652</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5055,25 +5069,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5083,10 +5097,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558528</v>
+        <v>558405</v>
       </c>
       <c r="R41" t="n">
-        <v>6624316</v>
+        <v>6624226</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5149,10 +5163,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121394348</v>
+        <v>121394344</v>
       </c>
       <c r="B42" t="n">
-        <v>92020</v>
+        <v>92001</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5161,25 +5175,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1968</v>
+        <v>4366</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5189,10 +5203,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558437</v>
+        <v>558407</v>
       </c>
       <c r="R42" t="n">
-        <v>6624152</v>
+        <v>6624166</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5255,10 +5269,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121394355</v>
+        <v>121394354</v>
       </c>
       <c r="B43" t="n">
-        <v>92186</v>
+        <v>86294</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5271,37 +5285,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2079</v>
+        <v>3739</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558377</v>
+        <v>558390</v>
       </c>
       <c r="R43" t="n">
-        <v>6624159</v>
+        <v>6624037</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5328,12 +5339,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5342,24 +5353,8 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>undersida av grov ved mot mark # tall</t>
-        </is>
-      </c>
-      <c r="AQ43" t="inlineStr">
-        <is>
-          <t>Ralf Lundmark</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5380,10 +5375,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121394548</v>
+        <v>121394351</v>
       </c>
       <c r="B44" t="n">
-        <v>92017</v>
+        <v>5192</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5392,25 +5387,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5449</v>
+        <v>105930</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5420,10 +5415,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558480</v>
+        <v>558363</v>
       </c>
       <c r="R44" t="n">
-        <v>6624122</v>
+        <v>6624071</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5450,12 +5445,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5486,10 +5481,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121394343</v>
+        <v>121394363</v>
       </c>
       <c r="B45" t="n">
-        <v>74652</v>
+        <v>5172</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5502,21 +5497,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6426</v>
+        <v>100526</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5526,10 +5521,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>558405</v>
+        <v>558367</v>
       </c>
       <c r="R45" t="n">
-        <v>6624226</v>
+        <v>6624219</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5556,12 +5551,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5592,10 +5587,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121394359</v>
+        <v>121394357</v>
       </c>
       <c r="B46" t="n">
-        <v>74652</v>
+        <v>95392</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5608,21 +5603,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6426</v>
+        <v>2869</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5632,10 +5627,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558414</v>
+        <v>558396</v>
       </c>
       <c r="R46" t="n">
-        <v>6624238</v>
+        <v>6624233</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5698,10 +5693,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121394344</v>
+        <v>121394324</v>
       </c>
       <c r="B47" t="n">
-        <v>92001</v>
+        <v>5192</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5714,21 +5709,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4366</v>
+        <v>105930</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5738,10 +5733,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558407</v>
+        <v>558478</v>
       </c>
       <c r="R47" t="n">
-        <v>6624166</v>
+        <v>6624257</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5804,10 +5799,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121394357</v>
+        <v>121394321</v>
       </c>
       <c r="B48" t="n">
-        <v>95392</v>
+        <v>95645</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5816,25 +5811,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2869</v>
+        <v>53</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5844,10 +5839,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>558396</v>
+        <v>558450</v>
       </c>
       <c r="R48" t="n">
-        <v>6624233</v>
+        <v>6624202</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5874,12 +5869,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5910,10 +5905,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121394324</v>
+        <v>121394494</v>
       </c>
       <c r="B49" t="n">
-        <v>5192</v>
+        <v>89414</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5922,25 +5917,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>105930</v>
+        <v>6286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5950,10 +5945,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558478</v>
+        <v>558369</v>
       </c>
       <c r="R49" t="n">
-        <v>6624257</v>
+        <v>6624121</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5980,12 +5975,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5996,6 +5991,11 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>tallskog på finmorän</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6016,10 +6016,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121394325</v>
+        <v>121394270</v>
       </c>
       <c r="B50" t="n">
-        <v>5172</v>
+        <v>98098</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6028,38 +6028,42 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>558478</v>
+        <v>558522</v>
       </c>
       <c r="R50" t="n">
-        <v>6624257</v>
+        <v>6624290</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6086,12 +6090,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6122,10 +6126,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121394351</v>
+        <v>121394272</v>
       </c>
       <c r="B51" t="n">
-        <v>5192</v>
+        <v>58219</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6138,16 +6142,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>105930</v>
+        <v>208242</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6155,17 +6159,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>558363</v>
+        <v>558519</v>
       </c>
       <c r="R51" t="n">
-        <v>6624071</v>
+        <v>6624313</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6192,12 +6205,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>under ved i barrskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6228,10 +6246,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121394270</v>
+        <v>121394327</v>
       </c>
       <c r="B52" t="n">
-        <v>98098</v>
+        <v>90727</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6240,42 +6258,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>558522</v>
+        <v>558466</v>
       </c>
       <c r="R52" t="n">
-        <v>6624290</v>
+        <v>6624295</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6302,12 +6316,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6338,10 +6352,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121394356</v>
+        <v>121394309</v>
       </c>
       <c r="B53" t="n">
-        <v>91404</v>
+        <v>95684</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6350,20 +6364,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>757</v>
+        <v>2590</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6373,10 +6392,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>558364</v>
+        <v>558437</v>
       </c>
       <c r="R53" t="n">
-        <v>6624122</v>
+        <v>6624264</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6403,12 +6422,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6417,7 +6436,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6440,10 +6458,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121394352</v>
+        <v>121394313</v>
       </c>
       <c r="B54" t="n">
-        <v>5172</v>
+        <v>91106</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6452,25 +6470,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6480,10 +6493,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>558363</v>
+        <v>558412</v>
       </c>
       <c r="R54" t="n">
-        <v>6624071</v>
+        <v>6624060</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6518,12 +6531,18 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6546,10 +6565,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121394306</v>
+        <v>121394333</v>
       </c>
       <c r="B55" t="n">
-        <v>98098</v>
+        <v>95645</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6558,42 +6577,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>558437</v>
+        <v>558528</v>
       </c>
       <c r="R55" t="n">
-        <v>6624213</v>
+        <v>6624316</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6620,12 +6635,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6656,10 +6671,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121394321</v>
+        <v>121394348</v>
       </c>
       <c r="B56" t="n">
-        <v>95645</v>
+        <v>92020</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6672,21 +6687,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>1968</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6696,10 +6711,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>558450</v>
+        <v>558437</v>
       </c>
       <c r="R56" t="n">
-        <v>6624202</v>
+        <v>6624152</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6726,12 +6741,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6762,10 +6777,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121394310</v>
+        <v>121394350</v>
       </c>
       <c r="B57" t="n">
-        <v>95645</v>
+        <v>94763</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6774,25 +6789,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6802,10 +6817,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>558437</v>
+        <v>558402</v>
       </c>
       <c r="R57" t="n">
-        <v>6624264</v>
+        <v>6624073</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6832,12 +6847,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6868,10 +6883,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121394272</v>
+        <v>121394319</v>
       </c>
       <c r="B58" t="n">
-        <v>58219</v>
+        <v>8435</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6884,43 +6899,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>208242</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>558519</v>
+        <v>558461</v>
       </c>
       <c r="R58" t="n">
-        <v>6624313</v>
+        <v>6624164</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6947,17 +6953,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>under ved i barrskog</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6988,10 +6989,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121394363</v>
+        <v>121394365</v>
       </c>
       <c r="B59" t="n">
-        <v>5172</v>
+        <v>91105</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7000,25 +7001,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7028,10 +7024,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>558367</v>
+        <v>558351</v>
       </c>
       <c r="R59" t="n">
-        <v>6624219</v>
+        <v>6624213</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7072,6 +7068,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7094,10 +7091,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121394345</v>
+        <v>121394323</v>
       </c>
       <c r="B60" t="n">
-        <v>97046</v>
+        <v>5172</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7110,19 +7107,23 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221944</v>
+        <v>100526</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7130,10 +7131,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>558386</v>
+        <v>558492</v>
       </c>
       <c r="R60" t="n">
-        <v>6624222</v>
+        <v>6624223</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7174,7 +7175,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7197,10 +7197,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121394327</v>
+        <v>121394548</v>
       </c>
       <c r="B61" t="n">
-        <v>90727</v>
+        <v>92017</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7213,21 +7213,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1204</v>
+        <v>5449</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7237,10 +7237,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>558466</v>
+        <v>558480</v>
       </c>
       <c r="R61" t="n">
-        <v>6624295</v>
+        <v>6624122</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7267,12 +7267,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7409,10 +7409,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121394303</v>
+        <v>121394314</v>
       </c>
       <c r="B63" t="n">
-        <v>98098</v>
+        <v>91105</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7421,42 +7421,33 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>558385</v>
+        <v>558428</v>
       </c>
       <c r="R63" t="n">
-        <v>6624276</v>
+        <v>6624048</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7483,12 +7474,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7497,6 +7493,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7519,10 +7516,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121394354</v>
+        <v>121394359</v>
       </c>
       <c r="B64" t="n">
-        <v>86294</v>
+        <v>74652</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7531,25 +7528,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3739</v>
+        <v>6426</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7559,10 +7556,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>558390</v>
+        <v>558414</v>
       </c>
       <c r="R64" t="n">
-        <v>6624037</v>
+        <v>6624238</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7589,12 +7586,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7625,10 +7622,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121394315</v>
+        <v>121394352</v>
       </c>
       <c r="B65" t="n">
-        <v>91973</v>
+        <v>5172</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7637,25 +7634,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6055</v>
+        <v>100526</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7665,10 +7662,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>558428</v>
+        <v>558363</v>
       </c>
       <c r="R65" t="n">
-        <v>6624044</v>
+        <v>6624071</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7695,12 +7692,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7731,10 +7728,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121394319</v>
+        <v>121394353</v>
       </c>
       <c r="B66" t="n">
-        <v>8435</v>
+        <v>4769</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7747,21 +7744,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>100299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7771,10 +7768,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>558461</v>
+        <v>558363</v>
       </c>
       <c r="R66" t="n">
-        <v>6624164</v>
+        <v>6624071</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7801,12 +7798,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7837,10 +7834,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121394365</v>
+        <v>121394305</v>
       </c>
       <c r="B67" t="n">
-        <v>91105</v>
+        <v>98098</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7849,33 +7846,42 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6040162</v>
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>558351</v>
+        <v>558420</v>
       </c>
       <c r="R67" t="n">
-        <v>6624213</v>
+        <v>6624193</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7902,12 +7908,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7916,7 +7922,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7939,10 +7944,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121394320</v>
+        <v>121394304</v>
       </c>
       <c r="B68" t="n">
-        <v>89764</v>
+        <v>98098</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7951,38 +7956,42 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>558465</v>
+        <v>558372</v>
       </c>
       <c r="R68" t="n">
-        <v>6624192</v>
+        <v>6624277</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8009,12 +8018,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8045,10 +8054,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121394309</v>
+        <v>121394349</v>
       </c>
       <c r="B69" t="n">
-        <v>95684</v>
+        <v>84300</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8061,21 +8070,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2590</v>
+        <v>3518</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8085,10 +8094,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>558437</v>
+        <v>558419</v>
       </c>
       <c r="R69" t="n">
-        <v>6624264</v>
+        <v>6624081</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8115,12 +8124,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8151,10 +8160,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121394353</v>
+        <v>121394356</v>
       </c>
       <c r="B70" t="n">
-        <v>4769</v>
+        <v>91404</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8163,25 +8172,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100299</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Thomsons trägnagare</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8191,10 +8195,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>558363</v>
+        <v>558364</v>
       </c>
       <c r="R70" t="n">
-        <v>6624071</v>
+        <v>6624122</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8221,12 +8225,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8235,6 +8239,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8257,10 +8262,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121394323</v>
+        <v>121394326</v>
       </c>
       <c r="B71" t="n">
-        <v>5172</v>
+        <v>4769</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8273,21 +8278,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8297,10 +8302,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>558492</v>
+        <v>558478</v>
       </c>
       <c r="R71" t="n">
-        <v>6624223</v>
+        <v>6624257</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8363,10 +8368,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121394350</v>
+        <v>121394342</v>
       </c>
       <c r="B72" t="n">
-        <v>94763</v>
+        <v>74652</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8379,21 +8384,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2170</v>
+        <v>6426</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8403,10 +8408,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>558402</v>
+        <v>558435</v>
       </c>
       <c r="R72" t="n">
-        <v>6624073</v>
+        <v>6624227</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8469,10 +8474,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121394494</v>
+        <v>121394339</v>
       </c>
       <c r="B73" t="n">
-        <v>89414</v>
+        <v>74652</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8481,25 +8486,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6286</v>
+        <v>6426</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8509,10 +8514,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>558369</v>
+        <v>558458</v>
       </c>
       <c r="R73" t="n">
-        <v>6624121</v>
+        <v>6624309</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8539,12 +8544,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8555,11 +8560,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>tallskog på finmorän</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8580,10 +8580,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121394313</v>
+        <v>121394306</v>
       </c>
       <c r="B74" t="n">
-        <v>91106</v>
+        <v>98098</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8592,33 +8592,42 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>558412</v>
+        <v>558437</v>
       </c>
       <c r="R74" t="n">
-        <v>6624060</v>
+        <v>6624213</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8645,17 +8654,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8664,7 +8668,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8687,10 +8690,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121394326</v>
+        <v>121394320</v>
       </c>
       <c r="B75" t="n">
-        <v>4769</v>
+        <v>89764</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8699,25 +8702,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100299</v>
+        <v>1962</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8727,10 +8730,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>558478</v>
+        <v>558465</v>
       </c>
       <c r="R75" t="n">
-        <v>6624257</v>
+        <v>6624192</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8757,12 +8760,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8793,10 +8796,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121394342</v>
+        <v>121394345</v>
       </c>
       <c r="B76" t="n">
-        <v>74652</v>
+        <v>97046</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8809,23 +8812,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6426</v>
+        <v>221944</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8833,10 +8832,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>558435</v>
+        <v>558386</v>
       </c>
       <c r="R76" t="n">
-        <v>6624227</v>
+        <v>6624222</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8877,6 +8876,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -2069,10 +2069,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121359457</v>
+        <v>121359465</v>
       </c>
       <c r="B13" t="n">
-        <v>92017</v>
+        <v>91105</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2085,21 +2085,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2109,10 +2104,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558395</v>
+        <v>558460</v>
       </c>
       <c r="R13" t="n">
-        <v>6624316</v>
+        <v>6624272</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2153,6 +2148,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2175,10 +2171,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121359465</v>
+        <v>121359457</v>
       </c>
       <c r="B14" t="n">
-        <v>91105</v>
+        <v>92017</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2191,16 +2187,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6040162</v>
+        <v>5449</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2210,10 +2211,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558460</v>
+        <v>558395</v>
       </c>
       <c r="R14" t="n">
-        <v>6624272</v>
+        <v>6624316</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2254,7 +2255,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -4947,10 +4947,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121394303</v>
+        <v>121394343</v>
       </c>
       <c r="B40" t="n">
-        <v>98098</v>
+        <v>74652</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4959,42 +4959,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558385</v>
+        <v>558405</v>
       </c>
       <c r="R40" t="n">
-        <v>6624276</v>
+        <v>6624226</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5021,12 +5017,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5057,10 +5053,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121394343</v>
+        <v>121394303</v>
       </c>
       <c r="B41" t="n">
-        <v>74652</v>
+        <v>98098</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5069,38 +5065,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558405</v>
+        <v>558385</v>
       </c>
       <c r="R41" t="n">
-        <v>6624226</v>
+        <v>6624276</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5127,12 +5127,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5587,10 +5587,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121394357</v>
+        <v>121394324</v>
       </c>
       <c r="B46" t="n">
-        <v>95392</v>
+        <v>5192</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5603,21 +5603,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2869</v>
+        <v>105930</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558396</v>
+        <v>558478</v>
       </c>
       <c r="R46" t="n">
-        <v>6624233</v>
+        <v>6624257</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5657,12 +5657,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5693,10 +5693,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121394324</v>
+        <v>121394357</v>
       </c>
       <c r="B47" t="n">
-        <v>5192</v>
+        <v>95392</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5709,21 +5709,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>105930</v>
+        <v>2869</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558478</v>
+        <v>558396</v>
       </c>
       <c r="R47" t="n">
-        <v>6624257</v>
+        <v>6624233</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5763,12 +5763,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -7944,10 +7944,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121394304</v>
+        <v>121394349</v>
       </c>
       <c r="B68" t="n">
-        <v>98098</v>
+        <v>84300</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7956,42 +7956,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>3518</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>558372</v>
+        <v>558419</v>
       </c>
       <c r="R68" t="n">
-        <v>6624277</v>
+        <v>6624081</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8018,12 +8014,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8054,10 +8050,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121394349</v>
+        <v>121394356</v>
       </c>
       <c r="B69" t="n">
-        <v>84300</v>
+        <v>91404</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8066,25 +8062,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3518</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Smal svampklubba</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8094,10 +8085,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>558419</v>
+        <v>558364</v>
       </c>
       <c r="R69" t="n">
-        <v>6624081</v>
+        <v>6624122</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8124,12 +8115,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8138,6 +8129,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8160,10 +8152,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121394356</v>
+        <v>121394304</v>
       </c>
       <c r="B70" t="n">
-        <v>91404</v>
+        <v>98098</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8172,33 +8164,42 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>757</v>
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>558364</v>
+        <v>558372</v>
       </c>
       <c r="R70" t="n">
-        <v>6624122</v>
+        <v>6624277</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8225,12 +8226,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8239,7 +8240,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -5587,10 +5587,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121394324</v>
+        <v>121394357</v>
       </c>
       <c r="B46" t="n">
-        <v>5192</v>
+        <v>95392</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5603,21 +5603,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>105930</v>
+        <v>2869</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558478</v>
+        <v>558396</v>
       </c>
       <c r="R46" t="n">
-        <v>6624257</v>
+        <v>6624233</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5657,12 +5657,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5693,10 +5693,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121394357</v>
+        <v>121394324</v>
       </c>
       <c r="B47" t="n">
-        <v>95392</v>
+        <v>5192</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5709,21 +5709,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2869</v>
+        <v>105930</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558396</v>
+        <v>558478</v>
       </c>
       <c r="R47" t="n">
-        <v>6624233</v>
+        <v>6624257</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5763,12 +5763,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6016,10 +6016,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121394270</v>
+        <v>121394272</v>
       </c>
       <c r="B50" t="n">
-        <v>98098</v>
+        <v>58219</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6028,30 +6028,35 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>208242</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6060,10 +6065,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>558522</v>
+        <v>558519</v>
       </c>
       <c r="R50" t="n">
-        <v>6624290</v>
+        <v>6624313</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6096,6 +6101,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>under ved i barrskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6126,10 +6136,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121394272</v>
+        <v>121394270</v>
       </c>
       <c r="B51" t="n">
-        <v>58219</v>
+        <v>98098</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6138,35 +6148,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>208242</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6175,10 +6180,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>558519</v>
+        <v>558522</v>
       </c>
       <c r="R51" t="n">
-        <v>6624313</v>
+        <v>6624290</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6211,11 +6216,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>under ved i barrskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7944,10 +7944,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121394349</v>
+        <v>121394304</v>
       </c>
       <c r="B68" t="n">
-        <v>84300</v>
+        <v>98098</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7956,38 +7956,42 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3518</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>558419</v>
+        <v>558372</v>
       </c>
       <c r="R68" t="n">
-        <v>6624081</v>
+        <v>6624277</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8014,12 +8018,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8050,10 +8054,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121394356</v>
+        <v>121394349</v>
       </c>
       <c r="B69" t="n">
-        <v>91404</v>
+        <v>84300</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8062,20 +8066,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>757</v>
+        <v>3518</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Smal svampklubba</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8085,10 +8094,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>558364</v>
+        <v>558419</v>
       </c>
       <c r="R69" t="n">
-        <v>6624122</v>
+        <v>6624081</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8115,12 +8124,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8129,7 +8138,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8152,10 +8160,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121394304</v>
+        <v>121394356</v>
       </c>
       <c r="B70" t="n">
-        <v>98098</v>
+        <v>91404</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8164,42 +8172,33 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>558372</v>
+        <v>558364</v>
       </c>
       <c r="R70" t="n">
-        <v>6624277</v>
+        <v>6624122</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8226,12 +8225,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8240,6 +8239,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8262,10 +8262,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121394326</v>
+        <v>121394342</v>
       </c>
       <c r="B71" t="n">
-        <v>4769</v>
+        <v>74652</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8278,21 +8278,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100299</v>
+        <v>6426</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8302,10 +8302,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>558478</v>
+        <v>558435</v>
       </c>
       <c r="R71" t="n">
-        <v>6624257</v>
+        <v>6624227</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8368,7 +8368,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121394342</v>
+        <v>121394339</v>
       </c>
       <c r="B72" t="n">
         <v>74652</v>
@@ -8408,10 +8408,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>558435</v>
+        <v>558458</v>
       </c>
       <c r="R72" t="n">
-        <v>6624227</v>
+        <v>6624309</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8474,10 +8474,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121394339</v>
+        <v>121394326</v>
       </c>
       <c r="B73" t="n">
-        <v>74652</v>
+        <v>4769</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8490,21 +8490,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6426</v>
+        <v>100299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8514,10 +8514,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>558458</v>
+        <v>558478</v>
       </c>
       <c r="R73" t="n">
-        <v>6624309</v>
+        <v>6624257</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -2069,10 +2069,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121359465</v>
+        <v>121359466</v>
       </c>
       <c r="B13" t="n">
-        <v>91105</v>
+        <v>90684</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2081,20 +2081,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6040162</v>
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2104,10 +2109,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558460</v>
+        <v>558467</v>
       </c>
       <c r="R13" t="n">
-        <v>6624272</v>
+        <v>6624274</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2148,7 +2153,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2171,10 +2175,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121359457</v>
+        <v>121359467</v>
       </c>
       <c r="B14" t="n">
-        <v>92017</v>
+        <v>90936</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2187,21 +2191,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>1101</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2211,10 +2215,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558395</v>
+        <v>558464</v>
       </c>
       <c r="R14" t="n">
-        <v>6624316</v>
+        <v>6624306</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2277,10 +2281,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121359461</v>
+        <v>121359471</v>
       </c>
       <c r="B15" t="n">
-        <v>79225</v>
+        <v>95651</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2293,21 +2297,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2317,10 +2321,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558352</v>
+        <v>558521</v>
       </c>
       <c r="R15" t="n">
-        <v>6624226</v>
+        <v>6624319</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2383,10 +2387,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121359444</v>
+        <v>121359469</v>
       </c>
       <c r="B16" t="n">
-        <v>92022</v>
+        <v>90719</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2395,41 +2399,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558433</v>
+        <v>558491</v>
       </c>
       <c r="R16" t="n">
-        <v>6624286</v>
+        <v>6624274</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2470,7 +2471,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121359460</v>
+        <v>121359443</v>
       </c>
       <c r="B17" t="n">
-        <v>8435</v>
+        <v>90733</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2505,25 +2505,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558352</v>
+        <v>558441</v>
       </c>
       <c r="R17" t="n">
-        <v>6624226</v>
+        <v>6624265</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121359471</v>
+        <v>121359459</v>
       </c>
       <c r="B18" t="n">
-        <v>95645</v>
+        <v>79226</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2615,21 +2615,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558521</v>
+        <v>558364</v>
       </c>
       <c r="R18" t="n">
-        <v>6624319</v>
+        <v>6624216</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2705,10 +2705,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121359466</v>
+        <v>121359506</v>
       </c>
       <c r="B19" t="n">
-        <v>90678</v>
+        <v>8435</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2721,21 +2721,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558467</v>
+        <v>558352</v>
       </c>
       <c r="R19" t="n">
-        <v>6624274</v>
+        <v>6624128</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2811,10 +2811,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121359443</v>
+        <v>121359457</v>
       </c>
       <c r="B20" t="n">
-        <v>90727</v>
+        <v>92023</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2827,21 +2827,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>5449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2851,10 +2851,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558441</v>
+        <v>558395</v>
       </c>
       <c r="R20" t="n">
-        <v>6624265</v>
+        <v>6624316</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2917,10 +2917,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121359506</v>
+        <v>121359444</v>
       </c>
       <c r="B21" t="n">
-        <v>8435</v>
+        <v>92028</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2933,34 +2933,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558352</v>
+        <v>558433</v>
       </c>
       <c r="R21" t="n">
-        <v>6624128</v>
+        <v>6624286</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3001,6 +3004,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3023,10 +3027,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121359469</v>
+        <v>121359465</v>
       </c>
       <c r="B22" t="n">
-        <v>90713</v>
+        <v>91111</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3039,21 +3043,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3063,10 +3062,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558491</v>
+        <v>558460</v>
       </c>
       <c r="R22" t="n">
-        <v>6624274</v>
+        <v>6624272</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3107,6 +3106,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3129,10 +3129,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121359459</v>
+        <v>121359458</v>
       </c>
       <c r="B23" t="n">
-        <v>79225</v>
+        <v>92021</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3145,21 +3145,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>5448</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558364</v>
+        <v>558350</v>
       </c>
       <c r="R23" t="n">
-        <v>6624216</v>
+        <v>6624211</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121359467</v>
+        <v>121359460</v>
       </c>
       <c r="B24" t="n">
-        <v>90930</v>
+        <v>8435</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3247,25 +3247,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1101</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558464</v>
+        <v>558352</v>
       </c>
       <c r="R24" t="n">
-        <v>6624306</v>
+        <v>6624226</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3344,7 +3344,7 @@
         <v>121359462</v>
       </c>
       <c r="B25" t="n">
-        <v>90917</v>
+        <v>90923</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3447,10 +3447,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121359458</v>
+        <v>121359461</v>
       </c>
       <c r="B26" t="n">
-        <v>92015</v>
+        <v>79226</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3463,21 +3463,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5448</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558350</v>
+        <v>558352</v>
       </c>
       <c r="R26" t="n">
-        <v>6624211</v>
+        <v>6624226</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3556,7 +3556,7 @@
         <v>121394944</v>
       </c>
       <c r="B27" t="n">
-        <v>90678</v>
+        <v>90684</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3659,10 +3659,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121394932</v>
+        <v>121394943</v>
       </c>
       <c r="B28" t="n">
-        <v>91105</v>
+        <v>95651</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3675,16 +3675,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6040162</v>
+        <v>53</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3694,10 +3699,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558394</v>
+        <v>558390</v>
       </c>
       <c r="R28" t="n">
-        <v>6624091</v>
+        <v>6624295</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3738,7 +3743,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3761,10 +3765,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121394943</v>
+        <v>121394942</v>
       </c>
       <c r="B29" t="n">
-        <v>95645</v>
+        <v>95967</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3773,25 +3777,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>990</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3845,6 +3849,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3867,10 +3872,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121394934</v>
+        <v>121394945</v>
       </c>
       <c r="B30" t="n">
-        <v>95645</v>
+        <v>95651</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3907,10 +3912,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558377</v>
+        <v>558441</v>
       </c>
       <c r="R30" t="n">
-        <v>6624106</v>
+        <v>6624265</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3973,10 +3978,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121394549</v>
+        <v>121394933</v>
       </c>
       <c r="B31" t="n">
-        <v>92015</v>
+        <v>8435</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3985,25 +3990,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5448</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4013,10 +4018,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558468</v>
+        <v>558377</v>
       </c>
       <c r="R31" t="n">
-        <v>6624096</v>
+        <v>6624106</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4043,12 +4048,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4079,10 +4084,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121394933</v>
+        <v>121394932</v>
       </c>
       <c r="B32" t="n">
-        <v>8435</v>
+        <v>91111</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4091,25 +4096,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Mindre märgborre</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558377</v>
+        <v>558394</v>
       </c>
       <c r="R32" t="n">
-        <v>6624106</v>
+        <v>6624091</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4163,6 +4163,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4185,10 +4186,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121394942</v>
+        <v>121394549</v>
       </c>
       <c r="B33" t="n">
-        <v>95961</v>
+        <v>92021</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4197,25 +4198,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>990</v>
+        <v>5448</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4225,10 +4226,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558390</v>
+        <v>558468</v>
       </c>
       <c r="R33" t="n">
-        <v>6624295</v>
+        <v>6624096</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4255,12 +4256,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4269,7 +4270,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4292,10 +4292,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121394945</v>
+        <v>121394934</v>
       </c>
       <c r="B34" t="n">
-        <v>95645</v>
+        <v>95651</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4332,10 +4332,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558441</v>
+        <v>558377</v>
       </c>
       <c r="R34" t="n">
-        <v>6624265</v>
+        <v>6624106</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4398,10 +4398,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121394364</v>
+        <v>121394303</v>
       </c>
       <c r="B35" t="n">
-        <v>8435</v>
+        <v>98104</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4410,38 +4410,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558351</v>
+        <v>558385</v>
       </c>
       <c r="R35" t="n">
-        <v>6624213</v>
+        <v>6624276</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4468,12 +4472,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4504,10 +4508,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121394310</v>
+        <v>121394327</v>
       </c>
       <c r="B36" t="n">
-        <v>95645</v>
+        <v>90733</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4520,21 +4524,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>1204</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4544,10 +4548,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558437</v>
+        <v>558466</v>
       </c>
       <c r="R36" t="n">
-        <v>6624264</v>
+        <v>6624295</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4574,12 +4578,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4610,10 +4614,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121394355</v>
+        <v>121394349</v>
       </c>
       <c r="B37" t="n">
-        <v>92186</v>
+        <v>84304</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4622,41 +4626,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2079</v>
+        <v>3518</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558377</v>
+        <v>558419</v>
       </c>
       <c r="R37" t="n">
-        <v>6624159</v>
+        <v>6624081</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4683,12 +4684,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4697,24 +4698,8 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AL37" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>undersida av grov ved mot mark # tall</t>
-        </is>
-      </c>
-      <c r="AQ37" t="inlineStr">
-        <is>
-          <t>Ralf Lundmark</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4735,10 +4720,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121394315</v>
+        <v>121394355</v>
       </c>
       <c r="B38" t="n">
-        <v>91973</v>
+        <v>92192</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4747,38 +4732,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6055</v>
+        <v>2079</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558428</v>
+        <v>558377</v>
       </c>
       <c r="R38" t="n">
-        <v>6624044</v>
+        <v>6624159</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4805,12 +4793,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4819,8 +4807,24 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>undersida av grov ved mot mark # tall</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4841,7 +4845,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121394325</v>
+        <v>121394363</v>
       </c>
       <c r="B39" t="n">
         <v>5172</v>
@@ -4881,10 +4885,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558478</v>
+        <v>558367</v>
       </c>
       <c r="R39" t="n">
-        <v>6624257</v>
+        <v>6624219</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4911,12 +4915,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4947,10 +4951,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121394343</v>
+        <v>121394357</v>
       </c>
       <c r="B40" t="n">
-        <v>74652</v>
+        <v>95398</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4963,21 +4967,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6426</v>
+        <v>2869</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4987,10 +4991,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558405</v>
+        <v>558396</v>
       </c>
       <c r="R40" t="n">
-        <v>6624226</v>
+        <v>6624233</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5017,12 +5021,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5053,10 +5057,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121394303</v>
+        <v>121394354</v>
       </c>
       <c r="B41" t="n">
-        <v>98098</v>
+        <v>86298</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5065,42 +5069,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>3739</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558385</v>
+        <v>558390</v>
       </c>
       <c r="R41" t="n">
-        <v>6624276</v>
+        <v>6624037</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5127,12 +5127,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5163,10 +5163,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121394344</v>
+        <v>121394364</v>
       </c>
       <c r="B42" t="n">
-        <v>92001</v>
+        <v>8435</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5179,21 +5179,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4366</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5203,10 +5203,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558407</v>
+        <v>558351</v>
       </c>
       <c r="R42" t="n">
-        <v>6624166</v>
+        <v>6624213</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5233,12 +5233,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5269,10 +5269,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121394354</v>
+        <v>121394309</v>
       </c>
       <c r="B43" t="n">
-        <v>86294</v>
+        <v>95690</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5281,25 +5281,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3739</v>
+        <v>2590</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558390</v>
+        <v>558437</v>
       </c>
       <c r="R43" t="n">
-        <v>6624037</v>
+        <v>6624264</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5339,12 +5339,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5375,7 +5375,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121394351</v>
+        <v>121394324</v>
       </c>
       <c r="B44" t="n">
         <v>5192</v>
@@ -5415,10 +5415,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558363</v>
+        <v>558478</v>
       </c>
       <c r="R44" t="n">
-        <v>6624071</v>
+        <v>6624257</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5481,10 +5481,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121394363</v>
+        <v>121394333</v>
       </c>
       <c r="B45" t="n">
-        <v>5172</v>
+        <v>95651</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5493,25 +5493,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5521,10 +5521,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>558367</v>
+        <v>558528</v>
       </c>
       <c r="R45" t="n">
-        <v>6624219</v>
+        <v>6624316</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5551,12 +5551,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5587,10 +5587,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121394357</v>
+        <v>121394548</v>
       </c>
       <c r="B46" t="n">
-        <v>95392</v>
+        <v>92023</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5599,25 +5599,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2869</v>
+        <v>5449</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558396</v>
+        <v>558480</v>
       </c>
       <c r="R46" t="n">
-        <v>6624233</v>
+        <v>6624122</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5657,12 +5657,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5693,10 +5693,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121394324</v>
+        <v>121394350</v>
       </c>
       <c r="B47" t="n">
-        <v>5192</v>
+        <v>94769</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5709,21 +5709,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>105930</v>
+        <v>2170</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5733,10 +5733,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558478</v>
+        <v>558402</v>
       </c>
       <c r="R47" t="n">
-        <v>6624257</v>
+        <v>6624073</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5799,10 +5799,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121394321</v>
+        <v>121394326</v>
       </c>
       <c r="B48" t="n">
-        <v>95645</v>
+        <v>4769</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5811,25 +5811,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>558450</v>
+        <v>558478</v>
       </c>
       <c r="R48" t="n">
-        <v>6624202</v>
+        <v>6624257</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5905,10 +5905,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121394494</v>
+        <v>121394313</v>
       </c>
       <c r="B49" t="n">
-        <v>89414</v>
+        <v>91112</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5917,25 +5917,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6286</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Torrmusseron</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5945,10 +5940,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558369</v>
+        <v>558412</v>
       </c>
       <c r="R49" t="n">
-        <v>6624121</v>
+        <v>6624060</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5975,12 +5970,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5989,13 +5989,9 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>tallskog på finmorän</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6016,10 +6012,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121394272</v>
+        <v>121394322</v>
       </c>
       <c r="B50" t="n">
-        <v>58219</v>
+        <v>5192</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6032,16 +6028,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>208242</v>
+        <v>105930</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6049,26 +6045,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>558519</v>
+        <v>558492</v>
       </c>
       <c r="R50" t="n">
-        <v>6624313</v>
+        <v>6624223</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6095,17 +6082,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>under ved i barrskog</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6139,7 +6121,7 @@
         <v>121394270</v>
       </c>
       <c r="B51" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6246,10 +6228,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121394327</v>
+        <v>121394325</v>
       </c>
       <c r="B52" t="n">
-        <v>90727</v>
+        <v>5172</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6258,25 +6240,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1204</v>
+        <v>100526</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6286,10 +6268,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>558466</v>
+        <v>558478</v>
       </c>
       <c r="R52" t="n">
-        <v>6624295</v>
+        <v>6624257</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6352,10 +6334,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121394309</v>
+        <v>121394351</v>
       </c>
       <c r="B53" t="n">
-        <v>95684</v>
+        <v>5192</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6368,21 +6350,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2590</v>
+        <v>105930</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6392,10 +6374,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>558437</v>
+        <v>558363</v>
       </c>
       <c r="R53" t="n">
-        <v>6624264</v>
+        <v>6624071</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6422,12 +6404,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6458,10 +6440,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121394313</v>
+        <v>121394356</v>
       </c>
       <c r="B54" t="n">
-        <v>91106</v>
+        <v>91410</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6474,16 +6456,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6040186</v>
+        <v>757</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6493,10 +6475,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>558412</v>
+        <v>558364</v>
       </c>
       <c r="R54" t="n">
-        <v>6624060</v>
+        <v>6624122</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6523,17 +6505,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6565,10 +6542,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121394333</v>
+        <v>121394339</v>
       </c>
       <c r="B55" t="n">
-        <v>95645</v>
+        <v>74653</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6577,25 +6554,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6605,10 +6582,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>558528</v>
+        <v>558458</v>
       </c>
       <c r="R55" t="n">
-        <v>6624316</v>
+        <v>6624309</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6671,10 +6648,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121394348</v>
+        <v>121394342</v>
       </c>
       <c r="B56" t="n">
-        <v>92020</v>
+        <v>74653</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6683,25 +6660,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1968</v>
+        <v>6426</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6711,10 +6688,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>558437</v>
+        <v>558435</v>
       </c>
       <c r="R56" t="n">
-        <v>6624152</v>
+        <v>6624227</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6777,10 +6754,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121394350</v>
+        <v>121394344</v>
       </c>
       <c r="B57" t="n">
-        <v>94763</v>
+        <v>92007</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6793,21 +6770,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2170</v>
+        <v>4366</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6817,10 +6794,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>558402</v>
+        <v>558407</v>
       </c>
       <c r="R57" t="n">
-        <v>6624073</v>
+        <v>6624166</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6883,10 +6860,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121394319</v>
+        <v>121394348</v>
       </c>
       <c r="B58" t="n">
-        <v>8435</v>
+        <v>92026</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6895,25 +6872,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>1968</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6923,10 +6900,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>558461</v>
+        <v>558437</v>
       </c>
       <c r="R58" t="n">
-        <v>6624164</v>
+        <v>6624152</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6953,12 +6930,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6989,10 +6966,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121394365</v>
+        <v>121394352</v>
       </c>
       <c r="B59" t="n">
-        <v>91105</v>
+        <v>5172</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7001,20 +6978,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6040162</v>
+        <v>100526</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7024,10 +7006,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>558351</v>
+        <v>558363</v>
       </c>
       <c r="R59" t="n">
-        <v>6624213</v>
+        <v>6624071</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7054,12 +7036,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7068,7 +7050,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7091,10 +7072,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121394323</v>
+        <v>121394315</v>
       </c>
       <c r="B60" t="n">
-        <v>5172</v>
+        <v>91979</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7103,25 +7084,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100526</v>
+        <v>6055</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7131,10 +7112,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>558492</v>
+        <v>558428</v>
       </c>
       <c r="R60" t="n">
-        <v>6624223</v>
+        <v>6624044</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7161,12 +7142,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7197,10 +7178,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121394548</v>
+        <v>121394320</v>
       </c>
       <c r="B61" t="n">
-        <v>92017</v>
+        <v>89768</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7213,21 +7194,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5449</v>
+        <v>1962</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7237,10 +7218,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>558480</v>
+        <v>558465</v>
       </c>
       <c r="R61" t="n">
-        <v>6624122</v>
+        <v>6624192</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7267,12 +7248,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7303,10 +7284,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121394322</v>
+        <v>121394359</v>
       </c>
       <c r="B62" t="n">
-        <v>5192</v>
+        <v>74653</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7319,21 +7300,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7343,10 +7324,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>558492</v>
+        <v>558414</v>
       </c>
       <c r="R62" t="n">
-        <v>6624223</v>
+        <v>6624238</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7373,12 +7354,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7409,10 +7390,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121394314</v>
+        <v>121394353</v>
       </c>
       <c r="B63" t="n">
-        <v>91105</v>
+        <v>4769</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7421,20 +7402,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6040162</v>
+        <v>100299</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7444,10 +7430,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>558428</v>
+        <v>558363</v>
       </c>
       <c r="R63" t="n">
-        <v>6624048</v>
+        <v>6624071</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7482,18 +7468,12 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7516,10 +7496,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121394359</v>
+        <v>121394314</v>
       </c>
       <c r="B64" t="n">
-        <v>74652</v>
+        <v>91111</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7528,25 +7508,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6426</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Kattfotslav</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7556,10 +7531,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>558414</v>
+        <v>558428</v>
       </c>
       <c r="R64" t="n">
-        <v>6624238</v>
+        <v>6624048</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7586,12 +7561,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7600,6 +7580,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7622,10 +7603,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121394352</v>
+        <v>121394343</v>
       </c>
       <c r="B65" t="n">
-        <v>5172</v>
+        <v>74653</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7638,21 +7619,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7662,10 +7643,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>558363</v>
+        <v>558405</v>
       </c>
       <c r="R65" t="n">
-        <v>6624071</v>
+        <v>6624226</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7728,10 +7709,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121394353</v>
+        <v>121394272</v>
       </c>
       <c r="B66" t="n">
-        <v>4769</v>
+        <v>58220</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7744,34 +7725,43 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100299</v>
+        <v>208242</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>558363</v>
+        <v>558519</v>
       </c>
       <c r="R66" t="n">
-        <v>6624071</v>
+        <v>6624313</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7798,12 +7788,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>under ved i barrskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7834,10 +7829,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121394305</v>
+        <v>121394345</v>
       </c>
       <c r="B67" t="n">
-        <v>98098</v>
+        <v>97052</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7846,42 +7841,34 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>221944</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>558420</v>
+        <v>558386</v>
       </c>
       <c r="R67" t="n">
-        <v>6624193</v>
+        <v>6624222</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7908,12 +7895,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7922,6 +7909,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7944,10 +7932,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121394304</v>
+        <v>121394305</v>
       </c>
       <c r="B68" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7979,7 +7967,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7988,10 +7976,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>558372</v>
+        <v>558420</v>
       </c>
       <c r="R68" t="n">
-        <v>6624277</v>
+        <v>6624193</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8054,10 +8042,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121394349</v>
+        <v>121394304</v>
       </c>
       <c r="B69" t="n">
-        <v>84300</v>
+        <v>98104</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8066,38 +8054,42 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3518</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>558419</v>
+        <v>558372</v>
       </c>
       <c r="R69" t="n">
-        <v>6624081</v>
+        <v>6624277</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8124,12 +8116,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8160,10 +8152,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121394356</v>
+        <v>121394306</v>
       </c>
       <c r="B70" t="n">
-        <v>91404</v>
+        <v>98104</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8172,33 +8164,42 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>757</v>
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>558364</v>
+        <v>558437</v>
       </c>
       <c r="R70" t="n">
-        <v>6624122</v>
+        <v>6624213</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8225,12 +8226,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8239,7 +8240,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8262,10 +8262,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121394342</v>
+        <v>121394323</v>
       </c>
       <c r="B71" t="n">
-        <v>74652</v>
+        <v>5172</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8278,21 +8278,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6426</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8302,10 +8302,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>558435</v>
+        <v>558492</v>
       </c>
       <c r="R71" t="n">
-        <v>6624227</v>
+        <v>6624223</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8368,10 +8368,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121394339</v>
+        <v>121394321</v>
       </c>
       <c r="B72" t="n">
-        <v>74652</v>
+        <v>95651</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8380,25 +8380,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8408,10 +8408,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>558458</v>
+        <v>558450</v>
       </c>
       <c r="R72" t="n">
-        <v>6624309</v>
+        <v>6624202</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8438,12 +8438,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8474,10 +8474,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121394326</v>
+        <v>121394365</v>
       </c>
       <c r="B73" t="n">
-        <v>4769</v>
+        <v>91111</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8486,25 +8486,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100299</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Thomsons trägnagare</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8514,10 +8509,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>558478</v>
+        <v>558351</v>
       </c>
       <c r="R73" t="n">
-        <v>6624257</v>
+        <v>6624213</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8544,12 +8539,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8558,6 +8553,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8580,10 +8576,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121394306</v>
+        <v>121394319</v>
       </c>
       <c r="B74" t="n">
-        <v>98098</v>
+        <v>8435</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8592,42 +8588,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>558437</v>
+        <v>558461</v>
       </c>
       <c r="R74" t="n">
-        <v>6624213</v>
+        <v>6624164</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8654,12 +8646,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8690,10 +8682,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121394320</v>
+        <v>121394494</v>
       </c>
       <c r="B75" t="n">
-        <v>89764</v>
+        <v>89418</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8702,25 +8694,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1962</v>
+        <v>6286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8730,10 +8722,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>558465</v>
+        <v>558369</v>
       </c>
       <c r="R75" t="n">
-        <v>6624192</v>
+        <v>6624121</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8776,6 +8768,11 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>tallskog på finmorän</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -8796,10 +8793,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121394345</v>
+        <v>121394310</v>
       </c>
       <c r="B76" t="n">
-        <v>97046</v>
+        <v>95651</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8808,23 +8805,27 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221944</v>
+        <v>53</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8832,10 +8833,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>558386</v>
+        <v>558437</v>
       </c>
       <c r="R76" t="n">
-        <v>6624222</v>
+        <v>6624264</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8862,12 +8863,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8876,7 +8877,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -4186,10 +4186,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121394549</v>
+        <v>121394934</v>
       </c>
       <c r="B33" t="n">
-        <v>92021</v>
+        <v>95651</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4202,21 +4202,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5448</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558468</v>
+        <v>558377</v>
       </c>
       <c r="R33" t="n">
-        <v>6624096</v>
+        <v>6624106</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4256,12 +4256,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4292,10 +4292,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121394934</v>
+        <v>121394549</v>
       </c>
       <c r="B34" t="n">
-        <v>95651</v>
+        <v>92021</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4308,21 +4308,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>5448</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4332,10 +4332,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558377</v>
+        <v>558468</v>
       </c>
       <c r="R34" t="n">
-        <v>6624106</v>
+        <v>6624096</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4508,10 +4508,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121394327</v>
+        <v>121394349</v>
       </c>
       <c r="B36" t="n">
-        <v>90733</v>
+        <v>84304</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4520,25 +4520,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1204</v>
+        <v>3518</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4548,10 +4548,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558466</v>
+        <v>558419</v>
       </c>
       <c r="R36" t="n">
-        <v>6624295</v>
+        <v>6624081</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4614,10 +4614,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121394349</v>
+        <v>121394327</v>
       </c>
       <c r="B37" t="n">
-        <v>84304</v>
+        <v>90733</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4626,25 +4626,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3518</v>
+        <v>1204</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558419</v>
+        <v>558466</v>
       </c>
       <c r="R37" t="n">
-        <v>6624081</v>
+        <v>6624295</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -6754,10 +6754,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121394344</v>
+        <v>121394352</v>
       </c>
       <c r="B57" t="n">
-        <v>92007</v>
+        <v>5172</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6770,21 +6770,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4366</v>
+        <v>100526</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6794,10 +6794,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>558407</v>
+        <v>558363</v>
       </c>
       <c r="R57" t="n">
-        <v>6624166</v>
+        <v>6624071</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6860,10 +6860,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121394348</v>
+        <v>121394344</v>
       </c>
       <c r="B58" t="n">
-        <v>92026</v>
+        <v>92007</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6872,25 +6872,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1968</v>
+        <v>4366</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6900,10 +6900,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>558437</v>
+        <v>558407</v>
       </c>
       <c r="R58" t="n">
-        <v>6624152</v>
+        <v>6624166</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6966,10 +6966,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121394352</v>
+        <v>121394348</v>
       </c>
       <c r="B59" t="n">
-        <v>5172</v>
+        <v>92026</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6978,25 +6978,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100526</v>
+        <v>1968</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7006,10 +7006,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>558363</v>
+        <v>558437</v>
       </c>
       <c r="R59" t="n">
-        <v>6624071</v>
+        <v>6624152</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7709,10 +7709,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121394272</v>
+        <v>121394345</v>
       </c>
       <c r="B66" t="n">
-        <v>58220</v>
+        <v>97052</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7725,43 +7725,30 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>208242</v>
+        <v>221944</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>558519</v>
+        <v>558386</v>
       </c>
       <c r="R66" t="n">
-        <v>6624313</v>
+        <v>6624222</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7788,17 +7775,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>under ved i barrskog</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7807,6 +7789,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7829,10 +7812,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121394345</v>
+        <v>121394272</v>
       </c>
       <c r="B67" t="n">
-        <v>97052</v>
+        <v>58220</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7845,30 +7828,43 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221944</v>
+        <v>208242</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>558386</v>
+        <v>558519</v>
       </c>
       <c r="R67" t="n">
-        <v>6624222</v>
+        <v>6624313</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7895,12 +7891,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>under ved i barrskog</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7909,7 +7910,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -2069,10 +2069,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121359466</v>
+        <v>121359457</v>
       </c>
       <c r="B13" t="n">
-        <v>90684</v>
+        <v>92024</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2081,25 +2081,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2109,10 +2109,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558467</v>
+        <v>558395</v>
       </c>
       <c r="R13" t="n">
-        <v>6624274</v>
+        <v>6624316</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121359467</v>
+        <v>121359471</v>
       </c>
       <c r="B14" t="n">
-        <v>90936</v>
+        <v>95652</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1101</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558464</v>
+        <v>558521</v>
       </c>
       <c r="R14" t="n">
-        <v>6624306</v>
+        <v>6624319</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2281,10 +2281,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121359471</v>
+        <v>121359461</v>
       </c>
       <c r="B15" t="n">
-        <v>95651</v>
+        <v>79227</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2297,21 +2297,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558521</v>
+        <v>558352</v>
       </c>
       <c r="R15" t="n">
-        <v>6624319</v>
+        <v>6624226</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121359469</v>
+        <v>121359458</v>
       </c>
       <c r="B16" t="n">
-        <v>90719</v>
+        <v>92022</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2403,21 +2403,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5448</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558491</v>
+        <v>558350</v>
       </c>
       <c r="R16" t="n">
-        <v>6624274</v>
+        <v>6624211</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2496,7 +2496,7 @@
         <v>121359443</v>
       </c>
       <c r="B17" t="n">
-        <v>90733</v>
+        <v>90734</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121359459</v>
+        <v>121359469</v>
       </c>
       <c r="B18" t="n">
-        <v>79226</v>
+        <v>90720</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2615,21 +2615,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558364</v>
+        <v>558491</v>
       </c>
       <c r="R18" t="n">
-        <v>6624216</v>
+        <v>6624274</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2811,10 +2811,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121359457</v>
+        <v>121359462</v>
       </c>
       <c r="B20" t="n">
-        <v>92023</v>
+        <v>90924</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2823,25 +2823,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>1106</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2851,10 +2851,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558395</v>
+        <v>558376</v>
       </c>
       <c r="R20" t="n">
-        <v>6624316</v>
+        <v>6624261</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2917,10 +2917,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121359444</v>
+        <v>121359466</v>
       </c>
       <c r="B21" t="n">
-        <v>92028</v>
+        <v>90685</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2933,37 +2933,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558433</v>
+        <v>558467</v>
       </c>
       <c r="R21" t="n">
-        <v>6624286</v>
+        <v>6624274</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3004,7 +3001,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3030,7 +3026,7 @@
         <v>121359465</v>
       </c>
       <c r="B22" t="n">
-        <v>91111</v>
+        <v>91112</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3129,10 +3125,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121359458</v>
+        <v>121359467</v>
       </c>
       <c r="B23" t="n">
-        <v>92021</v>
+        <v>90937</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3145,21 +3141,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5448</v>
+        <v>1101</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3169,10 +3165,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558350</v>
+        <v>558464</v>
       </c>
       <c r="R23" t="n">
-        <v>6624211</v>
+        <v>6624306</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3235,10 +3231,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121359460</v>
+        <v>121359444</v>
       </c>
       <c r="B24" t="n">
-        <v>8435</v>
+        <v>92029</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3251,34 +3247,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558352</v>
+        <v>558433</v>
       </c>
       <c r="R24" t="n">
-        <v>6624226</v>
+        <v>6624286</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3319,6 +3318,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3341,10 +3341,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121359462</v>
+        <v>121359460</v>
       </c>
       <c r="B25" t="n">
-        <v>90923</v>
+        <v>8435</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3353,25 +3353,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1106</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558376</v>
+        <v>558352</v>
       </c>
       <c r="R25" t="n">
-        <v>6624261</v>
+        <v>6624226</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3447,10 +3447,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121359461</v>
+        <v>121359459</v>
       </c>
       <c r="B26" t="n">
-        <v>79226</v>
+        <v>79227</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558352</v>
+        <v>558364</v>
       </c>
       <c r="R26" t="n">
-        <v>6624226</v>
+        <v>6624216</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121394944</v>
+        <v>121394549</v>
       </c>
       <c r="B27" t="n">
-        <v>90684</v>
+        <v>92022</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3565,25 +3565,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>5448</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558441</v>
+        <v>558468</v>
       </c>
       <c r="R27" t="n">
-        <v>6624265</v>
+        <v>6624096</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3623,12 +3623,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3659,10 +3659,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121394943</v>
+        <v>121394933</v>
       </c>
       <c r="B28" t="n">
-        <v>95651</v>
+        <v>8435</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3671,25 +3671,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3699,10 +3699,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558390</v>
+        <v>558377</v>
       </c>
       <c r="R28" t="n">
-        <v>6624295</v>
+        <v>6624106</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3768,7 +3768,7 @@
         <v>121394942</v>
       </c>
       <c r="B29" t="n">
-        <v>95967</v>
+        <v>95968</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3872,10 +3872,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121394945</v>
+        <v>121394932</v>
       </c>
       <c r="B30" t="n">
-        <v>95651</v>
+        <v>91112</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3888,21 +3888,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3912,10 +3907,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558441</v>
+        <v>558394</v>
       </c>
       <c r="R30" t="n">
-        <v>6624265</v>
+        <v>6624091</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3956,6 +3951,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3978,10 +3974,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121394933</v>
+        <v>121394945</v>
       </c>
       <c r="B31" t="n">
-        <v>8435</v>
+        <v>95652</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3990,25 +3986,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4018,10 +4014,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558377</v>
+        <v>558441</v>
       </c>
       <c r="R31" t="n">
-        <v>6624106</v>
+        <v>6624265</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4084,10 +4080,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121394932</v>
+        <v>121394934</v>
       </c>
       <c r="B32" t="n">
-        <v>91111</v>
+        <v>95652</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4100,16 +4096,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6040162</v>
+        <v>53</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4119,10 +4120,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558394</v>
+        <v>558377</v>
       </c>
       <c r="R32" t="n">
-        <v>6624091</v>
+        <v>6624106</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4163,7 +4164,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4186,10 +4186,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121394934</v>
+        <v>121394943</v>
       </c>
       <c r="B33" t="n">
-        <v>95651</v>
+        <v>95652</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558377</v>
+        <v>558390</v>
       </c>
       <c r="R33" t="n">
-        <v>6624106</v>
+        <v>6624295</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4292,10 +4292,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121394549</v>
+        <v>121394944</v>
       </c>
       <c r="B34" t="n">
-        <v>92021</v>
+        <v>90685</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4304,25 +4304,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5448</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4332,10 +4332,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558468</v>
+        <v>558441</v>
       </c>
       <c r="R34" t="n">
-        <v>6624096</v>
+        <v>6624265</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4398,10 +4398,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121394303</v>
+        <v>121394355</v>
       </c>
       <c r="B35" t="n">
-        <v>98104</v>
+        <v>92193</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4410,42 +4410,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558385</v>
+        <v>558377</v>
       </c>
       <c r="R35" t="n">
-        <v>6624276</v>
+        <v>6624159</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4472,12 +4471,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4486,8 +4485,24 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>undersida av grov ved mot mark # tall</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4508,10 +4523,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121394349</v>
+        <v>121394319</v>
       </c>
       <c r="B36" t="n">
-        <v>84304</v>
+        <v>8435</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4524,21 +4539,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3518</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4548,10 +4563,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558419</v>
+        <v>558461</v>
       </c>
       <c r="R36" t="n">
-        <v>6624081</v>
+        <v>6624164</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4578,12 +4593,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4614,10 +4629,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121394327</v>
+        <v>121394364</v>
       </c>
       <c r="B37" t="n">
-        <v>90733</v>
+        <v>8435</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4626,25 +4641,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1204</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4654,10 +4669,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558466</v>
+        <v>558351</v>
       </c>
       <c r="R37" t="n">
-        <v>6624295</v>
+        <v>6624213</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4684,12 +4699,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4720,10 +4735,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121394355</v>
+        <v>121394321</v>
       </c>
       <c r="B38" t="n">
-        <v>92192</v>
+        <v>95652</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4736,37 +4751,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2079</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558377</v>
+        <v>558450</v>
       </c>
       <c r="R38" t="n">
-        <v>6624159</v>
+        <v>6624202</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4793,12 +4805,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4807,24 +4819,8 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AL38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>undersida av grov ved mot mark # tall</t>
-        </is>
-      </c>
-      <c r="AQ38" t="inlineStr">
-        <is>
-          <t>Ralf Lundmark</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4845,7 +4841,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121394363</v>
+        <v>121394323</v>
       </c>
       <c r="B39" t="n">
         <v>5172</v>
@@ -4885,10 +4881,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558367</v>
+        <v>558492</v>
       </c>
       <c r="R39" t="n">
-        <v>6624219</v>
+        <v>6624223</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4915,12 +4911,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4951,10 +4947,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121394357</v>
+        <v>121394272</v>
       </c>
       <c r="B40" t="n">
-        <v>95398</v>
+        <v>58221</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4967,34 +4963,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2869</v>
+        <v>208242</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558396</v>
+        <v>558519</v>
       </c>
       <c r="R40" t="n">
-        <v>6624233</v>
+        <v>6624313</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5021,12 +5026,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>under ved i barrskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5057,10 +5067,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121394354</v>
+        <v>121394339</v>
       </c>
       <c r="B41" t="n">
-        <v>86298</v>
+        <v>74654</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5069,25 +5079,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3739</v>
+        <v>6426</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5097,10 +5107,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558390</v>
+        <v>558458</v>
       </c>
       <c r="R41" t="n">
-        <v>6624037</v>
+        <v>6624309</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5163,10 +5173,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121394364</v>
+        <v>121394357</v>
       </c>
       <c r="B42" t="n">
-        <v>8435</v>
+        <v>95399</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5179,21 +5189,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>2869</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5203,10 +5213,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558351</v>
+        <v>558396</v>
       </c>
       <c r="R42" t="n">
-        <v>6624213</v>
+        <v>6624233</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5269,10 +5279,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121394309</v>
+        <v>121394313</v>
       </c>
       <c r="B43" t="n">
-        <v>95690</v>
+        <v>91113</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5281,25 +5291,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2590</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Kornknutmossa</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5309,10 +5314,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558437</v>
+        <v>558412</v>
       </c>
       <c r="R43" t="n">
-        <v>6624264</v>
+        <v>6624060</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5339,12 +5344,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5353,6 +5363,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5375,10 +5386,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121394324</v>
+        <v>121394310</v>
       </c>
       <c r="B44" t="n">
-        <v>5192</v>
+        <v>95652</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5387,25 +5398,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5415,10 +5426,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558478</v>
+        <v>558437</v>
       </c>
       <c r="R44" t="n">
-        <v>6624257</v>
+        <v>6624264</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5445,12 +5456,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5481,10 +5492,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121394333</v>
+        <v>121394356</v>
       </c>
       <c r="B45" t="n">
-        <v>95651</v>
+        <v>91411</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5497,21 +5508,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5521,10 +5527,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>558528</v>
+        <v>558364</v>
       </c>
       <c r="R45" t="n">
-        <v>6624316</v>
+        <v>6624122</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5551,12 +5557,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5565,6 +5571,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5587,10 +5594,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121394548</v>
+        <v>121394359</v>
       </c>
       <c r="B46" t="n">
-        <v>92023</v>
+        <v>74654</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5599,25 +5606,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5449</v>
+        <v>6426</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5627,10 +5634,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558480</v>
+        <v>558414</v>
       </c>
       <c r="R46" t="n">
-        <v>6624122</v>
+        <v>6624238</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5657,12 +5664,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5693,10 +5700,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121394350</v>
+        <v>121394305</v>
       </c>
       <c r="B47" t="n">
-        <v>94769</v>
+        <v>98105</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5705,38 +5712,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558402</v>
+        <v>558420</v>
       </c>
       <c r="R47" t="n">
-        <v>6624073</v>
+        <v>6624193</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5763,12 +5774,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5799,10 +5810,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121394326</v>
+        <v>121394333</v>
       </c>
       <c r="B48" t="n">
-        <v>4769</v>
+        <v>95652</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5811,25 +5822,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100299</v>
+        <v>53</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5839,10 +5850,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>558478</v>
+        <v>558528</v>
       </c>
       <c r="R48" t="n">
-        <v>6624257</v>
+        <v>6624316</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5905,10 +5916,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121394313</v>
+        <v>121394320</v>
       </c>
       <c r="B49" t="n">
-        <v>91112</v>
+        <v>89769</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5921,16 +5932,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6040186</v>
+        <v>1962</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5940,10 +5956,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558412</v>
+        <v>558465</v>
       </c>
       <c r="R49" t="n">
-        <v>6624060</v>
+        <v>6624192</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5970,17 +5986,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5989,7 +6000,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6012,7 +6022,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121394322</v>
+        <v>121394351</v>
       </c>
       <c r="B50" t="n">
         <v>5192</v>
@@ -6052,10 +6062,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>558492</v>
+        <v>558363</v>
       </c>
       <c r="R50" t="n">
-        <v>6624223</v>
+        <v>6624071</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6118,10 +6128,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121394270</v>
+        <v>121394304</v>
       </c>
       <c r="B51" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6153,7 +6163,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>400</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6162,10 +6172,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>558522</v>
+        <v>558372</v>
       </c>
       <c r="R51" t="n">
-        <v>6624290</v>
+        <v>6624277</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6228,10 +6238,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121394325</v>
+        <v>121394306</v>
       </c>
       <c r="B52" t="n">
-        <v>5172</v>
+        <v>98105</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6240,38 +6250,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>558478</v>
+        <v>558437</v>
       </c>
       <c r="R52" t="n">
-        <v>6624257</v>
+        <v>6624213</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6298,12 +6312,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6334,10 +6348,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121394351</v>
+        <v>121394327</v>
       </c>
       <c r="B53" t="n">
-        <v>5192</v>
+        <v>90734</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6346,25 +6360,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>105930</v>
+        <v>1204</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6374,10 +6388,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>558363</v>
+        <v>558466</v>
       </c>
       <c r="R53" t="n">
-        <v>6624071</v>
+        <v>6624295</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6440,10 +6454,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121394356</v>
+        <v>121394352</v>
       </c>
       <c r="B54" t="n">
-        <v>91410</v>
+        <v>5172</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6452,20 +6466,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>757</v>
+        <v>100526</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6475,10 +6494,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>558364</v>
+        <v>558363</v>
       </c>
       <c r="R54" t="n">
-        <v>6624122</v>
+        <v>6624071</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6505,12 +6524,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6519,7 +6538,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6542,10 +6560,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121394339</v>
+        <v>121394354</v>
       </c>
       <c r="B55" t="n">
-        <v>74653</v>
+        <v>86299</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6554,25 +6572,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6426</v>
+        <v>3739</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6582,10 +6600,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>558458</v>
+        <v>558390</v>
       </c>
       <c r="R55" t="n">
-        <v>6624309</v>
+        <v>6624037</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6651,7 +6669,7 @@
         <v>121394342</v>
       </c>
       <c r="B56" t="n">
-        <v>74653</v>
+        <v>74654</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6754,10 +6772,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121394352</v>
+        <v>121394322</v>
       </c>
       <c r="B57" t="n">
-        <v>5172</v>
+        <v>5192</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6770,21 +6788,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6794,10 +6812,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>558363</v>
+        <v>558492</v>
       </c>
       <c r="R57" t="n">
-        <v>6624071</v>
+        <v>6624223</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6860,10 +6878,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121394344</v>
+        <v>121394363</v>
       </c>
       <c r="B58" t="n">
-        <v>92007</v>
+        <v>5172</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6876,21 +6894,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4366</v>
+        <v>100526</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6900,10 +6918,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>558407</v>
+        <v>558367</v>
       </c>
       <c r="R58" t="n">
-        <v>6624166</v>
+        <v>6624219</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6930,12 +6948,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6966,10 +6984,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121394348</v>
+        <v>121394315</v>
       </c>
       <c r="B59" t="n">
-        <v>92026</v>
+        <v>91980</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6978,25 +6996,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1968</v>
+        <v>6055</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7006,10 +7024,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>558437</v>
+        <v>558428</v>
       </c>
       <c r="R59" t="n">
-        <v>6624152</v>
+        <v>6624044</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7036,12 +7054,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7072,10 +7090,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121394315</v>
+        <v>121394350</v>
       </c>
       <c r="B60" t="n">
-        <v>91979</v>
+        <v>94770</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7084,25 +7102,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6055</v>
+        <v>2170</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7112,10 +7130,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>558428</v>
+        <v>558402</v>
       </c>
       <c r="R60" t="n">
-        <v>6624044</v>
+        <v>6624073</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7142,12 +7160,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7178,10 +7196,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121394320</v>
+        <v>121394348</v>
       </c>
       <c r="B61" t="n">
-        <v>89768</v>
+        <v>92027</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7194,21 +7212,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1962</v>
+        <v>1968</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7218,10 +7236,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>558465</v>
+        <v>558437</v>
       </c>
       <c r="R61" t="n">
-        <v>6624192</v>
+        <v>6624152</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7248,12 +7266,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7284,10 +7302,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121394359</v>
+        <v>121394344</v>
       </c>
       <c r="B62" t="n">
-        <v>74653</v>
+        <v>92008</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7300,21 +7318,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6426</v>
+        <v>4366</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7324,10 +7342,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>558414</v>
+        <v>558407</v>
       </c>
       <c r="R62" t="n">
-        <v>6624238</v>
+        <v>6624166</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7354,12 +7372,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7390,10 +7408,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121394353</v>
+        <v>121394309</v>
       </c>
       <c r="B63" t="n">
-        <v>4769</v>
+        <v>95691</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7406,21 +7424,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100299</v>
+        <v>2590</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7430,10 +7448,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>558363</v>
+        <v>558437</v>
       </c>
       <c r="R63" t="n">
-        <v>6624071</v>
+        <v>6624264</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7460,12 +7478,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7496,10 +7514,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121394314</v>
+        <v>121394494</v>
       </c>
       <c r="B64" t="n">
-        <v>91111</v>
+        <v>89419</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7508,20 +7526,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6040162</v>
+        <v>6286</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7531,10 +7554,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>558428</v>
+        <v>558369</v>
       </c>
       <c r="R64" t="n">
-        <v>6624048</v>
+        <v>6624121</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7561,17 +7584,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7580,9 +7598,13 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>tallskog på finmorän</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7603,10 +7625,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121394343</v>
+        <v>121394353</v>
       </c>
       <c r="B65" t="n">
-        <v>74653</v>
+        <v>4769</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7619,21 +7641,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6426</v>
+        <v>100299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7643,10 +7665,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>558405</v>
+        <v>558363</v>
       </c>
       <c r="R65" t="n">
-        <v>6624226</v>
+        <v>6624071</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7709,10 +7731,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121394345</v>
+        <v>121394548</v>
       </c>
       <c r="B66" t="n">
-        <v>97052</v>
+        <v>92024</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7721,23 +7743,27 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221944</v>
+        <v>5449</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7745,10 +7771,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>558386</v>
+        <v>558480</v>
       </c>
       <c r="R66" t="n">
-        <v>6624222</v>
+        <v>6624122</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7775,12 +7801,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7789,7 +7815,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7812,10 +7837,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121394272</v>
+        <v>121394345</v>
       </c>
       <c r="B67" t="n">
-        <v>58220</v>
+        <v>97053</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7828,43 +7853,30 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>208242</v>
+        <v>221944</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>558519</v>
+        <v>558386</v>
       </c>
       <c r="R67" t="n">
-        <v>6624313</v>
+        <v>6624222</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7891,17 +7903,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>under ved i barrskog</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7910,6 +7917,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7932,10 +7940,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121394305</v>
+        <v>121394303</v>
       </c>
       <c r="B68" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7967,7 +7975,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7976,10 +7984,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>558420</v>
+        <v>558385</v>
       </c>
       <c r="R68" t="n">
-        <v>6624193</v>
+        <v>6624276</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8042,10 +8050,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121394304</v>
+        <v>121394314</v>
       </c>
       <c r="B69" t="n">
-        <v>98104</v>
+        <v>91112</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8054,42 +8062,33 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>558372</v>
+        <v>558428</v>
       </c>
       <c r="R69" t="n">
-        <v>6624277</v>
+        <v>6624048</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8116,12 +8115,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8130,6 +8134,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8152,10 +8157,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121394306</v>
+        <v>121394349</v>
       </c>
       <c r="B70" t="n">
-        <v>98104</v>
+        <v>84305</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8164,42 +8169,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>3518</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>558437</v>
+        <v>558419</v>
       </c>
       <c r="R70" t="n">
-        <v>6624213</v>
+        <v>6624081</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8226,12 +8227,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8262,10 +8263,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121394323</v>
+        <v>121394343</v>
       </c>
       <c r="B71" t="n">
-        <v>5172</v>
+        <v>74654</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8278,21 +8279,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8302,10 +8303,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>558492</v>
+        <v>558405</v>
       </c>
       <c r="R71" t="n">
-        <v>6624223</v>
+        <v>6624226</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8368,10 +8369,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121394321</v>
+        <v>121394270</v>
       </c>
       <c r="B72" t="n">
-        <v>95651</v>
+        <v>98105</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8380,38 +8381,42 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>558450</v>
+        <v>558522</v>
       </c>
       <c r="R72" t="n">
-        <v>6624202</v>
+        <v>6624290</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8438,12 +8443,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8474,10 +8479,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121394365</v>
+        <v>121394324</v>
       </c>
       <c r="B73" t="n">
-        <v>91111</v>
+        <v>5192</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8486,20 +8491,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6040162</v>
+        <v>105930</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8509,10 +8519,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>558351</v>
+        <v>558478</v>
       </c>
       <c r="R73" t="n">
-        <v>6624213</v>
+        <v>6624257</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8539,12 +8549,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8553,7 +8563,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8576,10 +8585,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121394319</v>
+        <v>121394326</v>
       </c>
       <c r="B74" t="n">
-        <v>8435</v>
+        <v>4769</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8592,21 +8601,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>100299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8616,10 +8625,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>558461</v>
+        <v>558478</v>
       </c>
       <c r="R74" t="n">
-        <v>6624164</v>
+        <v>6624257</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8646,12 +8655,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8682,10 +8691,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121394494</v>
+        <v>121394325</v>
       </c>
       <c r="B75" t="n">
-        <v>89418</v>
+        <v>5172</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8694,25 +8703,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6286</v>
+        <v>100526</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8722,10 +8731,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>558369</v>
+        <v>558478</v>
       </c>
       <c r="R75" t="n">
-        <v>6624121</v>
+        <v>6624257</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8752,12 +8761,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8768,11 +8777,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>tallskog på finmorän</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -8793,10 +8797,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121394310</v>
+        <v>121394365</v>
       </c>
       <c r="B76" t="n">
-        <v>95651</v>
+        <v>91112</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8809,21 +8813,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>53</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8833,10 +8832,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>558437</v>
+        <v>558351</v>
       </c>
       <c r="R76" t="n">
-        <v>6624264</v>
+        <v>6624213</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8863,12 +8862,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8877,6 +8876,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -2069,10 +2069,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121359457</v>
+        <v>121359467</v>
       </c>
       <c r="B13" t="n">
-        <v>92024</v>
+        <v>90937</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2085,21 +2085,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>1101</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2109,10 +2109,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558395</v>
+        <v>558464</v>
       </c>
       <c r="R13" t="n">
-        <v>6624316</v>
+        <v>6624306</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121359471</v>
+        <v>121359462</v>
       </c>
       <c r="B14" t="n">
-        <v>95652</v>
+        <v>90924</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2187,25 +2187,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>1106</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558521</v>
+        <v>558376</v>
       </c>
       <c r="R14" t="n">
-        <v>6624319</v>
+        <v>6624261</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2281,10 +2281,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121359461</v>
+        <v>121359466</v>
       </c>
       <c r="B15" t="n">
-        <v>79227</v>
+        <v>90685</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2293,25 +2293,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558352</v>
+        <v>558467</v>
       </c>
       <c r="R15" t="n">
-        <v>6624226</v>
+        <v>6624274</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121359458</v>
+        <v>121359469</v>
       </c>
       <c r="B16" t="n">
-        <v>92022</v>
+        <v>90720</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2403,21 +2403,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5448</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558350</v>
+        <v>558491</v>
       </c>
       <c r="R16" t="n">
-        <v>6624211</v>
+        <v>6624274</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121359443</v>
+        <v>121359457</v>
       </c>
       <c r="B17" t="n">
-        <v>90734</v>
+        <v>92024</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2509,21 +2509,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>5449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558441</v>
+        <v>558395</v>
       </c>
       <c r="R17" t="n">
-        <v>6624265</v>
+        <v>6624316</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121359469</v>
+        <v>121359461</v>
       </c>
       <c r="B18" t="n">
-        <v>90720</v>
+        <v>79227</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2615,21 +2615,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558491</v>
+        <v>558352</v>
       </c>
       <c r="R18" t="n">
-        <v>6624274</v>
+        <v>6624226</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2705,10 +2705,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121359506</v>
+        <v>121359465</v>
       </c>
       <c r="B19" t="n">
-        <v>8435</v>
+        <v>91112</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2717,25 +2717,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Mindre märgborre</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2745,10 +2740,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558352</v>
+        <v>558460</v>
       </c>
       <c r="R19" t="n">
-        <v>6624128</v>
+        <v>6624272</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2789,6 +2784,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2811,10 +2807,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121359462</v>
+        <v>121359460</v>
       </c>
       <c r="B20" t="n">
-        <v>90924</v>
+        <v>8435</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2823,25 +2819,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1106</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2851,10 +2847,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558376</v>
+        <v>558352</v>
       </c>
       <c r="R20" t="n">
-        <v>6624261</v>
+        <v>6624226</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2917,10 +2913,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121359466</v>
+        <v>121359443</v>
       </c>
       <c r="B21" t="n">
-        <v>90685</v>
+        <v>90734</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2929,25 +2925,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2957,10 +2953,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558467</v>
+        <v>558441</v>
       </c>
       <c r="R21" t="n">
-        <v>6624274</v>
+        <v>6624265</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3023,10 +3019,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121359465</v>
+        <v>121359458</v>
       </c>
       <c r="B22" t="n">
-        <v>91112</v>
+        <v>92022</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3039,16 +3035,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6040162</v>
+        <v>5448</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3058,10 +3059,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558460</v>
+        <v>558350</v>
       </c>
       <c r="R22" t="n">
-        <v>6624272</v>
+        <v>6624211</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3102,7 +3103,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3125,10 +3125,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121359467</v>
+        <v>121359459</v>
       </c>
       <c r="B23" t="n">
-        <v>90937</v>
+        <v>79227</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1101</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558464</v>
+        <v>558364</v>
       </c>
       <c r="R23" t="n">
-        <v>6624306</v>
+        <v>6624216</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3231,10 +3231,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121359444</v>
+        <v>121359471</v>
       </c>
       <c r="B24" t="n">
-        <v>92029</v>
+        <v>95652</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3243,41 +3243,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558433</v>
+        <v>558521</v>
       </c>
       <c r="R24" t="n">
-        <v>6624286</v>
+        <v>6624319</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3318,7 +3315,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3341,10 +3337,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121359460</v>
+        <v>121359444</v>
       </c>
       <c r="B25" t="n">
-        <v>8435</v>
+        <v>92029</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3357,34 +3353,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558352</v>
+        <v>558433</v>
       </c>
       <c r="R25" t="n">
-        <v>6624226</v>
+        <v>6624286</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3425,6 +3424,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3447,10 +3447,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121359459</v>
+        <v>121359506</v>
       </c>
       <c r="B26" t="n">
-        <v>79227</v>
+        <v>8435</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3459,25 +3459,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558364</v>
+        <v>558352</v>
       </c>
       <c r="R26" t="n">
-        <v>6624216</v>
+        <v>6624128</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3659,10 +3659,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121394933</v>
+        <v>121394943</v>
       </c>
       <c r="B28" t="n">
-        <v>8435</v>
+        <v>95652</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3671,25 +3671,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3699,10 +3699,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558377</v>
+        <v>558390</v>
       </c>
       <c r="R28" t="n">
-        <v>6624106</v>
+        <v>6624295</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3765,10 +3765,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121394942</v>
+        <v>121394933</v>
       </c>
       <c r="B29" t="n">
-        <v>95968</v>
+        <v>8435</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3777,25 +3777,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>990</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558390</v>
+        <v>558377</v>
       </c>
       <c r="R29" t="n">
-        <v>6624295</v>
+        <v>6624106</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3849,7 +3849,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3872,10 +3871,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121394932</v>
+        <v>121394934</v>
       </c>
       <c r="B30" t="n">
-        <v>91112</v>
+        <v>95652</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3888,16 +3887,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6040162</v>
+        <v>53</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3907,10 +3911,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558394</v>
+        <v>558377</v>
       </c>
       <c r="R30" t="n">
-        <v>6624091</v>
+        <v>6624106</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3951,7 +3955,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3974,10 +3977,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121394945</v>
+        <v>121394942</v>
       </c>
       <c r="B31" t="n">
-        <v>95652</v>
+        <v>95968</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3986,25 +3989,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>990</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4014,10 +4017,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558441</v>
+        <v>558390</v>
       </c>
       <c r="R31" t="n">
-        <v>6624265</v>
+        <v>6624295</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4058,6 +4061,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4080,7 +4084,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121394934</v>
+        <v>121394945</v>
       </c>
       <c r="B32" t="n">
         <v>95652</v>
@@ -4120,10 +4124,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558377</v>
+        <v>558441</v>
       </c>
       <c r="R32" t="n">
-        <v>6624106</v>
+        <v>6624265</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4186,10 +4190,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121394943</v>
+        <v>121394944</v>
       </c>
       <c r="B33" t="n">
-        <v>95652</v>
+        <v>90685</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4198,25 +4202,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4226,10 +4230,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558390</v>
+        <v>558441</v>
       </c>
       <c r="R33" t="n">
-        <v>6624295</v>
+        <v>6624265</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4292,10 +4296,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121394944</v>
+        <v>121394932</v>
       </c>
       <c r="B34" t="n">
-        <v>90685</v>
+        <v>91112</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4304,25 +4308,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4332,10 +4331,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558441</v>
+        <v>558394</v>
       </c>
       <c r="R34" t="n">
-        <v>6624265</v>
+        <v>6624091</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4376,6 +4375,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4398,10 +4398,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121394355</v>
+        <v>121394319</v>
       </c>
       <c r="B35" t="n">
-        <v>92193</v>
+        <v>8435</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4410,41 +4410,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2079</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558377</v>
+        <v>558461</v>
       </c>
       <c r="R35" t="n">
-        <v>6624159</v>
+        <v>6624164</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4471,12 +4468,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4485,24 +4482,8 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>undersida av grov ved mot mark # tall</t>
-        </is>
-      </c>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>Ralf Lundmark</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4523,10 +4504,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121394319</v>
+        <v>121394304</v>
       </c>
       <c r="B36" t="n">
-        <v>8435</v>
+        <v>98105</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4535,38 +4516,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558461</v>
+        <v>558372</v>
       </c>
       <c r="R36" t="n">
-        <v>6624164</v>
+        <v>6624277</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4593,12 +4578,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4629,10 +4614,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121394364</v>
+        <v>121394353</v>
       </c>
       <c r="B37" t="n">
-        <v>8435</v>
+        <v>4769</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4645,21 +4630,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>100299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4669,10 +4654,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558351</v>
+        <v>558363</v>
       </c>
       <c r="R37" t="n">
-        <v>6624213</v>
+        <v>6624071</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4699,12 +4684,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4735,10 +4720,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121394321</v>
+        <v>121394357</v>
       </c>
       <c r="B38" t="n">
-        <v>95652</v>
+        <v>95399</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4747,25 +4732,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>2869</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4775,10 +4760,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558450</v>
+        <v>558396</v>
       </c>
       <c r="R38" t="n">
-        <v>6624202</v>
+        <v>6624233</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4805,12 +4790,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4841,10 +4826,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121394323</v>
+        <v>121394339</v>
       </c>
       <c r="B39" t="n">
-        <v>5172</v>
+        <v>74654</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4857,21 +4842,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4881,10 +4866,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558492</v>
+        <v>558458</v>
       </c>
       <c r="R39" t="n">
-        <v>6624223</v>
+        <v>6624309</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4947,10 +4932,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121394272</v>
+        <v>121394313</v>
       </c>
       <c r="B40" t="n">
-        <v>58221</v>
+        <v>91113</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4959,47 +4944,33 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>208242</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Mindre vattensalamander</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558519</v>
+        <v>558412</v>
       </c>
       <c r="R40" t="n">
-        <v>6624313</v>
+        <v>6624060</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5026,17 +4997,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>under ved i barrskog</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5045,6 +5016,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5067,10 +5039,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121394339</v>
+        <v>121394303</v>
       </c>
       <c r="B41" t="n">
-        <v>74654</v>
+        <v>98105</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5079,38 +5051,42 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558458</v>
+        <v>558385</v>
       </c>
       <c r="R41" t="n">
-        <v>6624309</v>
+        <v>6624276</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5137,12 +5113,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5173,10 +5149,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121394357</v>
+        <v>121394365</v>
       </c>
       <c r="B42" t="n">
-        <v>95399</v>
+        <v>91112</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5185,25 +5161,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2869</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Bollvitmossa</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5213,10 +5184,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558396</v>
+        <v>558351</v>
       </c>
       <c r="R42" t="n">
-        <v>6624233</v>
+        <v>6624213</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5257,6 +5228,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5279,10 +5251,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121394313</v>
+        <v>121394324</v>
       </c>
       <c r="B43" t="n">
-        <v>91113</v>
+        <v>5192</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5291,20 +5263,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6040186</v>
+        <v>105930</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5314,10 +5291,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558412</v>
+        <v>558478</v>
       </c>
       <c r="R43" t="n">
-        <v>6624060</v>
+        <v>6624257</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5352,18 +5329,12 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5386,10 +5357,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121394310</v>
+        <v>121394345</v>
       </c>
       <c r="B44" t="n">
-        <v>95652</v>
+        <v>97053</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5398,27 +5369,23 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>221944</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5426,10 +5393,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558437</v>
+        <v>558386</v>
       </c>
       <c r="R44" t="n">
-        <v>6624264</v>
+        <v>6624222</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5456,12 +5423,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5470,6 +5437,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5492,10 +5460,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121394356</v>
+        <v>121394314</v>
       </c>
       <c r="B45" t="n">
-        <v>91411</v>
+        <v>91112</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5508,16 +5476,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>757</v>
+        <v>6040162</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5527,10 +5495,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>558364</v>
+        <v>558428</v>
       </c>
       <c r="R45" t="n">
-        <v>6624122</v>
+        <v>6624048</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5557,12 +5525,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5594,10 +5567,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121394359</v>
+        <v>121394344</v>
       </c>
       <c r="B46" t="n">
-        <v>74654</v>
+        <v>92008</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5610,21 +5583,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6426</v>
+        <v>4366</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5634,10 +5607,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558414</v>
+        <v>558407</v>
       </c>
       <c r="R46" t="n">
-        <v>6624238</v>
+        <v>6624166</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5664,12 +5637,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5700,10 +5673,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121394305</v>
+        <v>121394348</v>
       </c>
       <c r="B47" t="n">
-        <v>98105</v>
+        <v>92027</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5712,42 +5685,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>1968</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558420</v>
+        <v>558437</v>
       </c>
       <c r="R47" t="n">
-        <v>6624193</v>
+        <v>6624152</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5774,12 +5743,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5810,10 +5779,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121394333</v>
+        <v>121394350</v>
       </c>
       <c r="B48" t="n">
-        <v>95652</v>
+        <v>94770</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5822,25 +5791,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5850,10 +5819,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>558528</v>
+        <v>558402</v>
       </c>
       <c r="R48" t="n">
-        <v>6624316</v>
+        <v>6624073</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5916,10 +5885,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121394320</v>
+        <v>121394270</v>
       </c>
       <c r="B49" t="n">
-        <v>89769</v>
+        <v>98105</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5928,38 +5897,42 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558465</v>
+        <v>558522</v>
       </c>
       <c r="R49" t="n">
-        <v>6624192</v>
+        <v>6624290</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5986,12 +5959,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6022,10 +5995,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121394351</v>
+        <v>121394305</v>
       </c>
       <c r="B50" t="n">
-        <v>5192</v>
+        <v>98105</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6034,38 +6007,42 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>558363</v>
+        <v>558420</v>
       </c>
       <c r="R50" t="n">
-        <v>6624071</v>
+        <v>6624193</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6092,12 +6069,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6128,10 +6105,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121394304</v>
+        <v>121394326</v>
       </c>
       <c r="B51" t="n">
-        <v>98105</v>
+        <v>4769</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6140,42 +6117,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>558372</v>
+        <v>558478</v>
       </c>
       <c r="R51" t="n">
-        <v>6624277</v>
+        <v>6624257</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6202,12 +6175,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6238,10 +6211,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121394306</v>
+        <v>121394351</v>
       </c>
       <c r="B52" t="n">
-        <v>98105</v>
+        <v>5192</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6250,42 +6223,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>558437</v>
+        <v>558363</v>
       </c>
       <c r="R52" t="n">
-        <v>6624213</v>
+        <v>6624071</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6312,12 +6281,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6348,10 +6317,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121394327</v>
+        <v>121394354</v>
       </c>
       <c r="B53" t="n">
-        <v>90734</v>
+        <v>86299</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6364,21 +6333,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1204</v>
+        <v>3739</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6388,10 +6357,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>558466</v>
+        <v>558390</v>
       </c>
       <c r="R53" t="n">
-        <v>6624295</v>
+        <v>6624037</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6454,7 +6423,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121394352</v>
+        <v>121394323</v>
       </c>
       <c r="B54" t="n">
         <v>5172</v>
@@ -6494,10 +6463,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>558363</v>
+        <v>558492</v>
       </c>
       <c r="R54" t="n">
-        <v>6624071</v>
+        <v>6624223</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6560,10 +6529,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121394354</v>
+        <v>121394359</v>
       </c>
       <c r="B55" t="n">
-        <v>86299</v>
+        <v>74654</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6572,25 +6541,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3739</v>
+        <v>6426</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6600,10 +6569,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>558390</v>
+        <v>558414</v>
       </c>
       <c r="R55" t="n">
-        <v>6624037</v>
+        <v>6624238</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6630,12 +6599,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6666,10 +6635,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121394342</v>
+        <v>121394322</v>
       </c>
       <c r="B56" t="n">
-        <v>74654</v>
+        <v>5192</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6682,21 +6651,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6706,10 +6675,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>558435</v>
+        <v>558492</v>
       </c>
       <c r="R56" t="n">
-        <v>6624227</v>
+        <v>6624223</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6772,10 +6741,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121394322</v>
+        <v>121394342</v>
       </c>
       <c r="B57" t="n">
-        <v>5192</v>
+        <v>74654</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6788,21 +6757,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6812,10 +6781,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>558492</v>
+        <v>558435</v>
       </c>
       <c r="R57" t="n">
-        <v>6624223</v>
+        <v>6624227</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6878,10 +6847,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121394363</v>
+        <v>121394349</v>
       </c>
       <c r="B58" t="n">
-        <v>5172</v>
+        <v>84305</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6894,21 +6863,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100526</v>
+        <v>3518</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6918,10 +6887,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>558367</v>
+        <v>558419</v>
       </c>
       <c r="R58" t="n">
-        <v>6624219</v>
+        <v>6624081</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6948,12 +6917,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6984,10 +6953,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121394315</v>
+        <v>121394327</v>
       </c>
       <c r="B59" t="n">
-        <v>91980</v>
+        <v>90734</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6996,25 +6965,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6055</v>
+        <v>1204</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7024,10 +6993,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>558428</v>
+        <v>558466</v>
       </c>
       <c r="R59" t="n">
-        <v>6624044</v>
+        <v>6624295</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7054,12 +7023,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7090,10 +7059,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121394350</v>
+        <v>121394309</v>
       </c>
       <c r="B60" t="n">
-        <v>94770</v>
+        <v>95691</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7106,21 +7075,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2170</v>
+        <v>2590</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7130,10 +7099,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>558402</v>
+        <v>558437</v>
       </c>
       <c r="R60" t="n">
-        <v>6624073</v>
+        <v>6624264</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7160,12 +7129,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7196,10 +7165,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121394348</v>
+        <v>121394356</v>
       </c>
       <c r="B61" t="n">
-        <v>92027</v>
+        <v>91411</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7212,21 +7181,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1968</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Grantaggsvamp</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7236,10 +7200,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>558437</v>
+        <v>558364</v>
       </c>
       <c r="R61" t="n">
-        <v>6624152</v>
+        <v>6624122</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7266,12 +7230,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7280,6 +7244,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7302,10 +7267,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121394344</v>
+        <v>121394364</v>
       </c>
       <c r="B62" t="n">
-        <v>92008</v>
+        <v>8435</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7318,21 +7283,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4366</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7342,10 +7307,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>558407</v>
+        <v>558351</v>
       </c>
       <c r="R62" t="n">
-        <v>6624166</v>
+        <v>6624213</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7372,12 +7337,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7408,10 +7373,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121394309</v>
+        <v>121394321</v>
       </c>
       <c r="B63" t="n">
-        <v>95691</v>
+        <v>95652</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7420,25 +7385,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2590</v>
+        <v>53</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7448,10 +7413,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>558437</v>
+        <v>558450</v>
       </c>
       <c r="R63" t="n">
-        <v>6624264</v>
+        <v>6624202</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7478,12 +7443,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7514,10 +7479,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121394494</v>
+        <v>121394548</v>
       </c>
       <c r="B64" t="n">
-        <v>89419</v>
+        <v>92024</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7526,25 +7491,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6286</v>
+        <v>5449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7554,10 +7519,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>558369</v>
+        <v>558480</v>
       </c>
       <c r="R64" t="n">
-        <v>6624121</v>
+        <v>6624122</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7584,12 +7549,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7600,11 +7565,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>tallskog på finmorän</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7625,10 +7585,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121394353</v>
+        <v>121394315</v>
       </c>
       <c r="B65" t="n">
-        <v>4769</v>
+        <v>91980</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7637,25 +7597,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100299</v>
+        <v>6055</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7665,10 +7625,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>558363</v>
+        <v>558428</v>
       </c>
       <c r="R65" t="n">
-        <v>6624071</v>
+        <v>6624044</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7695,12 +7655,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7731,10 +7691,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121394548</v>
+        <v>121394363</v>
       </c>
       <c r="B66" t="n">
-        <v>92024</v>
+        <v>5172</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7743,25 +7703,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5449</v>
+        <v>100526</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7771,10 +7731,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>558480</v>
+        <v>558367</v>
       </c>
       <c r="R66" t="n">
-        <v>6624122</v>
+        <v>6624219</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7801,12 +7761,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7837,10 +7797,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121394345</v>
+        <v>121394306</v>
       </c>
       <c r="B67" t="n">
-        <v>97053</v>
+        <v>98105</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7849,34 +7809,42 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221944</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>558386</v>
+        <v>558437</v>
       </c>
       <c r="R67" t="n">
-        <v>6624222</v>
+        <v>6624213</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7903,12 +7871,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7917,7 +7885,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7940,10 +7907,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121394303</v>
+        <v>121394310</v>
       </c>
       <c r="B68" t="n">
-        <v>98105</v>
+        <v>95652</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7952,42 +7919,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>558385</v>
+        <v>558437</v>
       </c>
       <c r="R68" t="n">
-        <v>6624276</v>
+        <v>6624264</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8050,10 +8013,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121394314</v>
+        <v>121394272</v>
       </c>
       <c r="B69" t="n">
-        <v>91112</v>
+        <v>58221</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8062,33 +8025,47 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6040162</v>
+        <v>208242</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>558428</v>
+        <v>558519</v>
       </c>
       <c r="R69" t="n">
-        <v>6624048</v>
+        <v>6624313</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8115,17 +8092,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>under ved i barrskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8134,7 +8111,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8157,10 +8133,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121394349</v>
+        <v>121394352</v>
       </c>
       <c r="B70" t="n">
-        <v>84305</v>
+        <v>5172</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8173,21 +8149,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3518</v>
+        <v>100526</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8197,10 +8173,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>558419</v>
+        <v>558363</v>
       </c>
       <c r="R70" t="n">
-        <v>6624081</v>
+        <v>6624071</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8263,10 +8239,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121394343</v>
+        <v>121394325</v>
       </c>
       <c r="B71" t="n">
-        <v>74654</v>
+        <v>5172</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8279,21 +8255,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6426</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8303,10 +8279,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>558405</v>
+        <v>558478</v>
       </c>
       <c r="R71" t="n">
-        <v>6624226</v>
+        <v>6624257</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8369,10 +8345,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121394270</v>
+        <v>121394333</v>
       </c>
       <c r="B72" t="n">
-        <v>98105</v>
+        <v>95652</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8381,42 +8357,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>558522</v>
+        <v>558528</v>
       </c>
       <c r="R72" t="n">
-        <v>6624290</v>
+        <v>6624316</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8443,12 +8415,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8479,10 +8451,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121394324</v>
+        <v>121394355</v>
       </c>
       <c r="B73" t="n">
-        <v>5192</v>
+        <v>92193</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8491,38 +8463,41 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>105930</v>
+        <v>2079</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>558478</v>
+        <v>558377</v>
       </c>
       <c r="R73" t="n">
-        <v>6624257</v>
+        <v>6624159</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8549,12 +8524,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8563,8 +8538,24 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AL73" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>undersida av grov ved mot mark # tall</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8585,10 +8576,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121394326</v>
+        <v>121394320</v>
       </c>
       <c r="B74" t="n">
-        <v>4769</v>
+        <v>89769</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8597,25 +8588,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100299</v>
+        <v>1962</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8625,10 +8616,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>558478</v>
+        <v>558465</v>
       </c>
       <c r="R74" t="n">
-        <v>6624257</v>
+        <v>6624192</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8655,12 +8646,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8691,10 +8682,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121394325</v>
+        <v>121394343</v>
       </c>
       <c r="B75" t="n">
-        <v>5172</v>
+        <v>74654</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8707,21 +8698,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100526</v>
+        <v>6426</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8731,10 +8722,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>558478</v>
+        <v>558405</v>
       </c>
       <c r="R75" t="n">
-        <v>6624257</v>
+        <v>6624226</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8797,10 +8788,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121394365</v>
+        <v>121394494</v>
       </c>
       <c r="B76" t="n">
-        <v>91112</v>
+        <v>89419</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8809,20 +8800,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6040162</v>
+        <v>6286</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8832,10 +8828,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>558351</v>
+        <v>558369</v>
       </c>
       <c r="R76" t="n">
-        <v>6624213</v>
+        <v>6624121</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8862,12 +8858,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8876,9 +8872,13 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>tallskog på finmorän</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -2069,10 +2069,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121359467</v>
+        <v>121359459</v>
       </c>
       <c r="B13" t="n">
-        <v>90937</v>
+        <v>79227</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2085,21 +2085,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1101</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2109,10 +2109,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558464</v>
+        <v>558364</v>
       </c>
       <c r="R13" t="n">
-        <v>6624306</v>
+        <v>6624216</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121359462</v>
+        <v>121359457</v>
       </c>
       <c r="B14" t="n">
-        <v>90924</v>
+        <v>92024</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2187,25 +2187,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1106</v>
+        <v>5449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558376</v>
+        <v>558395</v>
       </c>
       <c r="R14" t="n">
-        <v>6624261</v>
+        <v>6624316</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2387,10 +2387,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121359469</v>
+        <v>121359443</v>
       </c>
       <c r="B16" t="n">
-        <v>90720</v>
+        <v>90734</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2403,21 +2403,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558491</v>
+        <v>558441</v>
       </c>
       <c r="R16" t="n">
-        <v>6624274</v>
+        <v>6624265</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121359457</v>
+        <v>121359469</v>
       </c>
       <c r="B17" t="n">
-        <v>92024</v>
+        <v>90720</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2509,21 +2509,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558395</v>
+        <v>558491</v>
       </c>
       <c r="R17" t="n">
-        <v>6624316</v>
+        <v>6624274</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121359461</v>
+        <v>121359465</v>
       </c>
       <c r="B18" t="n">
-        <v>79227</v>
+        <v>91112</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2615,21 +2615,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2639,10 +2634,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558352</v>
+        <v>558460</v>
       </c>
       <c r="R18" t="n">
-        <v>6624226</v>
+        <v>6624272</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2683,6 +2678,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2705,10 +2701,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121359465</v>
+        <v>121359458</v>
       </c>
       <c r="B19" t="n">
-        <v>91112</v>
+        <v>92022</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2721,16 +2717,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6040162</v>
+        <v>5448</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2740,10 +2741,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558460</v>
+        <v>558350</v>
       </c>
       <c r="R19" t="n">
-        <v>6624272</v>
+        <v>6624211</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2784,7 +2785,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2807,10 +2807,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121359460</v>
+        <v>121359461</v>
       </c>
       <c r="B20" t="n">
-        <v>8435</v>
+        <v>79227</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2819,25 +2819,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2913,10 +2913,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121359443</v>
+        <v>121359460</v>
       </c>
       <c r="B21" t="n">
-        <v>90734</v>
+        <v>8435</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2925,25 +2925,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2953,10 +2953,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558441</v>
+        <v>558352</v>
       </c>
       <c r="R21" t="n">
-        <v>6624265</v>
+        <v>6624226</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3019,10 +3019,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121359458</v>
+        <v>121359506</v>
       </c>
       <c r="B22" t="n">
-        <v>92022</v>
+        <v>8435</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3031,25 +3031,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5448</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558350</v>
+        <v>558352</v>
       </c>
       <c r="R22" t="n">
-        <v>6624211</v>
+        <v>6624128</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3125,10 +3125,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121359459</v>
+        <v>121359444</v>
       </c>
       <c r="B23" t="n">
-        <v>79227</v>
+        <v>92029</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3137,38 +3137,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>5964</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558364</v>
+        <v>558433</v>
       </c>
       <c r="R23" t="n">
-        <v>6624216</v>
+        <v>6624286</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3209,6 +3212,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3337,10 +3341,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121359444</v>
+        <v>121359467</v>
       </c>
       <c r="B25" t="n">
-        <v>92029</v>
+        <v>90937</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3349,41 +3353,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>1101</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558433</v>
+        <v>558464</v>
       </c>
       <c r="R25" t="n">
-        <v>6624286</v>
+        <v>6624306</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3424,7 +3425,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3447,10 +3447,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121359506</v>
+        <v>121359462</v>
       </c>
       <c r="B26" t="n">
-        <v>8435</v>
+        <v>90924</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3459,25 +3459,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>1106</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558352</v>
+        <v>558376</v>
       </c>
       <c r="R26" t="n">
-        <v>6624128</v>
+        <v>6624261</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121394549</v>
+        <v>121394944</v>
       </c>
       <c r="B27" t="n">
-        <v>92022</v>
+        <v>90685</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3565,25 +3565,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5448</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558468</v>
+        <v>558441</v>
       </c>
       <c r="R27" t="n">
-        <v>6624096</v>
+        <v>6624265</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3623,12 +3623,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3659,7 +3659,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121394943</v>
+        <v>121394945</v>
       </c>
       <c r="B28" t="n">
         <v>95652</v>
@@ -3699,10 +3699,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558390</v>
+        <v>558441</v>
       </c>
       <c r="R28" t="n">
-        <v>6624295</v>
+        <v>6624265</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3765,10 +3765,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121394933</v>
+        <v>121394549</v>
       </c>
       <c r="B29" t="n">
-        <v>8435</v>
+        <v>92022</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3777,25 +3777,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>5448</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558377</v>
+        <v>558468</v>
       </c>
       <c r="R29" t="n">
-        <v>6624106</v>
+        <v>6624096</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3835,12 +3835,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3871,10 +3871,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121394934</v>
+        <v>121394932</v>
       </c>
       <c r="B30" t="n">
-        <v>95652</v>
+        <v>91112</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3887,21 +3887,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3911,10 +3906,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558377</v>
+        <v>558394</v>
       </c>
       <c r="R30" t="n">
-        <v>6624106</v>
+        <v>6624091</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3955,6 +3950,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4084,7 +4080,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121394945</v>
+        <v>121394934</v>
       </c>
       <c r="B32" t="n">
         <v>95652</v>
@@ -4124,10 +4120,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558441</v>
+        <v>558377</v>
       </c>
       <c r="R32" t="n">
-        <v>6624265</v>
+        <v>6624106</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4190,10 +4186,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121394944</v>
+        <v>121394943</v>
       </c>
       <c r="B33" t="n">
-        <v>90685</v>
+        <v>95652</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4202,25 +4198,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4230,10 +4226,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558441</v>
+        <v>558390</v>
       </c>
       <c r="R33" t="n">
-        <v>6624265</v>
+        <v>6624295</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4296,10 +4292,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121394932</v>
+        <v>121394933</v>
       </c>
       <c r="B34" t="n">
-        <v>91112</v>
+        <v>8435</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4308,20 +4304,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6040162</v>
+        <v>106545</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4331,10 +4332,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558394</v>
+        <v>558377</v>
       </c>
       <c r="R34" t="n">
-        <v>6624091</v>
+        <v>6624106</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4375,7 +4376,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4398,10 +4398,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121394319</v>
+        <v>121394343</v>
       </c>
       <c r="B35" t="n">
-        <v>8435</v>
+        <v>74654</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4414,21 +4414,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6426</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4438,10 +4438,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558461</v>
+        <v>558405</v>
       </c>
       <c r="R35" t="n">
-        <v>6624164</v>
+        <v>6624226</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4468,12 +4468,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4504,10 +4504,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121394304</v>
+        <v>121394363</v>
       </c>
       <c r="B36" t="n">
-        <v>98105</v>
+        <v>5172</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4516,42 +4516,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558372</v>
+        <v>558367</v>
       </c>
       <c r="R36" t="n">
-        <v>6624277</v>
+        <v>6624219</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4578,12 +4574,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4614,10 +4610,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121394353</v>
+        <v>121394305</v>
       </c>
       <c r="B37" t="n">
-        <v>4769</v>
+        <v>98105</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4626,38 +4622,42 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558363</v>
+        <v>558420</v>
       </c>
       <c r="R37" t="n">
-        <v>6624071</v>
+        <v>6624193</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4684,12 +4684,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4720,10 +4720,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121394357</v>
+        <v>121394339</v>
       </c>
       <c r="B38" t="n">
-        <v>95399</v>
+        <v>74654</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4736,21 +4736,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2869</v>
+        <v>6426</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4760,10 +4760,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558396</v>
+        <v>558458</v>
       </c>
       <c r="R38" t="n">
-        <v>6624233</v>
+        <v>6624309</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4790,12 +4790,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4826,10 +4826,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121394339</v>
+        <v>121394356</v>
       </c>
       <c r="B39" t="n">
-        <v>74654</v>
+        <v>91411</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4838,25 +4838,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6426</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Kattfotslav</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4866,10 +4861,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558458</v>
+        <v>558364</v>
       </c>
       <c r="R39" t="n">
-        <v>6624309</v>
+        <v>6624122</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4896,12 +4891,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4910,6 +4905,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4932,10 +4928,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121394313</v>
+        <v>121394354</v>
       </c>
       <c r="B40" t="n">
-        <v>91113</v>
+        <v>86299</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4948,16 +4944,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6040186</v>
+        <v>3739</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4967,10 +4968,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558412</v>
+        <v>558390</v>
       </c>
       <c r="R40" t="n">
-        <v>6624060</v>
+        <v>6624037</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5005,18 +5006,12 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5039,10 +5034,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121394303</v>
+        <v>121394325</v>
       </c>
       <c r="B41" t="n">
-        <v>98105</v>
+        <v>5172</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5051,42 +5046,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558385</v>
+        <v>558478</v>
       </c>
       <c r="R41" t="n">
-        <v>6624276</v>
+        <v>6624257</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5113,12 +5104,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5149,10 +5140,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121394365</v>
+        <v>121394313</v>
       </c>
       <c r="B42" t="n">
-        <v>91112</v>
+        <v>91113</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5165,16 +5156,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6040162</v>
+        <v>6040186</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5184,10 +5175,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558351</v>
+        <v>558412</v>
       </c>
       <c r="R42" t="n">
-        <v>6624213</v>
+        <v>6624060</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5214,12 +5205,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5251,10 +5247,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121394324</v>
+        <v>121394303</v>
       </c>
       <c r="B43" t="n">
-        <v>5192</v>
+        <v>98105</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5263,38 +5259,42 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558478</v>
+        <v>558385</v>
       </c>
       <c r="R43" t="n">
-        <v>6624257</v>
+        <v>6624276</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5321,12 +5321,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5357,10 +5357,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121394345</v>
+        <v>121394315</v>
       </c>
       <c r="B44" t="n">
-        <v>97053</v>
+        <v>91980</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5369,23 +5369,27 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221944</v>
+        <v>6055</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Stereopsis vitellina</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5393,10 +5397,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558386</v>
+        <v>558428</v>
       </c>
       <c r="R44" t="n">
-        <v>6624222</v>
+        <v>6624044</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5423,12 +5427,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5437,7 +5441,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5460,10 +5463,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121394314</v>
+        <v>121394319</v>
       </c>
       <c r="B45" t="n">
-        <v>91112</v>
+        <v>8435</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5472,20 +5475,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6040162</v>
+        <v>106545</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5495,10 +5503,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>558428</v>
+        <v>558461</v>
       </c>
       <c r="R45" t="n">
-        <v>6624048</v>
+        <v>6624164</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5525,17 +5533,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5544,7 +5547,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5567,10 +5569,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121394344</v>
+        <v>121394350</v>
       </c>
       <c r="B46" t="n">
-        <v>92008</v>
+        <v>94770</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5583,21 +5585,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4366</v>
+        <v>2170</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5607,10 +5609,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558407</v>
+        <v>558402</v>
       </c>
       <c r="R46" t="n">
-        <v>6624166</v>
+        <v>6624073</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5779,10 +5781,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121394350</v>
+        <v>121394365</v>
       </c>
       <c r="B48" t="n">
-        <v>94770</v>
+        <v>91112</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5791,25 +5793,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2170</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Flagellkvastmossa</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5819,10 +5816,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>558402</v>
+        <v>558351</v>
       </c>
       <c r="R48" t="n">
-        <v>6624073</v>
+        <v>6624213</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5849,12 +5846,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5863,6 +5860,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5885,10 +5883,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121394270</v>
+        <v>121394272</v>
       </c>
       <c r="B49" t="n">
-        <v>98105</v>
+        <v>58221</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5897,30 +5895,35 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>208242</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5929,10 +5932,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558522</v>
+        <v>558519</v>
       </c>
       <c r="R49" t="n">
-        <v>6624290</v>
+        <v>6624313</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5965,6 +5968,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>under ved i barrskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5995,10 +6003,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121394305</v>
+        <v>121394322</v>
       </c>
       <c r="B50" t="n">
-        <v>98105</v>
+        <v>5192</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6007,42 +6015,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>558420</v>
+        <v>558492</v>
       </c>
       <c r="R50" t="n">
-        <v>6624193</v>
+        <v>6624223</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6069,12 +6073,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6105,10 +6109,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121394326</v>
+        <v>121394327</v>
       </c>
       <c r="B51" t="n">
-        <v>4769</v>
+        <v>90734</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6117,25 +6121,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100299</v>
+        <v>1204</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6145,10 +6149,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>558478</v>
+        <v>558466</v>
       </c>
       <c r="R51" t="n">
-        <v>6624257</v>
+        <v>6624295</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6211,10 +6215,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121394351</v>
+        <v>121394321</v>
       </c>
       <c r="B52" t="n">
-        <v>5192</v>
+        <v>95652</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6223,25 +6227,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>105930</v>
+        <v>53</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6251,10 +6255,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>558363</v>
+        <v>558450</v>
       </c>
       <c r="R52" t="n">
-        <v>6624071</v>
+        <v>6624202</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6281,12 +6285,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6317,10 +6321,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121394354</v>
+        <v>121394320</v>
       </c>
       <c r="B53" t="n">
-        <v>86299</v>
+        <v>89769</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6333,21 +6337,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3739</v>
+        <v>1962</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6357,10 +6361,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>558390</v>
+        <v>558465</v>
       </c>
       <c r="R53" t="n">
-        <v>6624037</v>
+        <v>6624192</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6387,12 +6391,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6423,10 +6427,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121394323</v>
+        <v>121394333</v>
       </c>
       <c r="B54" t="n">
-        <v>5172</v>
+        <v>95652</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6435,25 +6439,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6463,10 +6467,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>558492</v>
+        <v>558528</v>
       </c>
       <c r="R54" t="n">
-        <v>6624223</v>
+        <v>6624316</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6529,10 +6533,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121394359</v>
+        <v>121394349</v>
       </c>
       <c r="B55" t="n">
-        <v>74654</v>
+        <v>84305</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6545,21 +6549,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6426</v>
+        <v>3518</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6569,10 +6573,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>558414</v>
+        <v>558419</v>
       </c>
       <c r="R55" t="n">
-        <v>6624238</v>
+        <v>6624081</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6599,12 +6603,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6635,10 +6639,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121394322</v>
+        <v>121394357</v>
       </c>
       <c r="B56" t="n">
-        <v>5192</v>
+        <v>95399</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6651,21 +6655,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>105930</v>
+        <v>2869</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6675,10 +6679,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>558492</v>
+        <v>558396</v>
       </c>
       <c r="R56" t="n">
-        <v>6624223</v>
+        <v>6624233</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6705,12 +6709,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6741,10 +6745,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121394342</v>
+        <v>121394304</v>
       </c>
       <c r="B57" t="n">
-        <v>74654</v>
+        <v>98105</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6753,38 +6757,42 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>558435</v>
+        <v>558372</v>
       </c>
       <c r="R57" t="n">
-        <v>6624227</v>
+        <v>6624277</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6811,12 +6819,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6847,10 +6855,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121394349</v>
+        <v>121394355</v>
       </c>
       <c r="B58" t="n">
-        <v>84305</v>
+        <v>92193</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6859,38 +6867,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3518</v>
+        <v>2079</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>558419</v>
+        <v>558377</v>
       </c>
       <c r="R58" t="n">
-        <v>6624081</v>
+        <v>6624159</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6917,12 +6928,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6931,8 +6942,24 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>undersida av grov ved mot mark # tall</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -6953,10 +6980,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121394327</v>
+        <v>121394364</v>
       </c>
       <c r="B59" t="n">
-        <v>90734</v>
+        <v>8435</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6965,25 +6992,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1204</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6993,10 +7020,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>558466</v>
+        <v>558351</v>
       </c>
       <c r="R59" t="n">
-        <v>6624295</v>
+        <v>6624213</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7023,12 +7050,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7059,10 +7086,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121394309</v>
+        <v>121394270</v>
       </c>
       <c r="B60" t="n">
-        <v>95691</v>
+        <v>98105</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7071,38 +7098,42 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>558437</v>
+        <v>558522</v>
       </c>
       <c r="R60" t="n">
-        <v>6624264</v>
+        <v>6624290</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7165,10 +7196,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121394356</v>
+        <v>121394342</v>
       </c>
       <c r="B61" t="n">
-        <v>91411</v>
+        <v>74654</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7177,20 +7208,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>757</v>
+        <v>6426</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7200,10 +7236,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>558364</v>
+        <v>558435</v>
       </c>
       <c r="R61" t="n">
-        <v>6624122</v>
+        <v>6624227</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7230,12 +7266,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7244,7 +7280,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7267,10 +7302,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121394364</v>
+        <v>121394494</v>
       </c>
       <c r="B62" t="n">
-        <v>8435</v>
+        <v>89419</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7279,25 +7314,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>6286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7307,10 +7342,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>558351</v>
+        <v>558369</v>
       </c>
       <c r="R62" t="n">
-        <v>6624213</v>
+        <v>6624121</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7337,12 +7372,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7353,6 +7388,11 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>tallskog på finmorän</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7373,10 +7413,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121394321</v>
+        <v>121394326</v>
       </c>
       <c r="B63" t="n">
-        <v>95652</v>
+        <v>4769</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7385,25 +7425,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>100299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7413,10 +7453,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>558450</v>
+        <v>558478</v>
       </c>
       <c r="R63" t="n">
-        <v>6624202</v>
+        <v>6624257</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7443,12 +7483,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7479,10 +7519,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121394548</v>
+        <v>121394309</v>
       </c>
       <c r="B64" t="n">
-        <v>92024</v>
+        <v>95691</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7491,25 +7531,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5449</v>
+        <v>2590</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7519,10 +7559,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>558480</v>
+        <v>558437</v>
       </c>
       <c r="R64" t="n">
-        <v>6624122</v>
+        <v>6624264</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7549,12 +7589,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7585,10 +7625,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121394315</v>
+        <v>121394314</v>
       </c>
       <c r="B65" t="n">
-        <v>91980</v>
+        <v>91112</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7597,25 +7637,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6055</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Spadskinn</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7628,7 +7663,7 @@
         <v>558428</v>
       </c>
       <c r="R65" t="n">
-        <v>6624044</v>
+        <v>6624048</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7655,12 +7690,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7669,6 +7709,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7691,10 +7732,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121394363</v>
+        <v>121394345</v>
       </c>
       <c r="B66" t="n">
-        <v>5172</v>
+        <v>97053</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7707,23 +7748,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100526</v>
+        <v>221944</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7731,10 +7768,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>558367</v>
+        <v>558386</v>
       </c>
       <c r="R66" t="n">
-        <v>6624219</v>
+        <v>6624222</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7761,12 +7798,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7775,6 +7812,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7797,10 +7835,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121394306</v>
+        <v>121394344</v>
       </c>
       <c r="B67" t="n">
-        <v>98105</v>
+        <v>92008</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7809,42 +7847,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>558437</v>
+        <v>558407</v>
       </c>
       <c r="R67" t="n">
-        <v>6624213</v>
+        <v>6624166</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7871,12 +7905,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7907,10 +7941,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121394310</v>
+        <v>121394323</v>
       </c>
       <c r="B68" t="n">
-        <v>95652</v>
+        <v>5172</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7919,25 +7953,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7947,10 +7981,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>558437</v>
+        <v>558492</v>
       </c>
       <c r="R68" t="n">
-        <v>6624264</v>
+        <v>6624223</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7977,12 +8011,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8013,10 +8047,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121394272</v>
+        <v>121394310</v>
       </c>
       <c r="B69" t="n">
-        <v>58221</v>
+        <v>95652</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8025,47 +8059,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>208242</v>
+        <v>53</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>558519</v>
+        <v>558437</v>
       </c>
       <c r="R69" t="n">
-        <v>6624313</v>
+        <v>6624264</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8098,11 +8123,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>under ved i barrskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8133,10 +8153,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121394352</v>
+        <v>121394306</v>
       </c>
       <c r="B70" t="n">
-        <v>5172</v>
+        <v>98105</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8145,38 +8165,42 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>558363</v>
+        <v>558437</v>
       </c>
       <c r="R70" t="n">
-        <v>6624071</v>
+        <v>6624213</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8203,12 +8227,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8239,10 +8263,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121394325</v>
+        <v>121394324</v>
       </c>
       <c r="B71" t="n">
-        <v>5172</v>
+        <v>5192</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8255,21 +8279,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8345,10 +8369,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121394333</v>
+        <v>121394351</v>
       </c>
       <c r="B72" t="n">
-        <v>95652</v>
+        <v>5192</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8357,25 +8381,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8385,10 +8409,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>558528</v>
+        <v>558363</v>
       </c>
       <c r="R72" t="n">
-        <v>6624316</v>
+        <v>6624071</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8451,10 +8475,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121394355</v>
+        <v>121394548</v>
       </c>
       <c r="B73" t="n">
-        <v>92193</v>
+        <v>92024</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8467,37 +8491,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2079</v>
+        <v>5449</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>558377</v>
+        <v>558480</v>
       </c>
       <c r="R73" t="n">
-        <v>6624159</v>
+        <v>6624122</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8524,12 +8545,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8538,24 +8559,8 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AL73" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>undersida av grov ved mot mark # tall</t>
-        </is>
-      </c>
-      <c r="AQ73" t="inlineStr">
-        <is>
-          <t>Ralf Lundmark</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8576,10 +8581,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121394320</v>
+        <v>121394359</v>
       </c>
       <c r="B74" t="n">
-        <v>89769</v>
+        <v>74654</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8588,25 +8593,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1962</v>
+        <v>6426</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8616,10 +8621,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>558465</v>
+        <v>558414</v>
       </c>
       <c r="R74" t="n">
-        <v>6624192</v>
+        <v>6624238</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8646,12 +8651,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8682,10 +8687,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121394343</v>
+        <v>121394353</v>
       </c>
       <c r="B75" t="n">
-        <v>74654</v>
+        <v>4769</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8698,21 +8703,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6426</v>
+        <v>100299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8722,10 +8727,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>558405</v>
+        <v>558363</v>
       </c>
       <c r="R75" t="n">
-        <v>6624226</v>
+        <v>6624071</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8788,10 +8793,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121394494</v>
+        <v>121394352</v>
       </c>
       <c r="B76" t="n">
-        <v>89419</v>
+        <v>5172</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8800,25 +8805,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6286</v>
+        <v>100526</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8828,10 +8833,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>558369</v>
+        <v>558363</v>
       </c>
       <c r="R76" t="n">
-        <v>6624121</v>
+        <v>6624071</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8858,12 +8863,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8874,11 +8879,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>tallskog på finmorän</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -2069,10 +2069,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121359459</v>
+        <v>121359471</v>
       </c>
       <c r="B13" t="n">
-        <v>79227</v>
+        <v>95652</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2085,21 +2085,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2109,10 +2109,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558364</v>
+        <v>558521</v>
       </c>
       <c r="R13" t="n">
-        <v>6624216</v>
+        <v>6624319</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121359457</v>
+        <v>121359469</v>
       </c>
       <c r="B14" t="n">
-        <v>92024</v>
+        <v>90720</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558395</v>
+        <v>558491</v>
       </c>
       <c r="R14" t="n">
-        <v>6624316</v>
+        <v>6624274</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2281,10 +2281,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121359466</v>
+        <v>121359444</v>
       </c>
       <c r="B15" t="n">
-        <v>90685</v>
+        <v>92029</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2297,34 +2297,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>5964</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558467</v>
+        <v>558433</v>
       </c>
       <c r="R15" t="n">
-        <v>6624274</v>
+        <v>6624286</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2365,6 +2368,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2387,10 +2391,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121359443</v>
+        <v>121359467</v>
       </c>
       <c r="B16" t="n">
-        <v>90734</v>
+        <v>90937</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2403,21 +2407,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>1101</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Peck) Jülich</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2427,10 +2431,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558441</v>
+        <v>558464</v>
       </c>
       <c r="R16" t="n">
-        <v>6624265</v>
+        <v>6624306</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2493,10 +2497,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121359469</v>
+        <v>121359462</v>
       </c>
       <c r="B17" t="n">
-        <v>90720</v>
+        <v>90924</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2505,25 +2509,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1106</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2533,10 +2537,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558491</v>
+        <v>558376</v>
       </c>
       <c r="R17" t="n">
-        <v>6624274</v>
+        <v>6624261</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2599,10 +2603,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121359465</v>
+        <v>121359506</v>
       </c>
       <c r="B18" t="n">
-        <v>91112</v>
+        <v>8435</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2611,20 +2615,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6040162</v>
+        <v>106545</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2634,10 +2643,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558460</v>
+        <v>558352</v>
       </c>
       <c r="R18" t="n">
-        <v>6624272</v>
+        <v>6624128</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2678,7 +2687,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2701,10 +2709,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121359458</v>
+        <v>121359465</v>
       </c>
       <c r="B19" t="n">
-        <v>92022</v>
+        <v>91112</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2717,21 +2725,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5448</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Svartvit taggsvamp</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2741,10 +2744,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558350</v>
+        <v>558460</v>
       </c>
       <c r="R19" t="n">
-        <v>6624211</v>
+        <v>6624272</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2785,6 +2788,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2807,7 +2811,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121359461</v>
+        <v>121359459</v>
       </c>
       <c r="B20" t="n">
         <v>79227</v>
@@ -2847,10 +2851,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558352</v>
+        <v>558364</v>
       </c>
       <c r="R20" t="n">
-        <v>6624226</v>
+        <v>6624216</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2913,10 +2917,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121359460</v>
+        <v>121359461</v>
       </c>
       <c r="B21" t="n">
-        <v>8435</v>
+        <v>79227</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2925,25 +2929,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3019,7 +3023,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121359506</v>
+        <v>121359460</v>
       </c>
       <c r="B22" t="n">
         <v>8435</v>
@@ -3062,7 +3066,7 @@
         <v>558352</v>
       </c>
       <c r="R22" t="n">
-        <v>6624128</v>
+        <v>6624226</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3125,10 +3129,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121359444</v>
+        <v>121359443</v>
       </c>
       <c r="B23" t="n">
-        <v>92029</v>
+        <v>90734</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3137,41 +3141,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558433</v>
+        <v>558441</v>
       </c>
       <c r="R23" t="n">
-        <v>6624286</v>
+        <v>6624265</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3212,7 +3213,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3235,10 +3235,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121359471</v>
+        <v>121359466</v>
       </c>
       <c r="B24" t="n">
-        <v>95652</v>
+        <v>90685</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3247,25 +3247,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558521</v>
+        <v>558467</v>
       </c>
       <c r="R24" t="n">
-        <v>6624319</v>
+        <v>6624274</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3341,10 +3341,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121359467</v>
+        <v>121359457</v>
       </c>
       <c r="B25" t="n">
-        <v>90937</v>
+        <v>92024</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3357,21 +3357,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1101</v>
+        <v>5449</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558464</v>
+        <v>558395</v>
       </c>
       <c r="R25" t="n">
-        <v>6624306</v>
+        <v>6624316</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3447,10 +3447,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121359462</v>
+        <v>121359458</v>
       </c>
       <c r="B26" t="n">
-        <v>90924</v>
+        <v>92022</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3459,25 +3459,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1106</v>
+        <v>5448</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558376</v>
+        <v>558350</v>
       </c>
       <c r="R26" t="n">
-        <v>6624261</v>
+        <v>6624211</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121394944</v>
+        <v>121394932</v>
       </c>
       <c r="B27" t="n">
-        <v>90685</v>
+        <v>91112</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3565,25 +3565,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Vedticka</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3593,10 +3588,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558441</v>
+        <v>558394</v>
       </c>
       <c r="R27" t="n">
-        <v>6624265</v>
+        <v>6624091</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3637,6 +3632,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3659,7 +3655,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121394945</v>
+        <v>121394934</v>
       </c>
       <c r="B28" t="n">
         <v>95652</v>
@@ -3699,10 +3695,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558441</v>
+        <v>558377</v>
       </c>
       <c r="R28" t="n">
-        <v>6624265</v>
+        <v>6624106</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3765,10 +3761,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121394549</v>
+        <v>121394942</v>
       </c>
       <c r="B29" t="n">
-        <v>92022</v>
+        <v>95968</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3777,25 +3773,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5448</v>
+        <v>990</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3805,10 +3801,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558468</v>
+        <v>558390</v>
       </c>
       <c r="R29" t="n">
-        <v>6624096</v>
+        <v>6624295</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3835,12 +3831,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3849,6 +3845,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3871,10 +3868,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121394932</v>
+        <v>121394933</v>
       </c>
       <c r="B30" t="n">
-        <v>91112</v>
+        <v>8435</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3883,20 +3880,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6040162</v>
+        <v>106545</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3906,10 +3908,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558394</v>
+        <v>558377</v>
       </c>
       <c r="R30" t="n">
-        <v>6624091</v>
+        <v>6624106</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3950,7 +3952,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3973,10 +3974,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121394942</v>
+        <v>121394549</v>
       </c>
       <c r="B31" t="n">
-        <v>95968</v>
+        <v>92022</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3985,25 +3986,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>990</v>
+        <v>5448</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4013,10 +4014,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558390</v>
+        <v>558468</v>
       </c>
       <c r="R31" t="n">
-        <v>6624295</v>
+        <v>6624096</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4043,12 +4044,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4057,7 +4058,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4080,7 +4080,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121394934</v>
+        <v>121394945</v>
       </c>
       <c r="B32" t="n">
         <v>95652</v>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558377</v>
+        <v>558441</v>
       </c>
       <c r="R32" t="n">
-        <v>6624106</v>
+        <v>6624265</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4186,10 +4186,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121394943</v>
+        <v>121394944</v>
       </c>
       <c r="B33" t="n">
-        <v>95652</v>
+        <v>90685</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4198,25 +4198,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558390</v>
+        <v>558441</v>
       </c>
       <c r="R33" t="n">
-        <v>6624295</v>
+        <v>6624265</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4292,10 +4292,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121394933</v>
+        <v>121394943</v>
       </c>
       <c r="B34" t="n">
-        <v>8435</v>
+        <v>95652</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4304,25 +4304,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4332,10 +4332,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558377</v>
+        <v>558390</v>
       </c>
       <c r="R34" t="n">
-        <v>6624106</v>
+        <v>6624295</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4398,10 +4398,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121394343</v>
+        <v>121394272</v>
       </c>
       <c r="B35" t="n">
-        <v>74654</v>
+        <v>58221</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4414,34 +4414,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6426</v>
+        <v>208242</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558405</v>
+        <v>558519</v>
       </c>
       <c r="R35" t="n">
-        <v>6624226</v>
+        <v>6624313</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4468,12 +4477,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>under ved i barrskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4504,10 +4518,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121394363</v>
+        <v>121394350</v>
       </c>
       <c r="B36" t="n">
-        <v>5172</v>
+        <v>94770</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4520,21 +4534,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>2170</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4544,10 +4558,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558367</v>
+        <v>558402</v>
       </c>
       <c r="R36" t="n">
-        <v>6624219</v>
+        <v>6624073</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4574,12 +4588,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4610,10 +4624,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121394305</v>
+        <v>121394320</v>
       </c>
       <c r="B37" t="n">
-        <v>98105</v>
+        <v>89769</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4622,42 +4636,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558420</v>
+        <v>558465</v>
       </c>
       <c r="R37" t="n">
-        <v>6624193</v>
+        <v>6624192</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4684,12 +4694,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4720,10 +4730,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121394339</v>
+        <v>121394351</v>
       </c>
       <c r="B38" t="n">
-        <v>74654</v>
+        <v>5192</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4736,21 +4746,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4760,10 +4770,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558458</v>
+        <v>558363</v>
       </c>
       <c r="R38" t="n">
-        <v>6624309</v>
+        <v>6624071</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4826,10 +4836,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121394356</v>
+        <v>121394309</v>
       </c>
       <c r="B39" t="n">
-        <v>91411</v>
+        <v>95691</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4838,20 +4848,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>757</v>
+        <v>2590</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4861,10 +4876,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558364</v>
+        <v>558437</v>
       </c>
       <c r="R39" t="n">
-        <v>6624122</v>
+        <v>6624264</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4891,12 +4906,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4905,7 +4920,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4928,10 +4942,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121394354</v>
+        <v>121394357</v>
       </c>
       <c r="B40" t="n">
-        <v>86299</v>
+        <v>95399</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4940,25 +4954,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3739</v>
+        <v>2869</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4968,10 +4982,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558390</v>
+        <v>558396</v>
       </c>
       <c r="R40" t="n">
-        <v>6624037</v>
+        <v>6624233</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4998,12 +5012,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5034,7 +5048,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121394325</v>
+        <v>121394352</v>
       </c>
       <c r="B41" t="n">
         <v>5172</v>
@@ -5074,10 +5088,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558478</v>
+        <v>558363</v>
       </c>
       <c r="R41" t="n">
-        <v>6624257</v>
+        <v>6624071</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5140,10 +5154,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121394313</v>
+        <v>121394315</v>
       </c>
       <c r="B42" t="n">
-        <v>91113</v>
+        <v>91980</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5152,20 +5166,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6040186</v>
+        <v>6055</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spadskinn</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5175,10 +5194,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558412</v>
+        <v>558428</v>
       </c>
       <c r="R42" t="n">
-        <v>6624060</v>
+        <v>6624044</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5205,17 +5224,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5224,7 +5238,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5247,10 +5260,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121394303</v>
+        <v>121394313</v>
       </c>
       <c r="B43" t="n">
-        <v>98105</v>
+        <v>91113</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5259,42 +5272,33 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558385</v>
+        <v>558412</v>
       </c>
       <c r="R43" t="n">
-        <v>6624276</v>
+        <v>6624060</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5321,12 +5325,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5335,6 +5344,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5357,10 +5367,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121394315</v>
+        <v>121394322</v>
       </c>
       <c r="B44" t="n">
-        <v>91980</v>
+        <v>5192</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5369,25 +5379,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6055</v>
+        <v>105930</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5397,10 +5407,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558428</v>
+        <v>558492</v>
       </c>
       <c r="R44" t="n">
-        <v>6624044</v>
+        <v>6624223</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5427,12 +5437,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5463,10 +5473,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121394319</v>
+        <v>121394548</v>
       </c>
       <c r="B45" t="n">
-        <v>8435</v>
+        <v>92024</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5475,25 +5485,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>5449</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5503,10 +5513,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>558461</v>
+        <v>558480</v>
       </c>
       <c r="R45" t="n">
-        <v>6624164</v>
+        <v>6624122</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5533,12 +5543,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5569,10 +5579,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121394350</v>
+        <v>121394355</v>
       </c>
       <c r="B46" t="n">
-        <v>94770</v>
+        <v>92193</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5581,38 +5591,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2170</v>
+        <v>2079</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558402</v>
+        <v>558377</v>
       </c>
       <c r="R46" t="n">
-        <v>6624073</v>
+        <v>6624159</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5639,12 +5652,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5653,8 +5666,24 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>undersida av grov ved mot mark # tall</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5675,10 +5704,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121394348</v>
+        <v>121394365</v>
       </c>
       <c r="B47" t="n">
-        <v>92027</v>
+        <v>91112</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5691,21 +5720,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1968</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Grantaggsvamp</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5715,10 +5739,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558437</v>
+        <v>558351</v>
       </c>
       <c r="R47" t="n">
-        <v>6624152</v>
+        <v>6624213</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5745,12 +5769,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5759,6 +5783,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5781,10 +5806,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121394365</v>
+        <v>121394327</v>
       </c>
       <c r="B48" t="n">
-        <v>91112</v>
+        <v>90734</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5797,16 +5822,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6040162</v>
+        <v>1204</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5816,10 +5846,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>558351</v>
+        <v>558466</v>
       </c>
       <c r="R48" t="n">
-        <v>6624213</v>
+        <v>6624295</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5846,12 +5876,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5860,7 +5890,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5883,10 +5912,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121394272</v>
+        <v>121394270</v>
       </c>
       <c r="B49" t="n">
-        <v>58221</v>
+        <v>98105</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5895,35 +5924,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>208242</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>hona</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5932,10 +5956,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558519</v>
+        <v>558522</v>
       </c>
       <c r="R49" t="n">
-        <v>6624313</v>
+        <v>6624290</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5968,11 +5992,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>under ved i barrskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6003,10 +6022,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121394322</v>
+        <v>121394354</v>
       </c>
       <c r="B50" t="n">
-        <v>5192</v>
+        <v>86299</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6015,25 +6034,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>105930</v>
+        <v>3739</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6043,10 +6062,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>558492</v>
+        <v>558390</v>
       </c>
       <c r="R50" t="n">
-        <v>6624223</v>
+        <v>6624037</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6109,10 +6128,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121394327</v>
+        <v>121394342</v>
       </c>
       <c r="B51" t="n">
-        <v>90734</v>
+        <v>74654</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6121,25 +6140,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1204</v>
+        <v>6426</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6149,10 +6168,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>558466</v>
+        <v>558435</v>
       </c>
       <c r="R51" t="n">
-        <v>6624295</v>
+        <v>6624227</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6215,10 +6234,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121394321</v>
+        <v>121394494</v>
       </c>
       <c r="B52" t="n">
-        <v>95652</v>
+        <v>89419</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6227,25 +6246,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>6286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6255,10 +6274,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>558450</v>
+        <v>558369</v>
       </c>
       <c r="R52" t="n">
-        <v>6624202</v>
+        <v>6624121</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6301,6 +6320,11 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>tallskog på finmorän</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6321,10 +6345,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121394320</v>
+        <v>121394333</v>
       </c>
       <c r="B53" t="n">
-        <v>89769</v>
+        <v>95652</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6337,21 +6361,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1962</v>
+        <v>53</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6361,10 +6385,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>558465</v>
+        <v>558528</v>
       </c>
       <c r="R53" t="n">
-        <v>6624192</v>
+        <v>6624316</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6391,12 +6415,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6427,10 +6451,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121394333</v>
+        <v>121394323</v>
       </c>
       <c r="B54" t="n">
-        <v>95652</v>
+        <v>5172</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6439,25 +6463,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6467,10 +6491,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>558528</v>
+        <v>558492</v>
       </c>
       <c r="R54" t="n">
-        <v>6624316</v>
+        <v>6624223</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6533,10 +6557,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121394349</v>
+        <v>121394314</v>
       </c>
       <c r="B55" t="n">
-        <v>84305</v>
+        <v>91112</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6545,25 +6569,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3518</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Smal svampklubba</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6573,10 +6592,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>558419</v>
+        <v>558428</v>
       </c>
       <c r="R55" t="n">
-        <v>6624081</v>
+        <v>6624048</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6611,12 +6630,18 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6639,10 +6664,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121394357</v>
+        <v>121394344</v>
       </c>
       <c r="B56" t="n">
-        <v>95399</v>
+        <v>92008</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6655,21 +6680,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2869</v>
+        <v>4366</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6679,10 +6704,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>558396</v>
+        <v>558407</v>
       </c>
       <c r="R56" t="n">
-        <v>6624233</v>
+        <v>6624166</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6709,12 +6734,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6745,10 +6770,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121394304</v>
+        <v>121394356</v>
       </c>
       <c r="B57" t="n">
-        <v>98105</v>
+        <v>91411</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6757,42 +6782,33 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>558372</v>
+        <v>558364</v>
       </c>
       <c r="R57" t="n">
-        <v>6624277</v>
+        <v>6624122</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6819,12 +6835,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6833,6 +6849,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6855,10 +6872,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121394355</v>
+        <v>121394310</v>
       </c>
       <c r="B58" t="n">
-        <v>92193</v>
+        <v>95652</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6871,37 +6888,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2079</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>558377</v>
+        <v>558437</v>
       </c>
       <c r="R58" t="n">
-        <v>6624159</v>
+        <v>6624264</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6928,12 +6942,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6942,24 +6956,8 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AL58" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>undersida av grov ved mot mark # tall</t>
-        </is>
-      </c>
-      <c r="AQ58" t="inlineStr">
-        <is>
-          <t>Ralf Lundmark</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -6980,7 +6978,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121394364</v>
+        <v>121394319</v>
       </c>
       <c r="B59" t="n">
         <v>8435</v>
@@ -7020,10 +7018,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>558351</v>
+        <v>558461</v>
       </c>
       <c r="R59" t="n">
-        <v>6624213</v>
+        <v>6624164</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7050,12 +7048,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7086,10 +7084,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121394270</v>
+        <v>121394325</v>
       </c>
       <c r="B60" t="n">
-        <v>98105</v>
+        <v>5172</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7098,42 +7096,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>558522</v>
+        <v>558478</v>
       </c>
       <c r="R60" t="n">
-        <v>6624290</v>
+        <v>6624257</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7160,12 +7154,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7196,10 +7190,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121394342</v>
+        <v>121394321</v>
       </c>
       <c r="B61" t="n">
-        <v>74654</v>
+        <v>95652</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7208,25 +7202,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7236,10 +7230,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>558435</v>
+        <v>558450</v>
       </c>
       <c r="R61" t="n">
-        <v>6624227</v>
+        <v>6624202</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7266,12 +7260,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7302,10 +7296,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121394494</v>
+        <v>121394303</v>
       </c>
       <c r="B62" t="n">
-        <v>89419</v>
+        <v>98105</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7318,34 +7312,38 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6286</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>558369</v>
+        <v>558385</v>
       </c>
       <c r="R62" t="n">
-        <v>6624121</v>
+        <v>6624276</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7372,12 +7370,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7388,11 +7386,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>tallskog på finmorän</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7519,10 +7512,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121394309</v>
+        <v>121394348</v>
       </c>
       <c r="B64" t="n">
-        <v>95691</v>
+        <v>92027</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7531,25 +7524,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2590</v>
+        <v>1968</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7562,7 +7555,7 @@
         <v>558437</v>
       </c>
       <c r="R64" t="n">
-        <v>6624264</v>
+        <v>6624152</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7589,12 +7582,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7625,10 +7618,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121394314</v>
+        <v>121394343</v>
       </c>
       <c r="B65" t="n">
-        <v>91112</v>
+        <v>74654</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7637,20 +7630,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6040162</v>
+        <v>6426</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7660,10 +7658,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>558428</v>
+        <v>558405</v>
       </c>
       <c r="R65" t="n">
-        <v>6624048</v>
+        <v>6624226</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7698,18 +7696,12 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7732,10 +7724,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121394345</v>
+        <v>121394359</v>
       </c>
       <c r="B66" t="n">
-        <v>97053</v>
+        <v>74654</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7748,19 +7740,23 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221944</v>
+        <v>6426</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7768,10 +7764,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>558386</v>
+        <v>558414</v>
       </c>
       <c r="R66" t="n">
-        <v>6624222</v>
+        <v>6624238</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7798,12 +7794,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7812,7 +7808,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7835,10 +7830,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121394344</v>
+        <v>121394339</v>
       </c>
       <c r="B67" t="n">
-        <v>92008</v>
+        <v>74654</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7851,21 +7846,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4366</v>
+        <v>6426</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7875,10 +7870,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>558407</v>
+        <v>558458</v>
       </c>
       <c r="R67" t="n">
-        <v>6624166</v>
+        <v>6624309</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7941,10 +7936,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121394323</v>
+        <v>121394305</v>
       </c>
       <c r="B68" t="n">
-        <v>5172</v>
+        <v>98105</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7953,38 +7948,42 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>558492</v>
+        <v>558420</v>
       </c>
       <c r="R68" t="n">
-        <v>6624223</v>
+        <v>6624193</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8011,12 +8010,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8047,10 +8046,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121394310</v>
+        <v>121394363</v>
       </c>
       <c r="B69" t="n">
-        <v>95652</v>
+        <v>5172</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8059,25 +8058,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8087,10 +8086,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>558437</v>
+        <v>558367</v>
       </c>
       <c r="R69" t="n">
-        <v>6624264</v>
+        <v>6624219</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8117,12 +8116,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8153,10 +8152,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121394306</v>
+        <v>121394364</v>
       </c>
       <c r="B70" t="n">
-        <v>98105</v>
+        <v>8435</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8165,39 +8164,35 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>558437</v>
+        <v>558351</v>
       </c>
       <c r="R70" t="n">
         <v>6624213</v>
@@ -8227,12 +8222,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8263,10 +8258,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121394324</v>
+        <v>121394306</v>
       </c>
       <c r="B71" t="n">
-        <v>5192</v>
+        <v>98105</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8275,38 +8270,42 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>558478</v>
+        <v>558437</v>
       </c>
       <c r="R71" t="n">
-        <v>6624257</v>
+        <v>6624213</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8333,12 +8332,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8369,10 +8368,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121394351</v>
+        <v>121394345</v>
       </c>
       <c r="B72" t="n">
-        <v>5192</v>
+        <v>97053</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8385,23 +8384,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>105930</v>
+        <v>221944</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8409,10 +8404,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>558363</v>
+        <v>558386</v>
       </c>
       <c r="R72" t="n">
-        <v>6624071</v>
+        <v>6624222</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8453,6 +8448,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8475,10 +8471,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121394548</v>
+        <v>121394353</v>
       </c>
       <c r="B73" t="n">
-        <v>92024</v>
+        <v>4769</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8487,25 +8483,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5449</v>
+        <v>100299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8515,10 +8511,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>558480</v>
+        <v>558363</v>
       </c>
       <c r="R73" t="n">
-        <v>6624122</v>
+        <v>6624071</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8545,12 +8541,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8581,10 +8577,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121394359</v>
+        <v>121394304</v>
       </c>
       <c r="B74" t="n">
-        <v>74654</v>
+        <v>98105</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8593,38 +8589,42 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>558414</v>
+        <v>558372</v>
       </c>
       <c r="R74" t="n">
-        <v>6624238</v>
+        <v>6624277</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8651,12 +8651,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8687,10 +8687,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121394353</v>
+        <v>121394324</v>
       </c>
       <c r="B75" t="n">
-        <v>4769</v>
+        <v>5192</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8703,21 +8703,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8727,10 +8727,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>558363</v>
+        <v>558478</v>
       </c>
       <c r="R75" t="n">
-        <v>6624071</v>
+        <v>6624257</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8793,10 +8793,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121394352</v>
+        <v>121394349</v>
       </c>
       <c r="B76" t="n">
-        <v>5172</v>
+        <v>84305</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8809,21 +8809,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100526</v>
+        <v>3518</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8833,10 +8833,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>558363</v>
+        <v>558419</v>
       </c>
       <c r="R76" t="n">
-        <v>6624071</v>
+        <v>6624081</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -4398,10 +4398,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121394272</v>
+        <v>121394350</v>
       </c>
       <c r="B35" t="n">
-        <v>58221</v>
+        <v>94770</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4414,43 +4414,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>208242</v>
+        <v>2170</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558519</v>
+        <v>558402</v>
       </c>
       <c r="R35" t="n">
-        <v>6624313</v>
+        <v>6624073</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4477,17 +4468,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>under ved i barrskog</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4518,10 +4504,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121394350</v>
+        <v>121394272</v>
       </c>
       <c r="B36" t="n">
-        <v>94770</v>
+        <v>58221</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4534,34 +4520,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2170</v>
+        <v>208242</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558402</v>
+        <v>558519</v>
       </c>
       <c r="R36" t="n">
-        <v>6624073</v>
+        <v>6624313</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4588,12 +4583,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>under ved i barrskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -6128,10 +6128,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121394342</v>
+        <v>121394333</v>
       </c>
       <c r="B51" t="n">
-        <v>74654</v>
+        <v>95652</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6140,25 +6140,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>558435</v>
+        <v>558528</v>
       </c>
       <c r="R51" t="n">
-        <v>6624227</v>
+        <v>6624316</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6234,10 +6234,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121394494</v>
+        <v>121394314</v>
       </c>
       <c r="B52" t="n">
-        <v>89419</v>
+        <v>91112</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6246,25 +6246,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6286</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Torrmusseron</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6274,10 +6269,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>558369</v>
+        <v>558428</v>
       </c>
       <c r="R52" t="n">
-        <v>6624121</v>
+        <v>6624048</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6304,12 +6299,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6318,13 +6318,9 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>tallskog på finmorän</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6345,10 +6341,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121394333</v>
+        <v>121394342</v>
       </c>
       <c r="B53" t="n">
-        <v>95652</v>
+        <v>74654</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6357,25 +6353,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6385,10 +6381,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>558528</v>
+        <v>558435</v>
       </c>
       <c r="R53" t="n">
-        <v>6624316</v>
+        <v>6624227</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6451,10 +6447,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121394323</v>
+        <v>121394494</v>
       </c>
       <c r="B54" t="n">
-        <v>5172</v>
+        <v>89419</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6463,25 +6459,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100526</v>
+        <v>6286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6491,10 +6487,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>558492</v>
+        <v>558369</v>
       </c>
       <c r="R54" t="n">
-        <v>6624223</v>
+        <v>6624121</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6521,12 +6517,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6537,6 +6533,11 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>tallskog på finmorän</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6557,10 +6558,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121394314</v>
+        <v>121394323</v>
       </c>
       <c r="B55" t="n">
-        <v>91112</v>
+        <v>5172</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6569,20 +6570,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6040162</v>
+        <v>100526</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6592,10 +6598,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>558428</v>
+        <v>558492</v>
       </c>
       <c r="R55" t="n">
-        <v>6624048</v>
+        <v>6624223</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6630,18 +6636,12 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6872,10 +6872,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121394310</v>
+        <v>121394319</v>
       </c>
       <c r="B58" t="n">
-        <v>95652</v>
+        <v>8435</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6884,25 +6884,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6912,10 +6912,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>558437</v>
+        <v>558461</v>
       </c>
       <c r="R58" t="n">
-        <v>6624264</v>
+        <v>6624164</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6942,12 +6942,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6978,10 +6978,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121394319</v>
+        <v>121394310</v>
       </c>
       <c r="B59" t="n">
-        <v>8435</v>
+        <v>95652</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6990,25 +6990,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>558461</v>
+        <v>558437</v>
       </c>
       <c r="R59" t="n">
-        <v>6624164</v>
+        <v>6624264</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7048,12 +7048,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD59" t="b">

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -4398,10 +4398,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121394350</v>
+        <v>121394272</v>
       </c>
       <c r="B35" t="n">
-        <v>94770</v>
+        <v>58221</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4414,34 +4414,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2170</v>
+        <v>208242</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558402</v>
+        <v>558519</v>
       </c>
       <c r="R35" t="n">
-        <v>6624073</v>
+        <v>6624313</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4468,12 +4477,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>under ved i barrskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4504,10 +4518,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121394272</v>
+        <v>121394350</v>
       </c>
       <c r="B36" t="n">
-        <v>58221</v>
+        <v>94770</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4520,43 +4534,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>208242</v>
+        <v>2170</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558519</v>
+        <v>558402</v>
       </c>
       <c r="R36" t="n">
-        <v>6624313</v>
+        <v>6624073</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4583,17 +4588,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>under ved i barrskog</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -6128,10 +6128,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121394333</v>
+        <v>121394342</v>
       </c>
       <c r="B51" t="n">
-        <v>95652</v>
+        <v>74654</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6140,25 +6140,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>558528</v>
+        <v>558435</v>
       </c>
       <c r="R51" t="n">
-        <v>6624316</v>
+        <v>6624227</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6234,10 +6234,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121394314</v>
+        <v>121394494</v>
       </c>
       <c r="B52" t="n">
-        <v>91112</v>
+        <v>89419</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6246,20 +6246,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6040162</v>
+        <v>6286</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6269,10 +6274,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>558428</v>
+        <v>558369</v>
       </c>
       <c r="R52" t="n">
-        <v>6624048</v>
+        <v>6624121</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6299,17 +6304,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6318,9 +6318,13 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>tallskog på finmorän</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6341,10 +6345,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121394342</v>
+        <v>121394333</v>
       </c>
       <c r="B53" t="n">
-        <v>74654</v>
+        <v>95652</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6353,25 +6357,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6381,10 +6385,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>558435</v>
+        <v>558528</v>
       </c>
       <c r="R53" t="n">
-        <v>6624227</v>
+        <v>6624316</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6447,10 +6451,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121394494</v>
+        <v>121394323</v>
       </c>
       <c r="B54" t="n">
-        <v>89419</v>
+        <v>5172</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6459,25 +6463,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6286</v>
+        <v>100526</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6487,10 +6491,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>558369</v>
+        <v>558492</v>
       </c>
       <c r="R54" t="n">
-        <v>6624121</v>
+        <v>6624223</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6517,12 +6521,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6533,11 +6537,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>tallskog på finmorän</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6558,10 +6557,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121394323</v>
+        <v>121394314</v>
       </c>
       <c r="B55" t="n">
-        <v>5172</v>
+        <v>91112</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6570,25 +6569,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6598,10 +6592,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>558492</v>
+        <v>558428</v>
       </c>
       <c r="R55" t="n">
-        <v>6624223</v>
+        <v>6624048</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6636,12 +6630,18 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6872,10 +6872,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121394319</v>
+        <v>121394310</v>
       </c>
       <c r="B58" t="n">
-        <v>8435</v>
+        <v>95652</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6884,25 +6884,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6912,10 +6912,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>558461</v>
+        <v>558437</v>
       </c>
       <c r="R58" t="n">
-        <v>6624164</v>
+        <v>6624264</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6942,12 +6942,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6978,10 +6978,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121394310</v>
+        <v>121394319</v>
       </c>
       <c r="B59" t="n">
-        <v>95652</v>
+        <v>8435</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6990,25 +6990,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>558437</v>
+        <v>558461</v>
       </c>
       <c r="R59" t="n">
-        <v>6624264</v>
+        <v>6624164</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7048,12 +7048,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8577,10 +8577,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121394304</v>
+        <v>121394349</v>
       </c>
       <c r="B74" t="n">
-        <v>98105</v>
+        <v>84305</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8589,42 +8589,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>3518</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>558372</v>
+        <v>558419</v>
       </c>
       <c r="R74" t="n">
-        <v>6624277</v>
+        <v>6624081</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8651,12 +8647,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8687,10 +8683,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121394324</v>
+        <v>121394304</v>
       </c>
       <c r="B75" t="n">
-        <v>5192</v>
+        <v>98105</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8699,38 +8695,42 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>558478</v>
+        <v>558372</v>
       </c>
       <c r="R75" t="n">
-        <v>6624257</v>
+        <v>6624277</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8757,12 +8757,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8793,10 +8793,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121394349</v>
+        <v>121394324</v>
       </c>
       <c r="B76" t="n">
-        <v>84305</v>
+        <v>5192</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8809,21 +8809,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>3518</v>
+        <v>105930</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8833,10 +8833,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>558419</v>
+        <v>558478</v>
       </c>
       <c r="R76" t="n">
-        <v>6624081</v>
+        <v>6624257</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -2069,10 +2069,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121359471</v>
+        <v>121359461</v>
       </c>
       <c r="B13" t="n">
-        <v>95652</v>
+        <v>79234</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2085,21 +2085,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2109,10 +2109,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558521</v>
+        <v>558352</v>
       </c>
       <c r="R13" t="n">
-        <v>6624319</v>
+        <v>6624226</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121359469</v>
+        <v>121359460</v>
       </c>
       <c r="B14" t="n">
-        <v>90720</v>
+        <v>8436</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2187,25 +2187,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558491</v>
+        <v>558352</v>
       </c>
       <c r="R14" t="n">
-        <v>6624274</v>
+        <v>6624226</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2281,10 +2281,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121359444</v>
+        <v>121359443</v>
       </c>
       <c r="B15" t="n">
-        <v>92029</v>
+        <v>90742</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2293,41 +2293,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558433</v>
+        <v>558441</v>
       </c>
       <c r="R15" t="n">
-        <v>6624286</v>
+        <v>6624265</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2368,7 +2365,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2394,7 +2390,7 @@
         <v>121359467</v>
       </c>
       <c r="B16" t="n">
-        <v>90937</v>
+        <v>90945</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2497,10 +2493,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121359462</v>
+        <v>121359466</v>
       </c>
       <c r="B17" t="n">
-        <v>90924</v>
+        <v>90693</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2509,25 +2505,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1106</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2537,10 +2533,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558376</v>
+        <v>558467</v>
       </c>
       <c r="R17" t="n">
-        <v>6624261</v>
+        <v>6624274</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2603,10 +2599,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121359506</v>
+        <v>121359459</v>
       </c>
       <c r="B18" t="n">
-        <v>8435</v>
+        <v>79234</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2615,25 +2611,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2643,10 +2639,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558352</v>
+        <v>558364</v>
       </c>
       <c r="R18" t="n">
-        <v>6624128</v>
+        <v>6624216</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2709,10 +2705,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121359465</v>
+        <v>121359506</v>
       </c>
       <c r="B19" t="n">
-        <v>91112</v>
+        <v>8436</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2721,20 +2717,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6040162</v>
+        <v>106545</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2744,10 +2745,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558460</v>
+        <v>558352</v>
       </c>
       <c r="R19" t="n">
-        <v>6624272</v>
+        <v>6624128</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2788,7 +2789,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2811,10 +2811,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121359459</v>
+        <v>121359465</v>
       </c>
       <c r="B20" t="n">
-        <v>79227</v>
+        <v>91120</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2827,21 +2827,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2851,10 +2846,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558364</v>
+        <v>558460</v>
       </c>
       <c r="R20" t="n">
-        <v>6624216</v>
+        <v>6624272</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2895,6 +2890,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2917,10 +2913,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121359461</v>
+        <v>121359469</v>
       </c>
       <c r="B21" t="n">
-        <v>79227</v>
+        <v>90728</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2933,21 +2929,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2957,10 +2953,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558352</v>
+        <v>558491</v>
       </c>
       <c r="R21" t="n">
-        <v>6624226</v>
+        <v>6624274</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3023,10 +3019,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121359460</v>
+        <v>121359457</v>
       </c>
       <c r="B22" t="n">
-        <v>8435</v>
+        <v>92032</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3035,25 +3031,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>5449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3063,10 +3059,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558352</v>
+        <v>558395</v>
       </c>
       <c r="R22" t="n">
-        <v>6624226</v>
+        <v>6624316</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3129,10 +3125,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121359443</v>
+        <v>121359471</v>
       </c>
       <c r="B23" t="n">
-        <v>90734</v>
+        <v>95660</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3145,21 +3141,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3169,10 +3165,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558441</v>
+        <v>558521</v>
       </c>
       <c r="R23" t="n">
-        <v>6624265</v>
+        <v>6624319</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3235,10 +3231,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121359466</v>
+        <v>121359458</v>
       </c>
       <c r="B24" t="n">
-        <v>90685</v>
+        <v>92030</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3247,25 +3243,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>5448</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3275,10 +3271,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558467</v>
+        <v>558350</v>
       </c>
       <c r="R24" t="n">
-        <v>6624274</v>
+        <v>6624211</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3341,10 +3337,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121359457</v>
+        <v>121359462</v>
       </c>
       <c r="B25" t="n">
-        <v>92024</v>
+        <v>90932</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3353,25 +3349,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>1106</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3381,10 +3377,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558395</v>
+        <v>558376</v>
       </c>
       <c r="R25" t="n">
-        <v>6624316</v>
+        <v>6624261</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3447,10 +3443,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121359458</v>
+        <v>121359444</v>
       </c>
       <c r="B26" t="n">
-        <v>92022</v>
+        <v>92037</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3459,38 +3455,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5448</v>
+        <v>5964</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558350</v>
+        <v>558433</v>
       </c>
       <c r="R26" t="n">
-        <v>6624211</v>
+        <v>6624286</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3531,6 +3530,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121394932</v>
+        <v>121394549</v>
       </c>
       <c r="B27" t="n">
-        <v>91112</v>
+        <v>92030</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3569,16 +3569,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6040162</v>
+        <v>5448</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3588,10 +3593,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558394</v>
+        <v>558468</v>
       </c>
       <c r="R27" t="n">
-        <v>6624091</v>
+        <v>6624096</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3618,12 +3623,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3632,7 +3637,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3655,10 +3659,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121394934</v>
+        <v>121394945</v>
       </c>
       <c r="B28" t="n">
-        <v>95652</v>
+        <v>95660</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3695,10 +3699,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558377</v>
+        <v>558441</v>
       </c>
       <c r="R28" t="n">
-        <v>6624106</v>
+        <v>6624265</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3761,10 +3765,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121394942</v>
+        <v>121394932</v>
       </c>
       <c r="B29" t="n">
-        <v>95968</v>
+        <v>91120</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3773,25 +3777,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>990</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Liten hornflikmossa</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3801,10 +3800,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558390</v>
+        <v>558394</v>
       </c>
       <c r="R29" t="n">
-        <v>6624295</v>
+        <v>6624091</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3871,7 +3870,7 @@
         <v>121394933</v>
       </c>
       <c r="B30" t="n">
-        <v>8435</v>
+        <v>8436</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3974,10 +3973,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121394549</v>
+        <v>121394943</v>
       </c>
       <c r="B31" t="n">
-        <v>92022</v>
+        <v>95660</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3990,21 +3989,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5448</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4014,10 +4013,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558468</v>
+        <v>558390</v>
       </c>
       <c r="R31" t="n">
-        <v>6624096</v>
+        <v>6624295</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4044,12 +4043,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4080,10 +4079,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121394945</v>
+        <v>121394942</v>
       </c>
       <c r="B32" t="n">
-        <v>95652</v>
+        <v>95976</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4092,25 +4091,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>990</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4120,10 +4119,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558441</v>
+        <v>558390</v>
       </c>
       <c r="R32" t="n">
-        <v>6624265</v>
+        <v>6624295</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4164,6 +4163,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4189,7 +4189,7 @@
         <v>121394944</v>
       </c>
       <c r="B33" t="n">
-        <v>90685</v>
+        <v>90693</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4292,10 +4292,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121394943</v>
+        <v>121394934</v>
       </c>
       <c r="B34" t="n">
-        <v>95652</v>
+        <v>95660</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4332,10 +4332,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558390</v>
+        <v>558377</v>
       </c>
       <c r="R34" t="n">
-        <v>6624295</v>
+        <v>6624106</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4398,10 +4398,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121394272</v>
+        <v>121394310</v>
       </c>
       <c r="B35" t="n">
-        <v>58221</v>
+        <v>95660</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4410,47 +4410,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>208242</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>558519</v>
+        <v>558437</v>
       </c>
       <c r="R35" t="n">
-        <v>6624313</v>
+        <v>6624264</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4483,11 +4474,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>under ved i barrskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4518,10 +4504,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121394350</v>
+        <v>121394363</v>
       </c>
       <c r="B36" t="n">
-        <v>94770</v>
+        <v>5173</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4534,21 +4520,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2170</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4558,10 +4544,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558402</v>
+        <v>558367</v>
       </c>
       <c r="R36" t="n">
-        <v>6624073</v>
+        <v>6624219</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4588,12 +4574,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4624,10 +4610,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121394320</v>
+        <v>121394333</v>
       </c>
       <c r="B37" t="n">
-        <v>89769</v>
+        <v>95660</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4640,21 +4626,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1962</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4664,10 +4650,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558465</v>
+        <v>558528</v>
       </c>
       <c r="R37" t="n">
-        <v>6624192</v>
+        <v>6624316</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4694,12 +4680,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4730,10 +4716,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121394351</v>
+        <v>121394352</v>
       </c>
       <c r="B38" t="n">
-        <v>5192</v>
+        <v>5173</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4746,21 +4732,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4836,10 +4822,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121394309</v>
+        <v>121394548</v>
       </c>
       <c r="B39" t="n">
-        <v>95691</v>
+        <v>92032</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4848,25 +4834,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2590</v>
+        <v>5449</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4876,10 +4862,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558437</v>
+        <v>558480</v>
       </c>
       <c r="R39" t="n">
-        <v>6624264</v>
+        <v>6624122</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4906,12 +4892,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4942,10 +4928,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121394357</v>
+        <v>121394304</v>
       </c>
       <c r="B40" t="n">
-        <v>95399</v>
+        <v>98113</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4954,38 +4940,42 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558396</v>
+        <v>558372</v>
       </c>
       <c r="R40" t="n">
-        <v>6624233</v>
+        <v>6624277</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5012,12 +5002,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5048,10 +5038,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121394352</v>
+        <v>121394357</v>
       </c>
       <c r="B41" t="n">
-        <v>5172</v>
+        <v>95407</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5064,21 +5054,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100526</v>
+        <v>2869</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5088,10 +5078,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558363</v>
+        <v>558396</v>
       </c>
       <c r="R41" t="n">
-        <v>6624071</v>
+        <v>6624233</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5118,12 +5108,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5154,10 +5144,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121394315</v>
+        <v>121394343</v>
       </c>
       <c r="B42" t="n">
-        <v>91980</v>
+        <v>74661</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5166,25 +5156,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6055</v>
+        <v>6426</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5194,10 +5184,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558428</v>
+        <v>558405</v>
       </c>
       <c r="R42" t="n">
-        <v>6624044</v>
+        <v>6624226</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5224,12 +5214,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5260,10 +5250,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121394313</v>
+        <v>121394320</v>
       </c>
       <c r="B43" t="n">
-        <v>91113</v>
+        <v>89776</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5276,16 +5266,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6040186</v>
+        <v>1962</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5295,10 +5290,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558412</v>
+        <v>558465</v>
       </c>
       <c r="R43" t="n">
-        <v>6624060</v>
+        <v>6624192</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5325,17 +5320,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5344,7 +5334,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5367,10 +5356,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121394322</v>
+        <v>121394327</v>
       </c>
       <c r="B44" t="n">
-        <v>5192</v>
+        <v>90742</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5379,25 +5368,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>105930</v>
+        <v>1204</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5407,10 +5396,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558492</v>
+        <v>558466</v>
       </c>
       <c r="R44" t="n">
-        <v>6624223</v>
+        <v>6624295</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5473,10 +5462,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121394548</v>
+        <v>121394324</v>
       </c>
       <c r="B45" t="n">
-        <v>92024</v>
+        <v>5193</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5485,25 +5474,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5449</v>
+        <v>105930</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5513,10 +5502,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>558480</v>
+        <v>558478</v>
       </c>
       <c r="R45" t="n">
-        <v>6624122</v>
+        <v>6624257</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5543,12 +5532,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5579,10 +5568,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121394355</v>
+        <v>121394349</v>
       </c>
       <c r="B46" t="n">
-        <v>92193</v>
+        <v>84312</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5591,41 +5580,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2079</v>
+        <v>3518</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558377</v>
+        <v>558419</v>
       </c>
       <c r="R46" t="n">
-        <v>6624159</v>
+        <v>6624081</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5652,12 +5638,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5666,24 +5652,8 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>undersida av grov ved mot mark # tall</t>
-        </is>
-      </c>
-      <c r="AQ46" t="inlineStr">
-        <is>
-          <t>Ralf Lundmark</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5704,10 +5674,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121394365</v>
+        <v>121394342</v>
       </c>
       <c r="B47" t="n">
-        <v>91112</v>
+        <v>74661</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5716,20 +5686,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6040162</v>
+        <v>6426</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5739,10 +5714,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558351</v>
+        <v>558435</v>
       </c>
       <c r="R47" t="n">
-        <v>6624213</v>
+        <v>6624227</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5769,12 +5744,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5783,7 +5758,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5806,10 +5780,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121394327</v>
+        <v>121394351</v>
       </c>
       <c r="B48" t="n">
-        <v>90734</v>
+        <v>5193</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5818,25 +5792,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1204</v>
+        <v>105930</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5846,10 +5820,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>558466</v>
+        <v>558363</v>
       </c>
       <c r="R48" t="n">
-        <v>6624295</v>
+        <v>6624071</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5912,10 +5886,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121394270</v>
+        <v>121394325</v>
       </c>
       <c r="B49" t="n">
-        <v>98105</v>
+        <v>5173</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5924,42 +5898,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558522</v>
+        <v>558478</v>
       </c>
       <c r="R49" t="n">
-        <v>6624290</v>
+        <v>6624257</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5986,12 +5956,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6022,10 +5992,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121394354</v>
+        <v>121394309</v>
       </c>
       <c r="B50" t="n">
-        <v>86299</v>
+        <v>95699</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6034,25 +6004,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3739</v>
+        <v>2590</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6062,10 +6032,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>558390</v>
+        <v>558437</v>
       </c>
       <c r="R50" t="n">
-        <v>6624037</v>
+        <v>6624264</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6092,12 +6062,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6128,10 +6098,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121394342</v>
+        <v>121394344</v>
       </c>
       <c r="B51" t="n">
-        <v>74654</v>
+        <v>92016</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6144,21 +6114,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6426</v>
+        <v>4366</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6168,10 +6138,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>558435</v>
+        <v>558407</v>
       </c>
       <c r="R51" t="n">
-        <v>6624227</v>
+        <v>6624166</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6237,7 +6207,7 @@
         <v>121394494</v>
       </c>
       <c r="B52" t="n">
-        <v>89419</v>
+        <v>89426</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6345,10 +6315,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121394333</v>
+        <v>121394365</v>
       </c>
       <c r="B53" t="n">
-        <v>95652</v>
+        <v>91120</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6361,21 +6331,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>53</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6385,10 +6350,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>558528</v>
+        <v>558351</v>
       </c>
       <c r="R53" t="n">
-        <v>6624316</v>
+        <v>6624213</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6415,12 +6380,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6429,6 +6394,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6451,10 +6417,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121394323</v>
+        <v>121394348</v>
       </c>
       <c r="B54" t="n">
-        <v>5172</v>
+        <v>92035</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6463,25 +6429,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100526</v>
+        <v>1968</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6491,10 +6457,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>558492</v>
+        <v>558437</v>
       </c>
       <c r="R54" t="n">
-        <v>6624223</v>
+        <v>6624152</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6557,10 +6523,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121394314</v>
+        <v>121394323</v>
       </c>
       <c r="B55" t="n">
-        <v>91112</v>
+        <v>5173</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6569,20 +6535,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6040162</v>
+        <v>100526</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6592,10 +6563,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>558428</v>
+        <v>558492</v>
       </c>
       <c r="R55" t="n">
-        <v>6624048</v>
+        <v>6624223</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6630,18 +6601,12 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6664,10 +6629,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121394344</v>
+        <v>121394303</v>
       </c>
       <c r="B56" t="n">
-        <v>92008</v>
+        <v>98113</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6676,38 +6641,42 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>558407</v>
+        <v>558385</v>
       </c>
       <c r="R56" t="n">
-        <v>6624166</v>
+        <v>6624276</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6734,12 +6703,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6770,10 +6739,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121394356</v>
+        <v>121394313</v>
       </c>
       <c r="B57" t="n">
-        <v>91411</v>
+        <v>91121</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6786,16 +6755,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>757</v>
+        <v>6040186</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6805,10 +6774,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>558364</v>
+        <v>558412</v>
       </c>
       <c r="R57" t="n">
-        <v>6624122</v>
+        <v>6624060</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6835,12 +6804,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6872,10 +6846,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121394310</v>
+        <v>121394345</v>
       </c>
       <c r="B58" t="n">
-        <v>95652</v>
+        <v>97061</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6884,27 +6858,23 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>221944</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6912,10 +6882,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>558437</v>
+        <v>558386</v>
       </c>
       <c r="R58" t="n">
-        <v>6624264</v>
+        <v>6624222</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6942,12 +6912,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6956,6 +6926,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6978,10 +6949,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121394319</v>
+        <v>121394322</v>
       </c>
       <c r="B59" t="n">
-        <v>8435</v>
+        <v>5193</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6994,21 +6965,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7018,10 +6989,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>558461</v>
+        <v>558492</v>
       </c>
       <c r="R59" t="n">
-        <v>6624164</v>
+        <v>6624223</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7048,12 +7019,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7084,10 +7055,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121394325</v>
+        <v>121394364</v>
       </c>
       <c r="B60" t="n">
-        <v>5172</v>
+        <v>8436</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7100,21 +7071,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7124,10 +7095,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>558478</v>
+        <v>558351</v>
       </c>
       <c r="R60" t="n">
-        <v>6624257</v>
+        <v>6624213</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7154,12 +7125,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7190,10 +7161,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121394321</v>
+        <v>121394359</v>
       </c>
       <c r="B61" t="n">
-        <v>95652</v>
+        <v>74661</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7202,25 +7173,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7230,10 +7201,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>558450</v>
+        <v>558414</v>
       </c>
       <c r="R61" t="n">
-        <v>6624202</v>
+        <v>6624238</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7260,12 +7231,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7296,10 +7267,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121394303</v>
+        <v>121394321</v>
       </c>
       <c r="B62" t="n">
-        <v>98105</v>
+        <v>95660</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7308,42 +7279,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>558385</v>
+        <v>558450</v>
       </c>
       <c r="R62" t="n">
-        <v>6624276</v>
+        <v>6624202</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7370,12 +7337,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7406,10 +7373,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121394326</v>
+        <v>121394306</v>
       </c>
       <c r="B63" t="n">
-        <v>4769</v>
+        <v>98113</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7418,38 +7385,42 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>558478</v>
+        <v>558437</v>
       </c>
       <c r="R63" t="n">
-        <v>6624257</v>
+        <v>6624213</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7476,12 +7447,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7512,10 +7483,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121394348</v>
+        <v>121394314</v>
       </c>
       <c r="B64" t="n">
-        <v>92027</v>
+        <v>91120</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7528,21 +7499,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1968</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Grantaggsvamp</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7552,10 +7518,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>558437</v>
+        <v>558428</v>
       </c>
       <c r="R64" t="n">
-        <v>6624152</v>
+        <v>6624048</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7590,12 +7556,18 @@
           <t>2024-10-03</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7618,10 +7590,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121394343</v>
+        <v>121394339</v>
       </c>
       <c r="B65" t="n">
-        <v>74654</v>
+        <v>74661</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7658,10 +7630,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>558405</v>
+        <v>558458</v>
       </c>
       <c r="R65" t="n">
-        <v>6624226</v>
+        <v>6624309</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7724,10 +7696,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121394359</v>
+        <v>121394315</v>
       </c>
       <c r="B66" t="n">
-        <v>74654</v>
+        <v>91988</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7736,25 +7708,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6426</v>
+        <v>6055</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7764,10 +7736,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>558414</v>
+        <v>558428</v>
       </c>
       <c r="R66" t="n">
-        <v>6624238</v>
+        <v>6624044</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7794,12 +7766,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7830,10 +7802,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121394339</v>
+        <v>121394354</v>
       </c>
       <c r="B67" t="n">
-        <v>74654</v>
+        <v>86306</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7842,25 +7814,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6426</v>
+        <v>3739</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7870,10 +7842,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>558458</v>
+        <v>558390</v>
       </c>
       <c r="R67" t="n">
-        <v>6624309</v>
+        <v>6624037</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7936,10 +7908,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121394305</v>
+        <v>121394353</v>
       </c>
       <c r="B68" t="n">
-        <v>98105</v>
+        <v>4770</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7948,42 +7920,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>558420</v>
+        <v>558363</v>
       </c>
       <c r="R68" t="n">
-        <v>6624193</v>
+        <v>6624071</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8010,12 +7978,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8046,10 +8014,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121394363</v>
+        <v>121394305</v>
       </c>
       <c r="B69" t="n">
-        <v>5172</v>
+        <v>98113</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8058,38 +8026,42 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>558367</v>
+        <v>558420</v>
       </c>
       <c r="R69" t="n">
-        <v>6624219</v>
+        <v>6624193</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8116,12 +8088,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8152,10 +8124,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121394364</v>
+        <v>121394355</v>
       </c>
       <c r="B70" t="n">
-        <v>8435</v>
+        <v>92201</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8164,38 +8136,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>558351</v>
+        <v>558377</v>
       </c>
       <c r="R70" t="n">
-        <v>6624213</v>
+        <v>6624159</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8236,8 +8211,24 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AL70" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>undersida av grov ved mot mark # tall</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8258,10 +8249,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121394306</v>
+        <v>121394326</v>
       </c>
       <c r="B71" t="n">
-        <v>98105</v>
+        <v>4770</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8270,42 +8261,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>558437</v>
+        <v>558478</v>
       </c>
       <c r="R71" t="n">
-        <v>6624213</v>
+        <v>6624257</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8332,12 +8319,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8368,10 +8355,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121394345</v>
+        <v>121394272</v>
       </c>
       <c r="B72" t="n">
-        <v>97053</v>
+        <v>58224</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8384,30 +8371,43 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221944</v>
+        <v>208242</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>558386</v>
+        <v>558519</v>
       </c>
       <c r="R72" t="n">
-        <v>6624222</v>
+        <v>6624313</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8434,12 +8434,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>under ved i barrskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8448,7 +8453,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8471,10 +8475,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121394353</v>
+        <v>121394350</v>
       </c>
       <c r="B73" t="n">
-        <v>4769</v>
+        <v>94778</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8487,21 +8491,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100299</v>
+        <v>2170</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8511,10 +8515,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>558363</v>
+        <v>558402</v>
       </c>
       <c r="R73" t="n">
-        <v>6624071</v>
+        <v>6624073</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8577,10 +8581,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121394349</v>
+        <v>121394356</v>
       </c>
       <c r="B74" t="n">
-        <v>84305</v>
+        <v>91419</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8589,25 +8593,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3518</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Smal svampklubba</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8617,10 +8616,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>558419</v>
+        <v>558364</v>
       </c>
       <c r="R74" t="n">
-        <v>6624081</v>
+        <v>6624122</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8647,12 +8646,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8661,6 +8660,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8683,10 +8683,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121394304</v>
+        <v>121394319</v>
       </c>
       <c r="B75" t="n">
-        <v>98105</v>
+        <v>8436</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8695,42 +8695,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>558372</v>
+        <v>558461</v>
       </c>
       <c r="R75" t="n">
-        <v>6624277</v>
+        <v>6624164</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8757,12 +8753,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8793,10 +8789,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121394324</v>
+        <v>121394270</v>
       </c>
       <c r="B76" t="n">
-        <v>5192</v>
+        <v>98113</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8805,38 +8801,42 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>558478</v>
+        <v>558522</v>
       </c>
       <c r="R76" t="n">
-        <v>6624257</v>
+        <v>6624290</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD76" t="b">

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -4504,10 +4504,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121394363</v>
+        <v>121394333</v>
       </c>
       <c r="B36" t="n">
-        <v>5173</v>
+        <v>95660</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4516,25 +4516,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558367</v>
+        <v>558528</v>
       </c>
       <c r="R36" t="n">
-        <v>6624219</v>
+        <v>6624316</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4574,12 +4574,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4610,10 +4610,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121394333</v>
+        <v>121394363</v>
       </c>
       <c r="B37" t="n">
-        <v>95660</v>
+        <v>5173</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4622,25 +4622,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558528</v>
+        <v>558367</v>
       </c>
       <c r="R37" t="n">
-        <v>6624316</v>
+        <v>6624219</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4680,12 +4680,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -7802,10 +7802,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121394354</v>
+        <v>121394305</v>
       </c>
       <c r="B67" t="n">
-        <v>86306</v>
+        <v>98113</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7814,38 +7814,42 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3739</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Quél.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>558390</v>
+        <v>558420</v>
       </c>
       <c r="R67" t="n">
-        <v>6624037</v>
+        <v>6624193</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7872,12 +7876,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7908,10 +7912,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121394353</v>
+        <v>121394354</v>
       </c>
       <c r="B68" t="n">
-        <v>4770</v>
+        <v>86306</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7920,25 +7924,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100299</v>
+        <v>3739</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7948,10 +7952,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>558363</v>
+        <v>558390</v>
       </c>
       <c r="R68" t="n">
-        <v>6624071</v>
+        <v>6624037</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8014,10 +8018,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121394305</v>
+        <v>121394353</v>
       </c>
       <c r="B69" t="n">
-        <v>98113</v>
+        <v>4770</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8026,42 +8030,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>558420</v>
+        <v>558363</v>
       </c>
       <c r="R69" t="n">
-        <v>6624193</v>
+        <v>6624071</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8088,12 +8088,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD69" t="b">

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -4504,10 +4504,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121394333</v>
+        <v>121394363</v>
       </c>
       <c r="B36" t="n">
-        <v>95660</v>
+        <v>5173</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4516,25 +4516,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558528</v>
+        <v>558367</v>
       </c>
       <c r="R36" t="n">
-        <v>6624316</v>
+        <v>6624219</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4574,12 +4574,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4610,10 +4610,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121394363</v>
+        <v>121394333</v>
       </c>
       <c r="B37" t="n">
-        <v>5173</v>
+        <v>95660</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4622,25 +4622,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4650,10 +4650,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558367</v>
+        <v>558528</v>
       </c>
       <c r="R37" t="n">
-        <v>6624219</v>
+        <v>6624316</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4680,12 +4680,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -7373,10 +7373,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121394306</v>
+        <v>121394339</v>
       </c>
       <c r="B63" t="n">
-        <v>98113</v>
+        <v>74661</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7385,42 +7385,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>558437</v>
+        <v>558458</v>
       </c>
       <c r="R63" t="n">
-        <v>6624213</v>
+        <v>6624309</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7447,12 +7443,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7483,10 +7479,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121394314</v>
+        <v>121394315</v>
       </c>
       <c r="B64" t="n">
-        <v>91120</v>
+        <v>91988</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7495,20 +7491,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6040162</v>
+        <v>6055</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Spadskinn</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7521,7 +7522,7 @@
         <v>558428</v>
       </c>
       <c r="R64" t="n">
-        <v>6624048</v>
+        <v>6624044</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7548,17 +7549,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7567,7 +7563,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7590,10 +7585,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121394339</v>
+        <v>121394306</v>
       </c>
       <c r="B65" t="n">
-        <v>74661</v>
+        <v>98113</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7602,38 +7597,42 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>558458</v>
+        <v>558437</v>
       </c>
       <c r="R65" t="n">
-        <v>6624309</v>
+        <v>6624213</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7660,12 +7659,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7696,10 +7695,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121394315</v>
+        <v>121394314</v>
       </c>
       <c r="B66" t="n">
-        <v>91988</v>
+        <v>91120</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7708,25 +7707,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6055</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Spadskinn</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7739,7 +7733,7 @@
         <v>558428</v>
       </c>
       <c r="R66" t="n">
-        <v>6624044</v>
+        <v>6624048</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7766,12 +7760,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7780,6 +7779,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8794,6 +8794,113 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>127436389</v>
+      </c>
+      <c r="B76" t="n">
+        <v>100857</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Syd Bosjön, Usträngsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>558432</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6624277</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Äldre barrskog påverkad av rörligt markvatten</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Jacob Rudhe, Mårten Berglind, Carl Hanson, Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -8799,7 +8799,7 @@
         <v>127436389</v>
       </c>
       <c r="B76" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -8799,7 +8799,7 @@
         <v>127436389</v>
       </c>
       <c r="B76" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -8799,7 +8799,7 @@
         <v>127436389</v>
       </c>
       <c r="B76" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -8799,7 +8799,7 @@
         <v>127436389</v>
       </c>
       <c r="B76" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -8799,7 +8799,7 @@
         <v>127436389</v>
       </c>
       <c r="B76" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -8799,7 +8799,7 @@
         <v>127436389</v>
       </c>
       <c r="B76" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -8799,7 +8799,7 @@
         <v>127436389</v>
       </c>
       <c r="B76" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -8799,7 +8799,7 @@
         <v>127436389</v>
       </c>
       <c r="B76" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -8799,7 +8799,7 @@
         <v>127436389</v>
       </c>
       <c r="B76" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -8799,7 +8799,7 @@
         <v>127436389</v>
       </c>
       <c r="B76" t="n">
-        <v>100913</v>
+        <v>100916</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -8799,7 +8799,7 @@
         <v>127436389</v>
       </c>
       <c r="B76" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -8799,7 +8799,7 @@
         <v>127436389</v>
       </c>
       <c r="B76" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -8799,7 +8799,7 @@
         <v>127436389</v>
       </c>
       <c r="B76" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AY77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5264,10 +5264,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121394333</v>
+        <v>121394345</v>
       </c>
       <c r="B43" t="n">
-        <v>95660</v>
+        <v>97061</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5276,27 +5276,23 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>221944</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5304,10 +5300,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558528</v>
+        <v>558386</v>
       </c>
       <c r="R43" t="n">
-        <v>6624316</v>
+        <v>6624222</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5348,6 +5344,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5370,10 +5367,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121394356</v>
+        <v>121394333</v>
       </c>
       <c r="B44" t="n">
-        <v>91419</v>
+        <v>95660</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5386,16 +5383,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>757</v>
+        <v>53</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5405,10 +5407,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558364</v>
+        <v>558528</v>
       </c>
       <c r="R44" t="n">
-        <v>6624122</v>
+        <v>6624316</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5435,12 +5437,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5449,7 +5451,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5472,10 +5473,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121394325</v>
+        <v>121394356</v>
       </c>
       <c r="B45" t="n">
-        <v>5173</v>
+        <v>91419</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5484,25 +5485,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
+        <v>757</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5512,10 +5508,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>558478</v>
+        <v>558364</v>
       </c>
       <c r="R45" t="n">
-        <v>6624257</v>
+        <v>6624122</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5542,12 +5538,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5556,6 +5552,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5578,10 +5575,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121394365</v>
+        <v>121394325</v>
       </c>
       <c r="B46" t="n">
-        <v>91120</v>
+        <v>5173</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5590,20 +5587,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6040162</v>
+        <v>100526</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5613,10 +5615,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558351</v>
+        <v>558478</v>
       </c>
       <c r="R46" t="n">
-        <v>6624213</v>
+        <v>6624257</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5643,12 +5645,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5657,7 +5659,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5680,10 +5681,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121394354</v>
+        <v>121394365</v>
       </c>
       <c r="B47" t="n">
-        <v>86306</v>
+        <v>91120</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5696,21 +5697,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3739</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Persiljespindling</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5720,10 +5716,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558390</v>
+        <v>558351</v>
       </c>
       <c r="R47" t="n">
-        <v>6624037</v>
+        <v>6624213</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5750,12 +5746,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5764,6 +5760,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5786,10 +5783,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121394548</v>
+        <v>121394354</v>
       </c>
       <c r="B48" t="n">
-        <v>92032</v>
+        <v>86306</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5802,21 +5799,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5449</v>
+        <v>3739</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5826,10 +5823,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>558480</v>
+        <v>558390</v>
       </c>
       <c r="R48" t="n">
-        <v>6624122</v>
+        <v>6624037</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5856,12 +5853,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5892,10 +5889,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121394323</v>
+        <v>121394548</v>
       </c>
       <c r="B49" t="n">
-        <v>5173</v>
+        <v>92032</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5904,25 +5901,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100526</v>
+        <v>5449</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5932,10 +5929,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558492</v>
+        <v>558480</v>
       </c>
       <c r="R49" t="n">
-        <v>6624223</v>
+        <v>6624122</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5962,12 +5959,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5998,10 +5995,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121394270</v>
+        <v>121394323</v>
       </c>
       <c r="B50" t="n">
-        <v>98113</v>
+        <v>5173</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6010,42 +6007,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>558522</v>
+        <v>558492</v>
       </c>
       <c r="R50" t="n">
-        <v>6624290</v>
+        <v>6624223</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6072,12 +6065,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6108,10 +6101,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121394309</v>
+        <v>121394270</v>
       </c>
       <c r="B51" t="n">
-        <v>95699</v>
+        <v>98113</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6120,38 +6113,42 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>558437</v>
+        <v>558522</v>
       </c>
       <c r="R51" t="n">
-        <v>6624264</v>
+        <v>6624290</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6214,10 +6211,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121394355</v>
+        <v>121394309</v>
       </c>
       <c r="B52" t="n">
-        <v>92201</v>
+        <v>95699</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6226,41 +6223,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2079</v>
+        <v>2590</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>558377</v>
+        <v>558437</v>
       </c>
       <c r="R52" t="n">
-        <v>6624159</v>
+        <v>6624264</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6287,12 +6281,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6301,24 +6295,8 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AL52" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>undersida av grov ved mot mark # tall</t>
-        </is>
-      </c>
-      <c r="AQ52" t="inlineStr">
-        <is>
-          <t>Ralf Lundmark</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6339,10 +6317,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121394326</v>
+        <v>121394355</v>
       </c>
       <c r="B53" t="n">
-        <v>4770</v>
+        <v>92201</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6351,38 +6329,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100299</v>
+        <v>2079</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>558478</v>
+        <v>558377</v>
       </c>
       <c r="R53" t="n">
-        <v>6624257</v>
+        <v>6624159</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6409,12 +6390,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6423,8 +6404,24 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>undersida av grov ved mot mark # tall</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6445,10 +6442,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121394364</v>
+        <v>121394326</v>
       </c>
       <c r="B54" t="n">
-        <v>8436</v>
+        <v>4770</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6461,21 +6458,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>100299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6485,10 +6482,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>558351</v>
+        <v>558478</v>
       </c>
       <c r="R54" t="n">
-        <v>6624213</v>
+        <v>6624257</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6515,12 +6512,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6551,10 +6548,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121394327</v>
+        <v>121394364</v>
       </c>
       <c r="B55" t="n">
-        <v>90742</v>
+        <v>8436</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6563,25 +6560,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1204</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6591,10 +6588,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>558466</v>
+        <v>558351</v>
       </c>
       <c r="R55" t="n">
-        <v>6624295</v>
+        <v>6624213</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6621,12 +6618,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6657,10 +6654,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121394339</v>
+        <v>121394327</v>
       </c>
       <c r="B56" t="n">
-        <v>74661</v>
+        <v>90742</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6669,25 +6666,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6426</v>
+        <v>1204</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6697,10 +6694,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>558458</v>
+        <v>558466</v>
       </c>
       <c r="R56" t="n">
-        <v>6624309</v>
+        <v>6624295</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6763,7 +6760,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121394359</v>
+        <v>121394339</v>
       </c>
       <c r="B57" t="n">
         <v>74661</v>
@@ -6803,10 +6800,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>558414</v>
+        <v>558458</v>
       </c>
       <c r="R57" t="n">
-        <v>6624238</v>
+        <v>6624309</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6833,12 +6830,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6869,10 +6866,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121394344</v>
+        <v>121394359</v>
       </c>
       <c r="B58" t="n">
-        <v>92016</v>
+        <v>74661</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6885,21 +6882,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4366</v>
+        <v>6426</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6909,10 +6906,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>558407</v>
+        <v>558414</v>
       </c>
       <c r="R58" t="n">
-        <v>6624166</v>
+        <v>6624238</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6939,12 +6936,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6975,10 +6972,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121394342</v>
+        <v>121394344</v>
       </c>
       <c r="B59" t="n">
-        <v>74661</v>
+        <v>92016</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6991,21 +6988,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6426</v>
+        <v>4366</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7015,10 +7012,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>558435</v>
+        <v>558407</v>
       </c>
       <c r="R59" t="n">
-        <v>6624227</v>
+        <v>6624166</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7081,10 +7078,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121394324</v>
+        <v>121394342</v>
       </c>
       <c r="B60" t="n">
-        <v>5193</v>
+        <v>74661</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7097,21 +7094,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7121,10 +7118,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>558478</v>
+        <v>558435</v>
       </c>
       <c r="R60" t="n">
-        <v>6624257</v>
+        <v>6624227</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7187,10 +7184,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121394321</v>
+        <v>121394324</v>
       </c>
       <c r="B61" t="n">
-        <v>95660</v>
+        <v>5193</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7199,25 +7196,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7227,10 +7224,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>558450</v>
+        <v>558478</v>
       </c>
       <c r="R61" t="n">
-        <v>6624202</v>
+        <v>6624257</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7257,12 +7254,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7293,10 +7290,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121394314</v>
+        <v>121394321</v>
       </c>
       <c r="B62" t="n">
-        <v>91120</v>
+        <v>95660</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7309,16 +7306,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6040162</v>
+        <v>53</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7328,10 +7330,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>558428</v>
+        <v>558450</v>
       </c>
       <c r="R62" t="n">
-        <v>6624048</v>
+        <v>6624202</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7358,17 +7360,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7377,7 +7374,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7400,10 +7396,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121394320</v>
+        <v>121394314</v>
       </c>
       <c r="B63" t="n">
-        <v>89776</v>
+        <v>91120</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7416,21 +7412,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1962</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Vaddporing</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7440,10 +7431,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>558465</v>
+        <v>558428</v>
       </c>
       <c r="R63" t="n">
-        <v>6624192</v>
+        <v>6624048</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7470,12 +7461,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7484,6 +7480,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7506,10 +7503,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121394351</v>
+        <v>121394320</v>
       </c>
       <c r="B64" t="n">
-        <v>5193</v>
+        <v>89776</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7518,25 +7515,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>105930</v>
+        <v>1962</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7546,10 +7543,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>558363</v>
+        <v>558465</v>
       </c>
       <c r="R64" t="n">
-        <v>6624071</v>
+        <v>6624192</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7576,12 +7573,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7612,10 +7609,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121394313</v>
+        <v>121394351</v>
       </c>
       <c r="B65" t="n">
-        <v>91121</v>
+        <v>5193</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7624,20 +7621,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6040186</v>
+        <v>105930</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7647,10 +7649,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>558412</v>
+        <v>558363</v>
       </c>
       <c r="R65" t="n">
-        <v>6624060</v>
+        <v>6624071</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7685,18 +7687,12 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7719,10 +7715,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121394310</v>
+        <v>121394313</v>
       </c>
       <c r="B66" t="n">
-        <v>95660</v>
+        <v>91121</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7735,21 +7731,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>53</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7759,10 +7750,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>558437</v>
+        <v>558412</v>
       </c>
       <c r="R66" t="n">
-        <v>6624264</v>
+        <v>6624060</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7789,12 +7780,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7803,6 +7799,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7825,10 +7822,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121394357</v>
+        <v>121394310</v>
       </c>
       <c r="B67" t="n">
-        <v>95407</v>
+        <v>95660</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7837,25 +7834,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2869</v>
+        <v>53</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7865,10 +7862,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>558396</v>
+        <v>558437</v>
       </c>
       <c r="R67" t="n">
-        <v>6624233</v>
+        <v>6624264</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7895,12 +7892,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7931,10 +7928,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121394303</v>
+        <v>121394357</v>
       </c>
       <c r="B68" t="n">
-        <v>98113</v>
+        <v>95407</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7943,42 +7940,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>558385</v>
+        <v>558396</v>
       </c>
       <c r="R68" t="n">
-        <v>6624276</v>
+        <v>6624233</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8005,12 +7998,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8041,7 +8034,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121394305</v>
+        <v>121394303</v>
       </c>
       <c r="B69" t="n">
         <v>98113</v>
@@ -8076,7 +8069,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8085,10 +8078,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>558420</v>
+        <v>558385</v>
       </c>
       <c r="R69" t="n">
-        <v>6624193</v>
+        <v>6624276</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8151,10 +8144,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121394352</v>
+        <v>121394305</v>
       </c>
       <c r="B70" t="n">
-        <v>5173</v>
+        <v>98113</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8163,38 +8156,42 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>558363</v>
+        <v>558420</v>
       </c>
       <c r="R70" t="n">
-        <v>6624071</v>
+        <v>6624193</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8221,12 +8218,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8257,10 +8254,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121394322</v>
+        <v>121394352</v>
       </c>
       <c r="B71" t="n">
-        <v>5193</v>
+        <v>5173</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8273,21 +8270,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8297,10 +8294,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>558492</v>
+        <v>558363</v>
       </c>
       <c r="R71" t="n">
-        <v>6624223</v>
+        <v>6624071</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8363,10 +8360,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121394494</v>
+        <v>121394322</v>
       </c>
       <c r="B72" t="n">
-        <v>89426</v>
+        <v>5193</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8375,25 +8372,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6286</v>
+        <v>105930</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8403,10 +8400,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>558369</v>
+        <v>558492</v>
       </c>
       <c r="R72" t="n">
-        <v>6624121</v>
+        <v>6624223</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8433,12 +8430,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8449,11 +8446,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>tallskog på finmorän</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8474,10 +8466,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121394353</v>
+        <v>121394494</v>
       </c>
       <c r="B73" t="n">
-        <v>4770</v>
+        <v>89426</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8486,25 +8478,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100299</v>
+        <v>6286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8514,10 +8506,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>558363</v>
+        <v>558369</v>
       </c>
       <c r="R73" t="n">
-        <v>6624071</v>
+        <v>6624121</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8544,12 +8536,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8560,6 +8552,11 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>tallskog på finmorän</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -8580,10 +8577,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121394363</v>
+        <v>121394353</v>
       </c>
       <c r="B74" t="n">
-        <v>5173</v>
+        <v>4770</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8596,21 +8593,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8620,10 +8617,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>558367</v>
+        <v>558363</v>
       </c>
       <c r="R74" t="n">
-        <v>6624219</v>
+        <v>6624071</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8650,12 +8647,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8686,10 +8683,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121394306</v>
+        <v>121394363</v>
       </c>
       <c r="B75" t="n">
-        <v>98113</v>
+        <v>5173</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8698,42 +8695,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>558437</v>
+        <v>558367</v>
       </c>
       <c r="R75" t="n">
-        <v>6624213</v>
+        <v>6624219</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8760,12 +8753,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8796,53 +8789,57 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127436389</v>
+        <v>121394306</v>
       </c>
       <c r="B76" t="n">
-        <v>100958</v>
+        <v>98113</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Syd Bosjön, Usträngsbo, Vstm</t>
+          <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>558432</v>
+        <v>558437</v>
       </c>
       <c r="R76" t="n">
-        <v>6624277</v>
+        <v>6624213</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8866,12 +8863,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8882,24 +8879,130 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>Äldre barrskog påverkad av rörligt markvatten</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>127436389</v>
+      </c>
+      <c r="B77" t="n">
+        <v>100958</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Syd Bosjön, Usträngsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>558432</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6624277</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Äldre barrskog påverkad av rörligt markvatten</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
           <t>Jacob Rudhe</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
+      <c r="AX77" t="inlineStr">
         <is>
           <t>Jacob Rudhe, Mårten Berglind, Carl Hanson, Ralf Lundmark</t>
         </is>
       </c>
-      <c r="AY76" t="inlineStr"/>
+      <c r="AY77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AY92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5981824</v>
+        <v>121359455</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fanfluken, Sura sn, Vstm</t>
+          <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558391.0992563891</v>
+        <v>558368</v>
       </c>
       <c r="R2" t="n">
-        <v>6624213.553436895</v>
+        <v>6624331</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -741,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-07-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-07-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,74 +756,68 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Granskog, litet kärr</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3424440</v>
+        <v>121394198</v>
       </c>
       <c r="B3" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fanfluken, Sura sn, Vstm</t>
+          <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558349.8816008881</v>
+        <v>558390</v>
       </c>
       <c r="R3" t="n">
-        <v>6624234.077081325</v>
+        <v>6624295</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2010-07-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2010-07-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,80 +857,65 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Gles tallskog på tunn morän</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119713808</v>
+        <v>121394206</v>
       </c>
       <c r="B4" t="n">
-        <v>8432</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fanfluken, Sura sn, Vstm</t>
+          <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558363</v>
+        <v>558377</v>
       </c>
       <c r="R4" t="n">
-        <v>6624123</v>
+        <v>6624106</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,27 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På tall-låga</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,85 +956,67 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119713553</v>
+        <v>121394310</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558372</v>
+        <v>558437</v>
       </c>
       <c r="R5" t="n">
-        <v>6624267</v>
+        <v>6624264</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1118,22 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,85 +1057,67 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119713735</v>
+        <v>121394321</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fanfluken, Sura sn, Vstm</t>
+          <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>558369</v>
+        <v>558450</v>
       </c>
       <c r="R6" t="n">
-        <v>6624275</v>
+        <v>6624202</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1247,27 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Enstaka överblommade plantor</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1276,80 +1158,67 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119713775</v>
+        <v>121394945</v>
       </c>
       <c r="B7" t="n">
-        <v>90545</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fanfluken, Sura sn, Vstm</t>
+          <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>558433</v>
+        <v>558441</v>
       </c>
       <c r="R7" t="n">
-        <v>6624268</v>
+        <v>6624265</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1376,27 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,85 +1259,67 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119713512</v>
+        <v>121394356</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92640</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>757</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fanfluken, Sura sn, Vstm</t>
+          <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>558369</v>
+        <v>558364</v>
       </c>
       <c r="R8" t="n">
-        <v>6624269</v>
+        <v>6624122</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1510,22 +1346,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1541,27 +1367,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119713527</v>
+        <v>121394942</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,50 +1394,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>990</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Warnst.) R.M.Schust.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fanfluken, Sura sn, Vstm</t>
+          <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558367</v>
+        <v>558390</v>
       </c>
       <c r="R9" t="n">
-        <v>6624274</v>
+        <v>6624295</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1639,22 +1448,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1670,78 +1469,61 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119713516</v>
+        <v>121359467</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92147</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1101</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fanfluken, Sura sn, Vstm</t>
+          <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558369</v>
+        <v>558464</v>
       </c>
       <c r="R10" t="n">
-        <v>6624271</v>
+        <v>6624306</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1768,22 +1550,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1792,85 +1564,67 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119713763</v>
+        <v>121359462</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1106</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fanfluken, Sura sn, Vstm</t>
+          <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>558353</v>
+        <v>558376</v>
       </c>
       <c r="R11" t="n">
-        <v>6624271</v>
+        <v>6624261</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1897,22 +1651,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1921,85 +1665,67 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119713818</v>
+        <v>121359469</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fanfluken, Sura sn, Vstm</t>
+          <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558246</v>
+        <v>558491</v>
       </c>
       <c r="R12" t="n">
-        <v>6624165</v>
+        <v>6624274</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2026,22 +1752,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2050,56 +1766,54 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121359461</v>
+        <v>121359443</v>
       </c>
       <c r="B13" t="n">
-        <v>79234</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2109,10 +1823,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558352</v>
+        <v>558441</v>
       </c>
       <c r="R13" t="n">
-        <v>6624226</v>
+        <v>6624265</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2175,37 +1889,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121359506</v>
+        <v>121394327</v>
       </c>
       <c r="B14" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2215,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558352</v>
+        <v>558466</v>
       </c>
       <c r="R14" t="n">
-        <v>6624128</v>
+        <v>6624295</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2245,12 +1954,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2281,15 +1990,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121359465</v>
+        <v>121394386</v>
       </c>
       <c r="B15" t="n">
-        <v>91120</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2297,16 +2001,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6040162</v>
+        <v>1209</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2316,10 +2025,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558460</v>
+        <v>558204</v>
       </c>
       <c r="R15" t="n">
-        <v>6624272</v>
+        <v>6624160</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2346,12 +2055,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2360,7 +2069,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2383,53 +2091,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121359462</v>
+        <v>127436384</v>
       </c>
       <c r="B16" t="n">
-        <v>90932</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1106</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fanfluken, Vstm</t>
+          <t>Syd Bosjön, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558376</v>
+        <v>558209</v>
       </c>
       <c r="R16" t="n">
-        <v>6624261</v>
+        <v>6624166</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2453,12 +2165,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2469,35 +2181,46 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Grov granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
-        </is>
-      </c>
+          <t>Jacob Rudhe, Mårten Berglind, Carl Hanson, Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121359457</v>
+        <v>121394320</v>
       </c>
       <c r="B17" t="n">
-        <v>92032</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2505,21 +2228,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>1962</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2529,10 +2252,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558395</v>
+        <v>558465</v>
       </c>
       <c r="R17" t="n">
-        <v>6624316</v>
+        <v>6624192</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2559,12 +2282,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2595,37 +2318,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121359460</v>
+        <v>121394348</v>
       </c>
       <c r="B18" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>1968</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2635,10 +2353,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558352</v>
+        <v>558437</v>
       </c>
       <c r="R18" t="n">
-        <v>6624226</v>
+        <v>6624152</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2665,12 +2383,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2701,15 +2419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121359471</v>
+        <v>121394355</v>
       </c>
       <c r="B19" t="n">
-        <v>95660</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2717,34 +2430,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>2079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558521</v>
+        <v>558377</v>
       </c>
       <c r="R19" t="n">
-        <v>6624319</v>
+        <v>6624159</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2771,12 +2487,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,8 +2501,24 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>undersida av grov ved mot mark # tall</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2807,37 +2539,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121359469</v>
+        <v>121394350</v>
       </c>
       <c r="B20" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>2170</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2847,10 +2574,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558491</v>
+        <v>558402</v>
       </c>
       <c r="R20" t="n">
-        <v>6624274</v>
+        <v>6624073</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2877,12 +2604,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2913,37 +2640,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121359458</v>
+        <v>121394309</v>
       </c>
       <c r="B21" t="n">
-        <v>92030</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5448</v>
+        <v>2590</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2953,10 +2675,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558350</v>
+        <v>558437</v>
       </c>
       <c r="R21" t="n">
-        <v>6624211</v>
+        <v>6624264</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2983,12 +2705,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3019,37 +2741,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121359459</v>
+        <v>121394357</v>
       </c>
       <c r="B22" t="n">
-        <v>79234</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>2869</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3059,10 +2776,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558364</v>
+        <v>558396</v>
       </c>
       <c r="R22" t="n">
-        <v>6624216</v>
+        <v>6624233</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3089,12 +2806,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3125,37 +2842,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121359443</v>
+        <v>121394311</v>
       </c>
       <c r="B23" t="n">
-        <v>90742</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>3215</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3165,10 +2877,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558441</v>
+        <v>558458</v>
       </c>
       <c r="R23" t="n">
-        <v>6624265</v>
+        <v>6624331</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3195,12 +2907,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3231,15 +2943,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121359466</v>
+        <v>121394349</v>
       </c>
       <c r="B24" t="n">
-        <v>90693</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85274</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3247,21 +2954,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>3518</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3271,10 +2978,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558467</v>
+        <v>558419</v>
       </c>
       <c r="R24" t="n">
-        <v>6624274</v>
+        <v>6624081</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3301,12 +3008,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3337,53 +3044,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121359444</v>
+        <v>121394354</v>
       </c>
       <c r="B25" t="n">
-        <v>92037</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87375</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>3739</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558433</v>
+        <v>558390</v>
       </c>
       <c r="R25" t="n">
-        <v>6624286</v>
+        <v>6624037</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3410,12 +3109,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3424,7 +3123,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3447,15 +3145,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121359467</v>
+        <v>121394344</v>
       </c>
       <c r="B26" t="n">
-        <v>90945</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3463,21 +3156,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1101</v>
+        <v>4366</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gropticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Postia guttulata</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Peck) Jülich</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3487,10 +3180,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558464</v>
+        <v>558407</v>
       </c>
       <c r="R26" t="n">
-        <v>6624306</v>
+        <v>6624166</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3517,12 +3210,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3553,15 +3246,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121394943</v>
+        <v>121359507</v>
       </c>
       <c r="B27" t="n">
-        <v>95660</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,21 +3257,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3593,10 +3281,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558390</v>
+        <v>558347</v>
       </c>
       <c r="R27" t="n">
-        <v>6624295</v>
+        <v>6624120</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3659,45 +3347,56 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121394932</v>
+        <v>119713775</v>
       </c>
       <c r="B28" t="n">
-        <v>91120</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6040162</v>
+        <v>5447</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fanfluken, Vstm</t>
+          <t>Fanfluken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>558394</v>
+        <v>558433</v>
       </c>
       <c r="R28" t="n">
-        <v>6624091</v>
+        <v>6624268</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3724,12 +3423,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3745,53 +3459,44 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
-        </is>
-      </c>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121394934</v>
+        <v>121359466</v>
       </c>
       <c r="B29" t="n">
-        <v>95660</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3801,10 +3506,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558377</v>
+        <v>558467</v>
       </c>
       <c r="R29" t="n">
-        <v>6624106</v>
+        <v>6624274</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3870,12 +3575,7 @@
         <v>121394944</v>
       </c>
       <c r="B30" t="n">
-        <v>90693</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3973,15 +3673,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121394549</v>
+        <v>121359458</v>
       </c>
       <c r="B31" t="n">
-        <v>92030</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4013,10 +3708,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558468</v>
+        <v>558350</v>
       </c>
       <c r="R31" t="n">
-        <v>6624096</v>
+        <v>6624211</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4043,12 +3738,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4079,37 +3774,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121394933</v>
+        <v>121394549</v>
       </c>
       <c r="B32" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>5448</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4119,10 +3809,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>558377</v>
+        <v>558468</v>
       </c>
       <c r="R32" t="n">
-        <v>6624106</v>
+        <v>6624096</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4149,12 +3839,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4185,15 +3875,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121394945</v>
+        <v>121359444</v>
       </c>
       <c r="B33" t="n">
-        <v>95660</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4201,34 +3886,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>5964</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>558441</v>
+        <v>558433</v>
       </c>
       <c r="R33" t="n">
-        <v>6624265</v>
+        <v>6624286</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4269,6 +3957,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4291,15 +3980,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121394942</v>
+        <v>121394202</v>
       </c>
       <c r="B34" t="n">
-        <v>95976</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93181</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4307,21 +3991,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>990</v>
+        <v>6055</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4331,10 +4015,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>558390</v>
+        <v>558315</v>
       </c>
       <c r="R34" t="n">
-        <v>6624295</v>
+        <v>6624258</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4361,12 +4045,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4375,7 +4059,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4401,12 +4084,7 @@
         <v>121394315</v>
       </c>
       <c r="B35" t="n">
-        <v>91988</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93181</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4504,59 +4182,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121394272</v>
+        <v>121394494</v>
       </c>
       <c r="B36" t="n">
-        <v>58224</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90710</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>208242</v>
+        <v>6286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>558519</v>
+        <v>558369</v>
       </c>
       <c r="R36" t="n">
-        <v>6624313</v>
+        <v>6624121</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4583,17 +4247,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>under ved i barrskog</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4604,6 +4263,11 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>tallskog på finmorän</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4624,54 +4288,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121394304</v>
+        <v>121394336</v>
       </c>
       <c r="B37" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>558372</v>
+        <v>558505</v>
       </c>
       <c r="R37" t="n">
-        <v>6624277</v>
+        <v>6624341</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4698,12 +4353,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4734,19 +4389,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121394343</v>
+        <v>121394339</v>
       </c>
       <c r="B38" t="n">
-        <v>74661</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4774,10 +4424,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>558405</v>
+        <v>558458</v>
       </c>
       <c r="R38" t="n">
-        <v>6624226</v>
+        <v>6624309</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4840,37 +4490,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121394350</v>
+        <v>121394342</v>
       </c>
       <c r="B39" t="n">
-        <v>94778</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2170</v>
+        <v>6426</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4880,10 +4525,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>558402</v>
+        <v>558435</v>
       </c>
       <c r="R39" t="n">
-        <v>6624073</v>
+        <v>6624227</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4946,37 +4591,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121394319</v>
+        <v>121394343</v>
       </c>
       <c r="B40" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6426</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4986,10 +4626,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>558461</v>
+        <v>558405</v>
       </c>
       <c r="R40" t="n">
-        <v>6624164</v>
+        <v>6624226</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5016,12 +4656,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5052,15 +4692,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121394348</v>
+        <v>121394359</v>
       </c>
       <c r="B41" t="n">
-        <v>92035</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5068,21 +4703,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1968</v>
+        <v>6426</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5092,10 +4727,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>558437</v>
+        <v>558414</v>
       </c>
       <c r="R41" t="n">
-        <v>6624152</v>
+        <v>6624238</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5122,12 +4757,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5158,37 +4793,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121394349</v>
+        <v>121394366</v>
       </c>
       <c r="B42" t="n">
-        <v>84312</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3518</v>
+        <v>6426</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5198,10 +4828,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>558419</v>
+        <v>558405</v>
       </c>
       <c r="R42" t="n">
-        <v>6624081</v>
+        <v>6624351</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5228,12 +4858,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5264,15 +4894,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121394345</v>
+        <v>121394334</v>
       </c>
       <c r="B43" t="n">
-        <v>97061</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5280,19 +4905,23 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221944</v>
+        <v>6428</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5300,10 +4929,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>558386</v>
+        <v>558505</v>
       </c>
       <c r="R43" t="n">
-        <v>6624222</v>
+        <v>6624341</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5344,7 +4973,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5367,15 +4995,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121394333</v>
+        <v>121359459</v>
       </c>
       <c r="B44" t="n">
-        <v>95660</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5383,21 +5006,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5407,10 +5030,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>558528</v>
+        <v>558364</v>
       </c>
       <c r="R44" t="n">
-        <v>6624316</v>
+        <v>6624216</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5437,12 +5060,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5473,15 +5096,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121394356</v>
+        <v>121359461</v>
       </c>
       <c r="B45" t="n">
-        <v>91419</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5489,16 +5107,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>757</v>
+        <v>6453</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5508,10 +5131,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>558364</v>
+        <v>558352</v>
       </c>
       <c r="R45" t="n">
-        <v>6624122</v>
+        <v>6624226</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5552,7 +5175,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5575,37 +5197,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121394325</v>
+        <v>121359505</v>
       </c>
       <c r="B46" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5615,10 +5232,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>558478</v>
+        <v>558475</v>
       </c>
       <c r="R46" t="n">
-        <v>6624257</v>
+        <v>6624340</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5645,12 +5262,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5681,15 +5298,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121394365</v>
+        <v>121394203</v>
       </c>
       <c r="B47" t="n">
-        <v>91120</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5697,16 +5309,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6040162</v>
+        <v>6453</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5716,10 +5333,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>558351</v>
+        <v>558318</v>
       </c>
       <c r="R47" t="n">
-        <v>6624213</v>
+        <v>6624247</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5746,12 +5363,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5760,7 +5377,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5783,37 +5399,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121394354</v>
+        <v>121394326</v>
       </c>
       <c r="B48" t="n">
-        <v>86306</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3739</v>
+        <v>100299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5823,10 +5434,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>558390</v>
+        <v>558478</v>
       </c>
       <c r="R48" t="n">
-        <v>6624037</v>
+        <v>6624257</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5889,37 +5500,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121394548</v>
+        <v>121394353</v>
       </c>
       <c r="B49" t="n">
-        <v>92032</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5449</v>
+        <v>100299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5929,10 +5535,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>558480</v>
+        <v>558363</v>
       </c>
       <c r="R49" t="n">
-        <v>6624122</v>
+        <v>6624071</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5959,12 +5565,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5995,53 +5601,61 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121394323</v>
+        <v>121447429</v>
       </c>
       <c r="B50" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>53595</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100526</v>
+        <v>100388</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knölspindel</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Araneus angulatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>Clerck, 1757</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>558492</v>
+        <v>558337</v>
       </c>
       <c r="R50" t="n">
-        <v>6624223</v>
+        <v>6624318</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6065,12 +5679,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2023-06-16</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2023-06-16</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6079,6 +5693,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6101,54 +5716,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121394270</v>
+        <v>121394323</v>
       </c>
       <c r="B51" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>558522</v>
+        <v>558492</v>
       </c>
       <c r="R51" t="n">
-        <v>6624290</v>
+        <v>6624223</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6175,12 +5781,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6211,15 +5817,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121394309</v>
+        <v>121394325</v>
       </c>
       <c r="B52" t="n">
-        <v>95699</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6227,21 +5828,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2590</v>
+        <v>100526</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6251,10 +5852,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>558437</v>
+        <v>558478</v>
       </c>
       <c r="R52" t="n">
-        <v>6624264</v>
+        <v>6624257</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6281,12 +5882,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6317,53 +5918,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121394355</v>
+        <v>121394352</v>
       </c>
       <c r="B53" t="n">
-        <v>92201</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2079</v>
+        <v>100526</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>558377</v>
+        <v>558363</v>
       </c>
       <c r="R53" t="n">
-        <v>6624159</v>
+        <v>6624071</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6390,12 +5983,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6404,24 +5997,8 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AL53" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>undersida av grov ved mot mark # tall</t>
-        </is>
-      </c>
-      <c r="AQ53" t="inlineStr">
-        <is>
-          <t>Ralf Lundmark</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6442,15 +6019,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121394326</v>
+        <v>121394363</v>
       </c>
       <c r="B54" t="n">
-        <v>4770</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6458,21 +6030,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6482,10 +6054,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>558478</v>
+        <v>558367</v>
       </c>
       <c r="R54" t="n">
-        <v>6624257</v>
+        <v>6624219</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6512,12 +6084,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6548,15 +6120,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121394364</v>
+        <v>119830133</v>
       </c>
       <c r="B55" t="n">
-        <v>8436</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6564,37 +6131,41 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fanfluken, Vstm</t>
+          <t>A 31280-2024, Vstm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>558351</v>
+        <v>558477</v>
       </c>
       <c r="R55" t="n">
-        <v>6624213</v>
+        <v>6624326</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6618,12 +6189,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6638,31 +6219,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
-        </is>
-      </c>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121394327</v>
+        <v>119830097</v>
       </c>
       <c r="B56" t="n">
-        <v>90742</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6670,37 +6242,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1204</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fanfluken, Vstm</t>
+          <t>A 31280-2024, Vstm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>558466</v>
+        <v>558477</v>
       </c>
       <c r="R56" t="n">
-        <v>6624295</v>
+        <v>6624326</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6724,12 +6301,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6744,31 +6331,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
-        </is>
-      </c>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121394339</v>
+        <v>121394322</v>
       </c>
       <c r="B57" t="n">
-        <v>74661</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6776,21 +6354,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6800,10 +6378,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>558458</v>
+        <v>558492</v>
       </c>
       <c r="R57" t="n">
-        <v>6624309</v>
+        <v>6624223</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6866,15 +6444,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121394359</v>
+        <v>121394324</v>
       </c>
       <c r="B58" t="n">
-        <v>74661</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6882,21 +6455,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6906,10 +6479,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>558414</v>
+        <v>558478</v>
       </c>
       <c r="R58" t="n">
-        <v>6624238</v>
+        <v>6624257</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6936,12 +6509,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6972,15 +6545,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121394344</v>
+        <v>121394351</v>
       </c>
       <c r="B59" t="n">
-        <v>92016</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6988,21 +6556,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4366</v>
+        <v>105930</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7012,10 +6580,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>558407</v>
+        <v>558363</v>
       </c>
       <c r="R59" t="n">
-        <v>6624166</v>
+        <v>6624071</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7078,15 +6646,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121394342</v>
+        <v>119713808</v>
       </c>
       <c r="B60" t="n">
-        <v>74661</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7094,34 +6657,43 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6426</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fanfluken, Vstm</t>
+          <t>Fanfluken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>558435</v>
+        <v>558363</v>
       </c>
       <c r="R60" t="n">
-        <v>6624227</v>
+        <v>6624123</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7148,12 +6720,27 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På tall-låga</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7162,37 +6749,29 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
-        </is>
-      </c>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121394324</v>
+        <v>121359453</v>
       </c>
       <c r="B61" t="n">
-        <v>5193</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7200,21 +6779,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7224,10 +6803,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>558478</v>
+        <v>558368</v>
       </c>
       <c r="R61" t="n">
-        <v>6624257</v>
+        <v>6624331</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7254,12 +6833,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7290,37 +6869,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121394321</v>
+        <v>121359460</v>
       </c>
       <c r="B62" t="n">
-        <v>95660</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7330,10 +6904,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>558450</v>
+        <v>558352</v>
       </c>
       <c r="R62" t="n">
-        <v>6624202</v>
+        <v>6624226</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7360,12 +6934,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7396,32 +6970,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121394314</v>
+        <v>121359506</v>
       </c>
       <c r="B63" t="n">
-        <v>91120</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6040162</v>
+        <v>106545</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7431,10 +7005,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>558428</v>
+        <v>558352</v>
       </c>
       <c r="R63" t="n">
-        <v>6624048</v>
+        <v>6624128</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7461,17 +7035,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7480,7 +7049,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7503,37 +7071,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121394320</v>
+        <v>121394205</v>
       </c>
       <c r="B64" t="n">
-        <v>89776</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7543,10 +7106,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>558465</v>
+        <v>558377</v>
       </c>
       <c r="R64" t="n">
-        <v>6624192</v>
+        <v>6624106</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7573,12 +7136,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7609,15 +7172,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121394351</v>
+        <v>121394319</v>
       </c>
       <c r="B65" t="n">
-        <v>5193</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7625,21 +7183,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7649,10 +7207,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>558363</v>
+        <v>558461</v>
       </c>
       <c r="R65" t="n">
-        <v>6624071</v>
+        <v>6624164</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7679,12 +7237,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2021-10-29</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7715,32 +7273,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121394313</v>
+        <v>121394364</v>
       </c>
       <c r="B66" t="n">
-        <v>91121</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6040186</v>
+        <v>106545</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7750,10 +7308,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>558412</v>
+        <v>558351</v>
       </c>
       <c r="R66" t="n">
-        <v>6624060</v>
+        <v>6624213</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7780,17 +7338,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7799,7 +7352,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7822,50 +7374,61 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121394310</v>
+        <v>119713512</v>
       </c>
       <c r="B67" t="n">
-        <v>95660</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Fanfluken, Vstm</t>
+          <t>Fanfluken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>558437</v>
+        <v>558369</v>
       </c>
       <c r="R67" t="n">
-        <v>6624264</v>
+        <v>6624269</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7892,12 +7455,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7906,72 +7479,80 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
-        </is>
-      </c>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121394357</v>
+        <v>119713516</v>
       </c>
       <c r="B68" t="n">
-        <v>95407</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2869</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Fanfluken, Vstm</t>
+          <t>Fanfluken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>558396</v>
+        <v>558369</v>
       </c>
       <c r="R68" t="n">
-        <v>6624233</v>
+        <v>6624271</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7998,12 +7579,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8012,37 +7603,29 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
-        </is>
-      </c>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121394303</v>
+        <v>119713527</v>
       </c>
       <c r="B69" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8069,19 +7652,31 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fanfluken, Vstm</t>
+          <t>Fanfluken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>558385</v>
+        <v>558367</v>
       </c>
       <c r="R69" t="n">
-        <v>6624276</v>
+        <v>6624274</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8108,12 +7703,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8122,37 +7727,29 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
-        </is>
-      </c>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121394305</v>
+        <v>119713553</v>
       </c>
       <c r="B70" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8179,19 +7776,31 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>558420</v>
+        <v>558372</v>
       </c>
       <c r="R70" t="n">
-        <v>6624193</v>
+        <v>6624267</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8218,12 +7827,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8232,72 +7851,80 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
-        </is>
-      </c>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121394352</v>
+        <v>119713735</v>
       </c>
       <c r="B71" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Fanfluken, Vstm</t>
+          <t>Fanfluken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>558363</v>
+        <v>558369</v>
       </c>
       <c r="R71" t="n">
-        <v>6624071</v>
+        <v>6624275</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8324,12 +7951,27 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Enstaka överblommade plantor</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8338,72 +7980,80 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
-        </is>
-      </c>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121394322</v>
+        <v>119713763</v>
       </c>
       <c r="B72" t="n">
-        <v>5193</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fanfluken, Vstm</t>
+          <t>Fanfluken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>558492</v>
+        <v>558353</v>
       </c>
       <c r="R72" t="n">
-        <v>6624223</v>
+        <v>6624271</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8430,12 +8080,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8444,37 +8104,29 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
-        </is>
-      </c>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121394494</v>
+        <v>119713818</v>
       </c>
       <c r="B73" t="n">
-        <v>89426</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8482,34 +8134,50 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6286</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Fanfluken, Vstm</t>
+          <t>Fanfluken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>558369</v>
+        <v>558246</v>
       </c>
       <c r="R73" t="n">
-        <v>6624121</v>
+        <v>6624165</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8536,12 +8204,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8550,77 +8228,68 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>tallskog på finmorän</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
-        </is>
-      </c>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121394353</v>
+        <v>121394303</v>
       </c>
       <c r="B74" t="n">
-        <v>4770</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>558363</v>
+        <v>558385</v>
       </c>
       <c r="R74" t="n">
-        <v>6624071</v>
+        <v>6624276</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8647,12 +8316,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8683,50 +8352,49 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121394363</v>
+        <v>121394304</v>
       </c>
       <c r="B75" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>558367</v>
+        <v>558372</v>
       </c>
       <c r="R75" t="n">
-        <v>6624219</v>
+        <v>6624277</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8753,12 +8421,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8789,15 +8457,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121394306</v>
+        <v>121394305</v>
       </c>
       <c r="B76" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8824,7 +8487,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8833,10 +8496,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>558437</v>
+        <v>558420</v>
       </c>
       <c r="R76" t="n">
-        <v>6624213</v>
+        <v>6624193</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8899,53 +8562,52 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127436389</v>
+        <v>121394306</v>
       </c>
       <c r="B77" t="n">
-        <v>100958</v>
+        <v>99118</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Syd Bosjön, Usträngsbo, Vstm</t>
+          <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>558432</v>
+        <v>558437</v>
       </c>
       <c r="R77" t="n">
-        <v>6624277</v>
+        <v>6624213</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8969,12 +8631,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8985,24 +8647,1577 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>Äldre barrskog påverkad av rörligt markvatten</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>3424440</v>
+      </c>
+      <c r="B78" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Fanfluken, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>558350</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6624234</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2010-07-09</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2010-07-09</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Gles tallskog på tunn morän</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>121394345</v>
+      </c>
+      <c r="B79" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>558386</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6624222</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>127436389</v>
+      </c>
+      <c r="B80" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Syd Bosjön, Usträngsbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>558432</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6624277</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-04-28</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Äldre barrskog påverkad av rörligt markvatten</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
           <t>Jacob Rudhe</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
+      <c r="AX80" t="inlineStr">
         <is>
           <t>Jacob Rudhe, Mårten Berglind, Carl Hanson, Ralf Lundmark</t>
         </is>
       </c>
-      <c r="AY77" t="inlineStr"/>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>5981824</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Fanfluken, Sura sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>558391</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6624214</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2010-07-09</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2010-07-09</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>Granskog, litet kärr</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>121359465</v>
+      </c>
+      <c r="B82" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>558460</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6624272</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2022-11-12</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2022-11-12</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>121394207</v>
+      </c>
+      <c r="B83" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>558394</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6624091</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2022-11-13</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2022-11-13</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>121394314</v>
+      </c>
+      <c r="B84" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>558428</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6624048</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>121394365</v>
+      </c>
+      <c r="B85" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>558351</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6624213</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-10-04</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>121394313</v>
+      </c>
+      <c r="B86" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>558412</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6624060</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>121359471</v>
+      </c>
+      <c r="B87" t="n">
+        <v>97358</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>53</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>558521</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6624319</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2022-11-12</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2022-11-12</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>121394333</v>
+      </c>
+      <c r="B88" t="n">
+        <v>97358</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>53</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>558528</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6624316</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>121394547</v>
+      </c>
+      <c r="B89" t="n">
+        <v>90522</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>4962</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Mjölsvärting</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Lyophyllum semitale</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>558553</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6624265</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2022-10-01</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>121394332</v>
+      </c>
+      <c r="B90" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>558554</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6624337</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>121394272</v>
+      </c>
+      <c r="B91" t="n">
+        <v>58826</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>558519</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6624313</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>under ved i barrskog</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>121394270</v>
+      </c>
+      <c r="B92" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>558522</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6624290</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY92"/>
+  <dimension ref="A1:AY93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8667,48 +8667,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>3424440</v>
+        <v>132753060</v>
       </c>
       <c r="B78" t="n">
-        <v>106244</v>
+        <v>99195</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Fanfluken, Sura sn, Vstm</t>
+          <t>Fanfluken, Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>558350</v>
+        <v>558386</v>
       </c>
       <c r="R78" t="n">
-        <v>6624234</v>
+        <v>6624273</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8732,12 +8732,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2010-07-09</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2010-07-09</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8748,31 +8748,26 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>Gles tallskog på tunn morän</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Per Appeltofft</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Per Appeltofft</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121394345</v>
+        <v>3424440</v>
       </c>
       <c r="B79" t="n">
-        <v>97977</v>
+        <v>106244</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8780,33 +8775,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221944</v>
+        <v>221144</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Fanfluken, Vstm</t>
+          <t>Fanfluken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>558386</v>
+        <v>558350</v>
       </c>
       <c r="R79" t="n">
-        <v>6624222</v>
+        <v>6624234</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8830,12 +8829,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2010-07-09</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2010-07-09</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8844,33 +8843,33 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Gles tallskog på tunn morän</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
-        </is>
-      </c>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127436389</v>
+        <v>121394345</v>
       </c>
       <c r="B80" t="n">
-        <v>101325</v>
+        <v>97977</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8878,42 +8877,33 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222498</v>
+        <v>221944</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Syd Bosjön, Usträngsbo, Vstm</t>
+          <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>558432</v>
+        <v>558386</v>
       </c>
       <c r="R80" t="n">
-        <v>6624277</v>
+        <v>6624222</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8937,12 +8927,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8951,33 +8941,33 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>Äldre barrskog påverkad av rörligt markvatten</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Jacob Rudhe, Mårten Berglind, Carl Hanson, Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>5981824</v>
+        <v>127436389</v>
       </c>
       <c r="B81" t="n">
-        <v>99038</v>
+        <v>101325</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8985,30 +8975,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>223597</v>
+        <v>222498</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Fanfluken, Sura sn, Vstm</t>
+          <t>Syd Bosjön, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>558391</v>
+        <v>558432</v>
       </c>
       <c r="R81" t="n">
-        <v>6624214</v>
+        <v>6624277</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9035,12 +9034,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2010-07-09</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2010-07-09</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9054,66 +9053,62 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Granskog, litet kärr</t>
+          <t>Äldre barrskog påverkad av rörligt markvatten</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Jacob Rudhe, Mårten Berglind, Carl Hanson, Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121359465</v>
+        <v>5981824</v>
       </c>
       <c r="B82" t="n">
-        <v>92328</v>
+        <v>99038</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6040162</v>
+        <v>223597</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Fanfluken, Vstm</t>
+          <t>Fanfluken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>558460</v>
+        <v>558391</v>
       </c>
       <c r="R82" t="n">
-        <v>6624272</v>
+        <v>6624214</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9137,12 +9132,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2010-07-09</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2010-07-09</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9151,30 +9146,30 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Granskog, litet kärr</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
-        </is>
-      </c>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121394207</v>
+        <v>121359465</v>
       </c>
       <c r="B83" t="n">
         <v>92328</v>
@@ -9209,10 +9204,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>558394</v>
+        <v>558460</v>
       </c>
       <c r="R83" t="n">
-        <v>6624091</v>
+        <v>6624272</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9239,17 +9234,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9281,7 +9271,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121394314</v>
+        <v>121394207</v>
       </c>
       <c r="B84" t="n">
         <v>92328</v>
@@ -9316,10 +9306,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>558428</v>
+        <v>558394</v>
       </c>
       <c r="R84" t="n">
-        <v>6624048</v>
+        <v>6624091</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9346,12 +9336,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
@@ -9388,7 +9378,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121394365</v>
+        <v>121394314</v>
       </c>
       <c r="B85" t="n">
         <v>92328</v>
@@ -9423,10 +9413,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>558351</v>
+        <v>558428</v>
       </c>
       <c r="R85" t="n">
-        <v>6624213</v>
+        <v>6624048</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9453,12 +9443,17 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9490,10 +9485,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121394313</v>
+        <v>121394365</v>
       </c>
       <c r="B86" t="n">
-        <v>92329</v>
+        <v>92328</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9501,21 +9496,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6040186</v>
+        <v>6040162</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tallkötticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9525,10 +9520,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>558412</v>
+        <v>558351</v>
       </c>
       <c r="R86" t="n">
-        <v>6624060</v>
+        <v>6624213</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9555,17 +9550,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9597,10 +9587,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121359471</v>
+        <v>121394313</v>
       </c>
       <c r="B87" t="n">
-        <v>97358</v>
+        <v>92329</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9608,21 +9598,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>53</v>
+        <v>6040186</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9632,10 +9622,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>558521</v>
+        <v>558412</v>
       </c>
       <c r="R87" t="n">
-        <v>6624319</v>
+        <v>6624060</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9662,12 +9652,17 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9676,6 +9671,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9698,7 +9694,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121394333</v>
+        <v>121359471</v>
       </c>
       <c r="B88" t="n">
         <v>97358</v>
@@ -9733,10 +9729,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>558528</v>
+        <v>558521</v>
       </c>
       <c r="R88" t="n">
-        <v>6624316</v>
+        <v>6624319</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9763,12 +9759,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9799,10 +9795,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121394547</v>
+        <v>121394333</v>
       </c>
       <c r="B89" t="n">
-        <v>90522</v>
+        <v>97358</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9810,21 +9806,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4962</v>
+        <v>53</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9834,10 +9830,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>558553</v>
+        <v>558528</v>
       </c>
       <c r="R89" t="n">
-        <v>6624265</v>
+        <v>6624316</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9864,12 +9860,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9900,10 +9896,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121394332</v>
+        <v>121394547</v>
       </c>
       <c r="B90" t="n">
-        <v>75428</v>
+        <v>90522</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9911,21 +9907,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6426</v>
+        <v>4962</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9935,10 +9931,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>558554</v>
+        <v>558553</v>
       </c>
       <c r="R90" t="n">
-        <v>6624337</v>
+        <v>6624265</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9965,12 +9961,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10001,54 +9997,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121394272</v>
+        <v>121394332</v>
       </c>
       <c r="B91" t="n">
-        <v>58826</v>
+        <v>75428</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>208242</v>
+        <v>6426</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>558519</v>
+        <v>558554</v>
       </c>
       <c r="R91" t="n">
-        <v>6624313</v>
+        <v>6624337</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10075,17 +10062,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>under ved i barrskog</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10116,37 +10098,42 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121394270</v>
+        <v>121394272</v>
       </c>
       <c r="B92" t="n">
-        <v>99118</v>
+        <v>58826</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>208242</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -10155,10 +10142,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>558522</v>
+        <v>558519</v>
       </c>
       <c r="R92" t="n">
-        <v>6624290</v>
+        <v>6624313</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10193,6 +10180,11 @@
           <t>2024-09-23</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>under ved i barrskog</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
@@ -10214,6 +10206,111 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>121394270</v>
+      </c>
+      <c r="B93" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>558522</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6624290</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
         <is>
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY93"/>
+  <dimension ref="A1:AY94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7374,50 +7374,43 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119713512</v>
+        <v>134450333</v>
       </c>
       <c r="B67" t="n">
-        <v>99118</v>
+        <v>56833</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>205998</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7425,13 +7418,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>558369</v>
+        <v>558312</v>
       </c>
       <c r="R67" t="n">
-        <v>6624269</v>
+        <v>6624069</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7455,22 +7448,27 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>23:45</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Pettersson Detector D 240x. Kan ha varit flera individer då det var mycket aktivt vissa studner. Flög såväl över vägen som i skogsglämta. Sågs även</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7479,7 +7477,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7491,14 +7488,14 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Sören Larsson, Bengt Eriksson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119713516</v>
+        <v>119713512</v>
       </c>
       <c r="B68" t="n">
         <v>99118</v>
@@ -7552,7 +7549,7 @@
         <v>558369</v>
       </c>
       <c r="R68" t="n">
-        <v>6624271</v>
+        <v>6624269</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7622,7 +7619,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119713527</v>
+        <v>119713516</v>
       </c>
       <c r="B69" t="n">
         <v>99118</v>
@@ -7652,12 +7649,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -7673,10 +7670,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>558367</v>
+        <v>558369</v>
       </c>
       <c r="R69" t="n">
-        <v>6624274</v>
+        <v>6624271</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7746,7 +7743,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119713553</v>
+        <v>119713527</v>
       </c>
       <c r="B70" t="n">
         <v>99118</v>
@@ -7781,7 +7778,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -7793,14 +7790,14 @@
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Fanfluken, Vstm</t>
+          <t>Fanfluken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>558372</v>
+        <v>558367</v>
       </c>
       <c r="R70" t="n">
-        <v>6624267</v>
+        <v>6624274</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7870,7 +7867,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119713735</v>
+        <v>119713553</v>
       </c>
       <c r="B71" t="n">
         <v>99118</v>
@@ -7900,12 +7897,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7917,14 +7914,14 @@
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Fanfluken, Sura sn, Vstm</t>
+          <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>558369</v>
+        <v>558372</v>
       </c>
       <c r="R71" t="n">
-        <v>6624275</v>
+        <v>6624267</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7967,11 +7964,6 @@
       <c r="AB71" t="inlineStr">
         <is>
           <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Enstaka överblommade plantor</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7999,7 +7991,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119713763</v>
+        <v>119713735</v>
       </c>
       <c r="B72" t="n">
         <v>99118</v>
@@ -8029,12 +8021,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -8050,10 +8042,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>558353</v>
+        <v>558369</v>
       </c>
       <c r="R72" t="n">
-        <v>6624271</v>
+        <v>6624275</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8096,6 +8088,11 @@
       <c r="AB72" t="inlineStr">
         <is>
           <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Enstaka överblommade plantor</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8123,7 +8120,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119713818</v>
+        <v>119713763</v>
       </c>
       <c r="B73" t="n">
         <v>99118</v>
@@ -8153,12 +8150,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -8174,10 +8171,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>558246</v>
+        <v>558353</v>
       </c>
       <c r="R73" t="n">
-        <v>6624165</v>
+        <v>6624271</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8247,7 +8244,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121394303</v>
+        <v>119713818</v>
       </c>
       <c r="B74" t="n">
         <v>99118</v>
@@ -8277,19 +8274,31 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Fanfluken, Vstm</t>
+          <t>Fanfluken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>558385</v>
+        <v>558246</v>
       </c>
       <c r="R74" t="n">
-        <v>6624276</v>
+        <v>6624165</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8316,12 +8325,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8330,29 +8349,26 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
-        </is>
-      </c>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121394304</v>
+        <v>121394303</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -8382,7 +8398,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8391,10 +8407,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>558372</v>
+        <v>558385</v>
       </c>
       <c r="R75" t="n">
-        <v>6624277</v>
+        <v>6624276</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8457,7 +8473,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121394305</v>
+        <v>121394304</v>
       </c>
       <c r="B76" t="n">
         <v>99118</v>
@@ -8487,7 +8503,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>400</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8496,10 +8512,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>558420</v>
+        <v>558372</v>
       </c>
       <c r="R76" t="n">
-        <v>6624193</v>
+        <v>6624277</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8562,7 +8578,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121394306</v>
+        <v>121394305</v>
       </c>
       <c r="B77" t="n">
         <v>99118</v>
@@ -8592,7 +8608,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -8601,10 +8617,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>558437</v>
+        <v>558420</v>
       </c>
       <c r="R77" t="n">
-        <v>6624213</v>
+        <v>6624193</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8667,10 +8683,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132753060</v>
+        <v>121394306</v>
       </c>
       <c r="B78" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8695,17 +8711,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Fanfluken, Fanfluken, Vstm</t>
+          <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>558386</v>
+        <v>558437</v>
       </c>
       <c r="R78" t="n">
-        <v>6624273</v>
+        <v>6624213</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8732,12 +8752,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8752,60 +8772,64 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Per Appeltofft</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Per Appeltofft</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>3424440</v>
+        <v>132753060</v>
       </c>
       <c r="B79" t="n">
-        <v>106244</v>
+        <v>99195</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Fanfluken, Sura sn, Vstm</t>
+          <t>Fanfluken, Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>558350</v>
+        <v>558386</v>
       </c>
       <c r="R79" t="n">
-        <v>6624234</v>
+        <v>6624273</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8829,12 +8853,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2010-07-09</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2010-07-09</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8845,31 +8869,26 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>Gles tallskog på tunn morän</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Per Appeltofft</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Per Appeltofft</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121394345</v>
+        <v>3424440</v>
       </c>
       <c r="B80" t="n">
-        <v>97977</v>
+        <v>106244</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8877,33 +8896,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221944</v>
+        <v>221144</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Fanfluken, Vstm</t>
+          <t>Fanfluken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>558386</v>
+        <v>558350</v>
       </c>
       <c r="R80" t="n">
-        <v>6624222</v>
+        <v>6624234</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8927,12 +8950,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2010-07-09</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2010-07-09</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8941,33 +8964,33 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Gles tallskog på tunn morän</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
-        </is>
-      </c>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127436389</v>
+        <v>121394345</v>
       </c>
       <c r="B81" t="n">
-        <v>101325</v>
+        <v>97977</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8975,42 +8998,33 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222498</v>
+        <v>221944</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Syd Bosjön, Usträngsbo, Vstm</t>
+          <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>558432</v>
+        <v>558386</v>
       </c>
       <c r="R81" t="n">
-        <v>6624277</v>
+        <v>6624222</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9034,12 +9048,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9048,33 +9062,33 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>Äldre barrskog påverkad av rörligt markvatten</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Jacob Rudhe, Mårten Berglind, Carl Hanson, Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>5981824</v>
+        <v>127436389</v>
       </c>
       <c r="B82" t="n">
-        <v>99038</v>
+        <v>101325</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9082,30 +9096,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>223597</v>
+        <v>222498</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Fanfluken, Sura sn, Vstm</t>
+          <t>Syd Bosjön, Usträngsbo, Vstm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>558391</v>
+        <v>558432</v>
       </c>
       <c r="R82" t="n">
-        <v>6624214</v>
+        <v>6624277</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9132,12 +9155,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2010-07-09</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2010-07-09</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9151,66 +9174,62 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Granskog, litet kärr</t>
+          <t>Äldre barrskog påverkad av rörligt markvatten</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Jacob Rudhe, Mårten Berglind, Carl Hanson, Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121359465</v>
+        <v>5981824</v>
       </c>
       <c r="B83" t="n">
-        <v>92328</v>
+        <v>99038</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6040162</v>
+        <v>223597</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Fanfluken, Vstm</t>
+          <t>Fanfluken, Sura sn, Vstm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>558460</v>
+        <v>558391</v>
       </c>
       <c r="R83" t="n">
-        <v>6624272</v>
+        <v>6624214</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9234,12 +9253,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2010-07-09</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2010-07-09</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9248,30 +9267,30 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>Granskog, litet kärr</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
-        </is>
-      </c>
+          <t>Sören Larsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121394207</v>
+        <v>121359465</v>
       </c>
       <c r="B84" t="n">
         <v>92328</v>
@@ -9306,10 +9325,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>558394</v>
+        <v>558460</v>
       </c>
       <c r="R84" t="n">
-        <v>6624091</v>
+        <v>6624272</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9336,17 +9355,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9378,7 +9392,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121394314</v>
+        <v>121394207</v>
       </c>
       <c r="B85" t="n">
         <v>92328</v>
@@ -9413,10 +9427,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>558428</v>
+        <v>558394</v>
       </c>
       <c r="R85" t="n">
-        <v>6624048</v>
+        <v>6624091</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9443,12 +9457,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -9485,7 +9499,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121394365</v>
+        <v>121394314</v>
       </c>
       <c r="B86" t="n">
         <v>92328</v>
@@ -9520,10 +9534,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>558351</v>
+        <v>558428</v>
       </c>
       <c r="R86" t="n">
-        <v>6624213</v>
+        <v>6624048</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9550,12 +9564,17 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-10-04</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9587,10 +9606,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121394313</v>
+        <v>121394365</v>
       </c>
       <c r="B87" t="n">
-        <v>92329</v>
+        <v>92328</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9598,21 +9617,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6040186</v>
+        <v>6040162</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Tallkötticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9622,10 +9641,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>558412</v>
+        <v>558351</v>
       </c>
       <c r="R87" t="n">
-        <v>6624060</v>
+        <v>6624213</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9652,17 +9671,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>gran</t>
+          <t>2024-10-04</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9694,10 +9708,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121359471</v>
+        <v>121394313</v>
       </c>
       <c r="B88" t="n">
-        <v>97358</v>
+        <v>92329</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9705,21 +9719,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>53</v>
+        <v>6040186</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9729,10 +9743,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>558521</v>
+        <v>558412</v>
       </c>
       <c r="R88" t="n">
-        <v>6624319</v>
+        <v>6624060</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9759,12 +9773,17 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2022-11-12</t>
+          <t>2024-10-03</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9773,6 +9792,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9795,7 +9815,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121394333</v>
+        <v>121359471</v>
       </c>
       <c r="B89" t="n">
         <v>97358</v>
@@ -9830,10 +9850,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>558528</v>
+        <v>558521</v>
       </c>
       <c r="R89" t="n">
-        <v>6624316</v>
+        <v>6624319</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9860,12 +9880,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9896,10 +9916,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121394547</v>
+        <v>121394333</v>
       </c>
       <c r="B90" t="n">
-        <v>90522</v>
+        <v>97358</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9907,21 +9927,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4962</v>
+        <v>53</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9931,10 +9951,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>558553</v>
+        <v>558528</v>
       </c>
       <c r="R90" t="n">
-        <v>6624265</v>
+        <v>6624316</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9961,12 +9981,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9997,10 +10017,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121394332</v>
+        <v>121394547</v>
       </c>
       <c r="B91" t="n">
-        <v>75428</v>
+        <v>90522</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10008,21 +10028,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6426</v>
+        <v>4962</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10032,10 +10052,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>558554</v>
+        <v>558553</v>
       </c>
       <c r="R91" t="n">
-        <v>6624337</v>
+        <v>6624265</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10062,12 +10082,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10098,54 +10118,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121394272</v>
+        <v>121394332</v>
       </c>
       <c r="B92" t="n">
-        <v>58826</v>
+        <v>75428</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>208242</v>
+        <v>6426</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Fanfluken, Vstm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>558519</v>
+        <v>558554</v>
       </c>
       <c r="R92" t="n">
-        <v>6624313</v>
+        <v>6624337</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10172,17 +10183,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>under ved i barrskog</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10213,37 +10219,42 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121394270</v>
+        <v>121394272</v>
       </c>
       <c r="B93" t="n">
-        <v>99118</v>
+        <v>58826</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>208242</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10252,10 +10263,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>558522</v>
+        <v>558519</v>
       </c>
       <c r="R93" t="n">
-        <v>6624290</v>
+        <v>6624313</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10290,6 +10301,11 @@
           <t>2024-09-23</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>under ved i barrskog</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
@@ -10311,6 +10327,111 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>121394270</v>
+      </c>
+      <c r="B94" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Fanfluken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>558522</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6624290</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-09-23</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
         <is>
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>

--- a/artfynd/A 31280-2024 artfynd.xlsx
+++ b/artfynd/A 31280-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY94"/>
+  <dimension ref="A1:AZ94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359455</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359471</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394198</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394206</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394310</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394321</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394333</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394945</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1582,6 +1627,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394356</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1684,6 +1734,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394942</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1785,6 +1840,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359467</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1886,6 +1946,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359462</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1987,6 +2052,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359469</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2088,6 +2158,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359443</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2189,6 +2264,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394327</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2290,6 +2370,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394386</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2416,6 +2501,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127436384</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2517,6 +2607,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394320</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2616,6 +2711,11 @@
       <c r="AY20" t="inlineStr">
         <is>
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394348</t>
         </is>
       </c>
     </row>
@@ -2738,6 +2838,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394355</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2839,6 +2944,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394350</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2940,6 +3050,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394309</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3041,6 +3156,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394357</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3142,6 +3262,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394311</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3243,6 +3368,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394349</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3344,6 +3474,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394354</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3445,6 +3580,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394344</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3546,6 +3686,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394547</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3647,6 +3792,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359507</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3771,6 +3921,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119713775</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3872,6 +4027,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359466</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3973,6 +4133,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394944</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4074,6 +4239,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359458</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4173,6 +4343,11 @@
       <c r="AY35" t="inlineStr">
         <is>
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394549</t>
         </is>
       </c>
     </row>
@@ -4280,6 +4455,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359444</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4381,6 +4561,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394202</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4482,6 +4667,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394315</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4588,6 +4778,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394494</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4689,6 +4884,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394332</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4790,6 +4990,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394336</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4891,6 +5096,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394339</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4992,6 +5202,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394342</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5093,6 +5308,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394343</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5194,6 +5414,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394359</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5295,6 +5520,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394366</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5396,6 +5626,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394334</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5497,6 +5732,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359459</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5598,6 +5838,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359461</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5699,6 +5944,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359505</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5800,6 +6050,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394203</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5901,6 +6156,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394326</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6002,6 +6262,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394353</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6117,6 +6382,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121447429</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6218,6 +6488,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394323</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6319,6 +6594,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394325</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6420,6 +6700,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394352</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6521,6 +6806,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394363</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6632,6 +6922,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830133</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6744,6 +7039,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119830097</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6845,6 +7145,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394322</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6946,6 +7251,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394324</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7045,6 +7355,11 @@
       <c r="AY63" t="inlineStr">
         <is>
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394351</t>
         </is>
       </c>
     </row>
@@ -7169,6 +7484,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119713808</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7270,6 +7590,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359453</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7371,6 +7696,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359460</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7472,6 +7802,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359506</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7573,6 +7908,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394205</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7674,6 +8014,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394319</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7775,6 +8120,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394364</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7896,6 +8246,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134450333</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8011,6 +8366,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394272</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8135,6 +8495,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119713512</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8259,6 +8624,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119713516</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8383,6 +8753,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119713527</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8507,6 +8882,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119713553</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8636,6 +9016,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119713735</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8760,6 +9145,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119713763</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8884,6 +9274,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119713818</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8989,6 +9384,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394270</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9094,6 +9494,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394303</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9199,6 +9604,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394304</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9304,6 +9714,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394305</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9409,6 +9824,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394306</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9506,6 +9926,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132753060</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9608,6 +10033,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3424440</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9706,6 +10136,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394345</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9813,6 +10248,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127436389</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9911,6 +10351,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5981824</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10013,6 +10458,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121359465</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10120,6 +10570,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394207</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10227,6 +10682,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394314</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10329,6 +10789,11 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394365</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10436,8 +10901,108 @@
           <t>Naturvärdesinventering i skogsmark kring Bosjön, Timmerbacksmyren, Fanfluken och Vålbo</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121394313</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>